--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W539"/>
+  <dimension ref="A1:W540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27611,7 +27611,7 @@
       <c r="S305" t="inlineStr"/>
       <c r="T305" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U305" t="inlineStr">
@@ -27619,7 +27619,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V305" t="inlineStr"/>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:23:34</t>
+        </is>
+      </c>
       <c r="W305" t="inlineStr"/>
     </row>
     <row r="306">
@@ -28056,7 +28060,7 @@
       <c r="S310" t="inlineStr"/>
       <c r="T310" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U310" t="inlineStr">
@@ -28064,7 +28068,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V310" t="inlineStr"/>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:23:34</t>
+        </is>
+      </c>
       <c r="W310" t="inlineStr"/>
     </row>
     <row r="311">
@@ -29391,7 +29399,7 @@
       <c r="S325" t="inlineStr"/>
       <c r="T325" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U325" t="inlineStr">
@@ -29399,7 +29407,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V325" t="inlineStr"/>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:23:34</t>
+        </is>
+      </c>
       <c r="W325" t="inlineStr"/>
     </row>
     <row r="326">
@@ -29569,7 +29581,7 @@
       <c r="S327" t="inlineStr"/>
       <c r="T327" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U327" t="inlineStr">
@@ -29577,7 +29589,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V327" t="inlineStr"/>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:23:34</t>
+        </is>
+      </c>
       <c r="W327" t="inlineStr"/>
     </row>
     <row r="328">
@@ -29658,7 +29674,7 @@
       <c r="S328" t="inlineStr"/>
       <c r="T328" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U328" t="inlineStr">
@@ -29666,7 +29682,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V328" t="inlineStr"/>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:23:34</t>
+        </is>
+      </c>
       <c r="W328" t="inlineStr"/>
     </row>
     <row r="329">
@@ -48562,6 +48582,103 @@
       <c r="V539" t="inlineStr"/>
       <c r="W539" t="inlineStr"/>
     </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41010759_1</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>41010759_1</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41010759</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:15:43</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>2026-03-04 08:06:33</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:15:43</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>2026-03-04 09:00:00</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:00:00</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>4809</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>47.38389</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>21.85938</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr"/>
+      <c r="P540" t="inlineStr"/>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>450.0</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S540" t="inlineStr"/>
+      <c r="T540" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:23:34</t>
+        </is>
+      </c>
+      <c r="V540" t="inlineStr"/>
+      <c r="W540" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W540"/>
+  <dimension ref="A1:W545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27704,7 +27704,7 @@
       <c r="S306" t="inlineStr"/>
       <c r="T306" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U306" t="inlineStr">
@@ -27712,7 +27712,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V306" t="inlineStr"/>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
       <c r="W306" t="inlineStr"/>
     </row>
     <row r="307">
@@ -27882,7 +27886,7 @@
       <c r="S308" t="inlineStr"/>
       <c r="T308" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U308" t="inlineStr">
@@ -27890,7 +27894,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V308" t="inlineStr"/>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
       <c r="W308" t="inlineStr"/>
     </row>
     <row r="309">
@@ -28331,7 +28339,7 @@
       <c r="S313" t="inlineStr"/>
       <c r="T313" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U313" t="inlineStr">
@@ -28339,7 +28347,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V313" t="inlineStr"/>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
       <c r="W313" t="inlineStr"/>
     </row>
     <row r="314">
@@ -28509,7 +28521,7 @@
       <c r="S315" t="inlineStr"/>
       <c r="T315" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U315" t="inlineStr">
@@ -28517,7 +28529,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V315" t="inlineStr"/>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
       <c r="W315" t="inlineStr"/>
     </row>
     <row r="316">
@@ -28954,7 +28970,7 @@
       <c r="S320" t="inlineStr"/>
       <c r="T320" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U320" t="inlineStr">
@@ -28962,7 +28978,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V320" t="inlineStr"/>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
       <c r="W320" t="inlineStr"/>
     </row>
     <row r="321">
@@ -29043,7 +29063,7 @@
       <c r="S321" t="inlineStr"/>
       <c r="T321" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U321" t="inlineStr">
@@ -29051,7 +29071,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V321" t="inlineStr"/>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
       <c r="W321" t="inlineStr"/>
     </row>
     <row r="322">
@@ -29492,7 +29516,7 @@
       <c r="S326" t="inlineStr"/>
       <c r="T326" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U326" t="inlineStr">
@@ -29500,7 +29524,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V326" t="inlineStr"/>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
       <c r="W326" t="inlineStr"/>
     </row>
     <row r="327">
@@ -30034,7 +30062,7 @@
       <c r="S332" t="inlineStr"/>
       <c r="T332" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U332" t="inlineStr">
@@ -30042,7 +30070,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V332" t="inlineStr"/>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
       <c r="W332" t="inlineStr"/>
     </row>
     <row r="333">
@@ -30661,7 +30693,7 @@
       <c r="S339" t="inlineStr"/>
       <c r="T339" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U339" t="inlineStr">
@@ -30669,7 +30701,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V339" t="inlineStr"/>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
       <c r="W339" t="inlineStr"/>
     </row>
     <row r="340">
@@ -32178,7 +32214,7 @@
       <c r="S356" t="inlineStr"/>
       <c r="T356" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U356" t="inlineStr">
@@ -32186,7 +32222,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V356" t="inlineStr"/>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
       <c r="W356" t="inlineStr"/>
     </row>
     <row r="357">
@@ -48668,7 +48708,7 @@
       <c r="S540" t="inlineStr"/>
       <c r="T540" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U540" t="inlineStr">
@@ -48676,8 +48716,497 @@
           <t>2026-03-04 16:23:34</t>
         </is>
       </c>
-      <c r="V540" t="inlineStr"/>
+      <c r="V540" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
       <c r="W540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011029_1</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>41011029_1</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011029</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:20:57</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:20:57</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:20:57</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:20:00</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:19:00</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>47.36562</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>19.145012</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr"/>
+      <c r="P541" t="inlineStr"/>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S541" t="inlineStr"/>
+      <c r="T541" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
+      <c r="V541" t="inlineStr"/>
+      <c r="W541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011030_1</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>41011030_1</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011030</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:36:31</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:36:31</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:36:31</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>2026-04-30 15:00:00</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>47.814903</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>19.678185</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr"/>
+      <c r="P542" t="inlineStr"/>
+      <c r="Q542" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S542" t="inlineStr"/>
+      <c r="T542" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
+      <c r="V542" t="inlineStr"/>
+      <c r="W542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011031_1</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>41011031_1</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011031</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>VehicleObstruction</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:41:05</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:41:05</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:41:05</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:35:00</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:40:00</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>47.193466</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>20.411259</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr"/>
+      <c r="P543" t="inlineStr"/>
+      <c r="Q543" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S543" t="inlineStr"/>
+      <c r="T543" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
+      <c r="V543" t="inlineStr"/>
+      <c r="W543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011032_1</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>41011032_1</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011032</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:44:32</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:44:32</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:44:32</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>2026-04-30 15:00:00</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>47.81495</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>19.678062</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr"/>
+      <c r="P544" t="inlineStr"/>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S544" t="inlineStr"/>
+      <c r="T544" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
+      <c r="V544" t="inlineStr"/>
+      <c r="W544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011033_1</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>41011033_1</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011033</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:51:59</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:51:59</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:51:59</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:00:00</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>47.962948</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>19.75675</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr"/>
+      <c r="P545" t="inlineStr"/>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>990.0</t>
+        </is>
+      </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S545" t="inlineStr"/>
+      <c r="T545" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:04:10</t>
+        </is>
+      </c>
+      <c r="V545" t="inlineStr"/>
+      <c r="W545" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W545"/>
+  <dimension ref="A1:W552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,7 +704,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -712,7 +712,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -26806,7 +26810,7 @@
       <c r="S296" t="inlineStr"/>
       <c r="T296" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U296" t="inlineStr">
@@ -26814,7 +26818,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V296" t="inlineStr"/>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
       <c r="W296" t="inlineStr"/>
     </row>
     <row r="297">
@@ -27797,7 +27805,7 @@
       <c r="S307" t="inlineStr"/>
       <c r="T307" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U307" t="inlineStr">
@@ -27805,7 +27813,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V307" t="inlineStr"/>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
       <c r="W307" t="inlineStr"/>
     </row>
     <row r="308">
@@ -30786,7 +30798,7 @@
       <c r="S340" t="inlineStr"/>
       <c r="T340" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U340" t="inlineStr">
@@ -30794,7 +30806,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V340" t="inlineStr"/>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
       <c r="W340" t="inlineStr"/>
     </row>
     <row r="341">
@@ -30968,7 +30984,7 @@
       <c r="S342" t="inlineStr"/>
       <c r="T342" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U342" t="inlineStr">
@@ -30976,7 +30992,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V342" t="inlineStr"/>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
       <c r="W342" t="inlineStr"/>
     </row>
     <row r="343">
@@ -32125,7 +32145,7 @@
       <c r="S355" t="inlineStr"/>
       <c r="T355" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U355" t="inlineStr">
@@ -32133,7 +32153,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V355" t="inlineStr"/>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
       <c r="W355" t="inlineStr"/>
     </row>
     <row r="356">
@@ -48514,7 +48538,7 @@
       <c r="S538" t="inlineStr"/>
       <c r="T538" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U538" t="inlineStr">
@@ -48522,7 +48546,11 @@
           <t>2026-03-04 16:12:19</t>
         </is>
       </c>
-      <c r="V538" t="inlineStr"/>
+      <c r="V538" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
       <c r="W538" t="inlineStr"/>
     </row>
     <row r="539">
@@ -48611,7 +48639,7 @@
       <c r="S539" t="inlineStr"/>
       <c r="T539" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U539" t="inlineStr">
@@ -48619,7 +48647,11 @@
           <t>2026-03-04 16:12:19</t>
         </is>
       </c>
-      <c r="V539" t="inlineStr"/>
+      <c r="V539" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
       <c r="W539" t="inlineStr"/>
     </row>
     <row r="540">
@@ -48809,7 +48841,7 @@
       <c r="S541" t="inlineStr"/>
       <c r="T541" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U541" t="inlineStr">
@@ -48817,7 +48849,11 @@
           <t>2026-03-04 17:04:10</t>
         </is>
       </c>
-      <c r="V541" t="inlineStr"/>
+      <c r="V541" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
       <c r="W541" t="inlineStr"/>
     </row>
     <row r="542">
@@ -49003,7 +49039,7 @@
       <c r="S543" t="inlineStr"/>
       <c r="T543" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U543" t="inlineStr">
@@ -49011,7 +49047,11 @@
           <t>2026-03-04 17:04:10</t>
         </is>
       </c>
-      <c r="V543" t="inlineStr"/>
+      <c r="V543" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
       <c r="W543" t="inlineStr"/>
     </row>
     <row r="544">
@@ -49207,6 +49247,681 @@
       </c>
       <c r="V545" t="inlineStr"/>
       <c r="W545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133691_1</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>3133691_1</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133691</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:53:21</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:37:47</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:53:21</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:30:00</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>47.912506</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>21.715769</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr"/>
+      <c r="P546" t="inlineStr"/>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S546" t="inlineStr"/>
+      <c r="T546" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
+      <c r="V546" t="inlineStr"/>
+      <c r="W546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011034_1</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>41011034_1</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011034</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:59:59</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:59:59</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:59:59</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>2026-03-20 15:00:00</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>2116</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>47.900497</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>19.33857</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr"/>
+      <c r="P547" t="inlineStr"/>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>970.0</t>
+        </is>
+      </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S547" t="inlineStr"/>
+      <c r="T547" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
+      <c r="V547" t="inlineStr"/>
+      <c r="W547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011035_1</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>41011035_1</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011035</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:05:23</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:05:23</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:05:23</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>2026-03-06 08:00:00</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>2026-05-30 15:00:00</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>47.958687</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>19.230423</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr"/>
+      <c r="P548" t="inlineStr"/>
+      <c r="Q548" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S548" t="inlineStr"/>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
+      <c r="V548" t="inlineStr"/>
+      <c r="W548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011036_1</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>41011036_1</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011036</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:12:09</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:12:09</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:12:09</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>2026-03-06 08:00:00</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>2026-05-30 15:00:00</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>47.963436</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>19.287127</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr"/>
+      <c r="P549" t="inlineStr"/>
+      <c r="Q549" t="inlineStr">
+        <is>
+          <t>394.0</t>
+        </is>
+      </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S549" t="inlineStr"/>
+      <c r="T549" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
+      <c r="V549" t="inlineStr"/>
+      <c r="W549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011037_1</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>41011037_1</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011037</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:20:54</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:20:54</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:20:54</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>2026-03-06 08:00:00</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>2026-03-30 15:00:00</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>2116</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>47.900536</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>19.338537</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr"/>
+      <c r="P550" t="inlineStr"/>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>966.0</t>
+        </is>
+      </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S550" t="inlineStr"/>
+      <c r="T550" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
+      <c r="V550" t="inlineStr"/>
+      <c r="W550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011038_1</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>41011038_1</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011038</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:38:40</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:38:40</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:38:40</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:30:00</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:30:00</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>47.90389</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>21.712402</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr"/>
+      <c r="P551" t="inlineStr"/>
+      <c r="Q551" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S551" t="inlineStr"/>
+      <c r="T551" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
+      <c r="V551" t="inlineStr"/>
+      <c r="W551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011039_1</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>41011039_1</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011039</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>AbnormalTraffic</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:59:15</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:59:15</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>2026-03-04 17:59:15</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:00:00</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>2026-03-04 23:58:00</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>47.50919</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>18.61698</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr"/>
+      <c r="P552" t="inlineStr"/>
+      <c r="Q552" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R552" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S552" t="inlineStr"/>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:01:44</t>
+        </is>
+      </c>
+      <c r="V552" t="inlineStr"/>
+      <c r="W552" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W552"/>
+  <dimension ref="A1:W557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,7 +619,7 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,7 +627,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:54:25</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -27352,7 +27356,7 @@
       <c r="S302" t="inlineStr"/>
       <c r="T302" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U302" t="inlineStr">
@@ -27360,7 +27364,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V302" t="inlineStr"/>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:54:25</t>
+        </is>
+      </c>
       <c r="W302" t="inlineStr"/>
     </row>
     <row r="303">
@@ -49923,6 +49931,495 @@
       <c r="V552" t="inlineStr"/>
       <c r="W552" t="inlineStr"/>
     </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41010041_1</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>41010041_1</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41010041</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:24:04</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>2026-03-02 14:56:59</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:24:04</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>2026-03-03 08:00:00</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>46.593163</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>20.296783</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr"/>
+      <c r="P553" t="inlineStr"/>
+      <c r="Q553" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R553" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>4413 kereszteződéstől vásárhely felé kb 200m ig külső sáv zárással kátyúzás</t>
+        </is>
+      </c>
+      <c r="T553" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:54:25</t>
+        </is>
+      </c>
+      <c r="V553" t="inlineStr"/>
+      <c r="W553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011040_1</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>41011040_1</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011040</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:07:48</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:07:48</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:07:48</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>46.382095</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>18.71068</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr"/>
+      <c r="P554" t="inlineStr"/>
+      <c r="Q554" t="inlineStr">
+        <is>
+          <t>980.0</t>
+        </is>
+      </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S554" t="inlineStr"/>
+      <c r="T554" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:54:25</t>
+        </is>
+      </c>
+      <c r="V554" t="inlineStr"/>
+      <c r="W554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011041_1</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>41011041_1</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011041</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:18:09</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:18:09</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:18:09</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:20:00</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>47.479607</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>20.005018</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr"/>
+      <c r="P555" t="inlineStr"/>
+      <c r="Q555" t="inlineStr">
+        <is>
+          <t>875.0</t>
+        </is>
+      </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S555" t="inlineStr"/>
+      <c r="T555" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:54:25</t>
+        </is>
+      </c>
+      <c r="V555" t="inlineStr"/>
+      <c r="W555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011042_1</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>41011042_1</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011042</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:19:32</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:19:32</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:19:32</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:20:00</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>47.32396</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>20.09212</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr"/>
+      <c r="P556" t="inlineStr"/>
+      <c r="Q556" t="inlineStr">
+        <is>
+          <t>681.0</t>
+        </is>
+      </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S556" t="inlineStr"/>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:54:25</t>
+        </is>
+      </c>
+      <c r="V556" t="inlineStr"/>
+      <c r="W556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011043_1</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>41011043_1</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011043</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:49:07</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:49:07</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:49:07</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:30:00</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>47.33023</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>19.142418</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr"/>
+      <c r="P557" t="inlineStr"/>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S557" t="inlineStr"/>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:54:25</t>
+        </is>
+      </c>
+      <c r="V557" t="inlineStr"/>
+      <c r="W557" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W557"/>
+  <dimension ref="A1:W565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45419,7 +45419,7 @@
       <c r="S503" t="inlineStr"/>
       <c r="T503" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U503" t="inlineStr">
@@ -45427,7 +45427,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V503" t="inlineStr"/>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
       <c r="W503" t="inlineStr"/>
     </row>
     <row r="504">
@@ -49338,7 +49342,7 @@
       <c r="S546" t="inlineStr"/>
       <c r="T546" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U546" t="inlineStr">
@@ -49346,7 +49350,11 @@
           <t>2026-03-04 18:01:44</t>
         </is>
       </c>
-      <c r="V546" t="inlineStr"/>
+      <c r="V546" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
       <c r="W546" t="inlineStr"/>
     </row>
     <row r="547">
@@ -49823,7 +49831,7 @@
       <c r="S551" t="inlineStr"/>
       <c r="T551" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U551" t="inlineStr">
@@ -49831,7 +49839,11 @@
           <t>2026-03-04 18:01:44</t>
         </is>
       </c>
-      <c r="V551" t="inlineStr"/>
+      <c r="V551" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
       <c r="W551" t="inlineStr"/>
     </row>
     <row r="552">
@@ -49920,7 +49932,7 @@
       <c r="S552" t="inlineStr"/>
       <c r="T552" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U552" t="inlineStr">
@@ -49928,7 +49940,11 @@
           <t>2026-03-04 18:01:44</t>
         </is>
       </c>
-      <c r="V552" t="inlineStr"/>
+      <c r="V552" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
       <c r="W552" t="inlineStr"/>
     </row>
     <row r="553">
@@ -50419,6 +50435,782 @@
       </c>
       <c r="V557" t="inlineStr"/>
       <c r="W557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011044_1</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>41011044_1</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011044</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>NonWeatherRelatedRoadConditions</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:08:52</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:08:52</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:08:52</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:06:00</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>2026-03-08 13:00:00</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>46.1574</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>18.432257</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr"/>
+      <c r="P558" t="inlineStr"/>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S558" t="inlineStr"/>
+      <c r="T558" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
+      <c r="V558" t="inlineStr"/>
+      <c r="W558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011045_1</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>41011045_1</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011045</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>PublicEvent</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:23:20</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:13:26</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:23:20</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>2026-04-19 08:30:00</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>2026-04-19 08:40:00</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>47.879177</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>17.280956</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr"/>
+      <c r="P559" t="inlineStr"/>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>710.0</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S559" t="inlineStr"/>
+      <c r="T559" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
+      <c r="V559" t="inlineStr"/>
+      <c r="W559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011046_1</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>41011046_1</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011046</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>PublicEvent</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:23:10</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:18:07</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:23:10</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>2026-04-19 08:30:00</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:00:00</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>47.857185</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>17.289127</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr"/>
+      <c r="P560" t="inlineStr"/>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S560" t="inlineStr"/>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
+      <c r="V560" t="inlineStr"/>
+      <c r="W560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011047_1</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>41011047_1</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011047</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>PublicEvent</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:43:18</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:23:02</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:43:18</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>2026-04-19 08:30:00</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:00:00</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>47.85673</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>17.279995</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr"/>
+      <c r="P561" t="inlineStr"/>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>225.0</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S561" t="inlineStr"/>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
+      <c r="V561" t="inlineStr"/>
+      <c r="W561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011048_1</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>41011048_1</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011048</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:29:42</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:29:42</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:29:42</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>2026-03-16 06:00:00</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>2026-06-30 22:00:00</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>47.4348</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>17.82487</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr"/>
+      <c r="P562" t="inlineStr"/>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>925.0</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S562" t="inlineStr"/>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
+      <c r="V562" t="inlineStr"/>
+      <c r="W562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011049_1</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>41011049_1</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011049</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:32:32</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:31:45</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:32:32</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>2026-03-16 06:00:00</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>2026-06-30 22:00:00</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>47.430645</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>17.828508</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr"/>
+      <c r="P563" t="inlineStr"/>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>386.0</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr"/>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
+      <c r="V563" t="inlineStr"/>
+      <c r="W563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011050_1</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>41011050_1</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011050</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:43:10</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:37:18</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:43:10</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>2026-03-09 06:00:00</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>2026-06-15 22:00:00</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>47.732807</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>17.829533</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr"/>
+      <c r="P564" t="inlineStr"/>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>529.0</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S564" t="inlineStr"/>
+      <c r="T564" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
+      <c r="V564" t="inlineStr"/>
+      <c r="W564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011051_1</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>41011051_1</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011051</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:48:52</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:48:52</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:48:52</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:47:00</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>2026-03-04 23:00:00</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>46.811295</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>21.01325</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr"/>
+      <c r="P565" t="inlineStr"/>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S565" t="inlineStr"/>
+      <c r="T565" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:12</t>
+        </is>
+      </c>
+      <c r="V565" t="inlineStr"/>
+      <c r="W565" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W565"/>
+  <dimension ref="A1:W567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51212,6 +51212,196 @@
       <c r="V565" t="inlineStr"/>
       <c r="W565" t="inlineStr"/>
     </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133692_1</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>3133692_1</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133692</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:21:04</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:04:18</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:21:04</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:00</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>47.47448</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>18.853289</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr"/>
+      <c r="P566" t="inlineStr"/>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>950.0</t>
+        </is>
+      </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S566" t="inlineStr"/>
+      <c r="T566" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:40:26</t>
+        </is>
+      </c>
+      <c r="V566" t="inlineStr"/>
+      <c r="W566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011052_1</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>41011052_1</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011052</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:54:02</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:54:02</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:54:02</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:50:00</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>2026-03-05 04:30:00</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>47.480156</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>18.842989</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr"/>
+      <c r="P567" t="inlineStr"/>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S567" t="inlineStr"/>
+      <c r="T567" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:40:26</t>
+        </is>
+      </c>
+      <c r="V567" t="inlineStr"/>
+      <c r="W567" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W567"/>
+  <dimension ref="A1:W569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51402,6 +51402,196 @@
       <c r="V567" t="inlineStr"/>
       <c r="W567" t="inlineStr"/>
     </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133693_1</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>3133693_1</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133693</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:47:54</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:47:54</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:47:54</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:18:00</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>47.60361</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>19.195032</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr"/>
+      <c r="P568" t="inlineStr"/>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="R568" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S568" t="inlineStr"/>
+      <c r="T568" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:56:51</t>
+        </is>
+      </c>
+      <c r="V568" t="inlineStr"/>
+      <c r="W568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011055_1</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>41011055_1</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011055</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:48:34</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:48:34</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:48:34</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>2026-03-04 18:18:00</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:48:00</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>47.603867</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>19.195568</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr"/>
+      <c r="P569" t="inlineStr"/>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S569" t="inlineStr"/>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:56:51</t>
+        </is>
+      </c>
+      <c r="V569" t="inlineStr"/>
+      <c r="W569" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W569"/>
+  <dimension ref="A1:W570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51391,7 +51391,7 @@
       <c r="S567" t="inlineStr"/>
       <c r="T567" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U567" t="inlineStr">
@@ -51399,7 +51399,11 @@
           <t>2026-03-04 20:40:26</t>
         </is>
       </c>
-      <c r="V567" t="inlineStr"/>
+      <c r="V567" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:04:47</t>
+        </is>
+      </c>
       <c r="W567" t="inlineStr"/>
     </row>
     <row r="568">
@@ -51484,7 +51488,7 @@
       <c r="S568" t="inlineStr"/>
       <c r="T568" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U568" t="inlineStr">
@@ -51492,7 +51496,11 @@
           <t>2026-03-04 20:56:51</t>
         </is>
       </c>
-      <c r="V568" t="inlineStr"/>
+      <c r="V568" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:04:47</t>
+        </is>
+      </c>
       <c r="W568" t="inlineStr"/>
     </row>
     <row r="569">
@@ -51581,7 +51589,7 @@
       <c r="S569" t="inlineStr"/>
       <c r="T569" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U569" t="inlineStr">
@@ -51589,8 +51597,109 @@
           <t>2026-03-04 20:56:51</t>
         </is>
       </c>
-      <c r="V569" t="inlineStr"/>
+      <c r="V569" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:04:47</t>
+        </is>
+      </c>
       <c r="W569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011056_1</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>41011056_1</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011056</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:59:30</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:59:30</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:59:30</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:50:00</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:15:00</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>47.480156</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>18.842989</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr"/>
+      <c r="P570" t="inlineStr"/>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S570" t="inlineStr"/>
+      <c r="T570" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:04:47</t>
+        </is>
+      </c>
+      <c r="V570" t="inlineStr"/>
+      <c r="W570" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W570"/>
+  <dimension ref="A1:W572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51701,6 +51701,200 @@
       <c r="V570" t="inlineStr"/>
       <c r="W570" t="inlineStr"/>
     </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011057_1</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>41011057_1</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011057</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:23:35</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:23:35</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:23:35</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:15:00</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>2026-03-04 23:15:00</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>47.870255</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>20.38241</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr"/>
+      <c r="P571" t="inlineStr"/>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>750.0</t>
+        </is>
+      </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S571" t="inlineStr"/>
+      <c r="T571" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:48:08</t>
+        </is>
+      </c>
+      <c r="V571" t="inlineStr"/>
+      <c r="W571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011058_1</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>41011058_1</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011058</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>NonWeatherRelatedRoadConditions</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:40:53</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:40:53</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:40:53</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:39:00</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>2026-03-08 13:00:00</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>5607</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>46.155712</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>18.436403</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr"/>
+      <c r="P572" t="inlineStr"/>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>638.0</t>
+        </is>
+      </c>
+      <c r="R572" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S572" t="inlineStr"/>
+      <c r="T572" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>2026-03-04 21:48:08</t>
+        </is>
+      </c>
+      <c r="V572" t="inlineStr"/>
+      <c r="W572" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -24941,7 +24941,7 @@
       <c r="S275" t="inlineStr"/>
       <c r="T275" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
@@ -24949,7 +24949,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V275" t="inlineStr"/>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:21:01</t>
+        </is>
+      </c>
       <c r="W275" t="inlineStr"/>
     </row>
     <row r="276">
@@ -51294,7 +51298,7 @@
       <c r="S566" t="inlineStr"/>
       <c r="T566" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U566" t="inlineStr">
@@ -51302,7 +51306,11 @@
           <t>2026-03-04 20:40:26</t>
         </is>
       </c>
-      <c r="V566" t="inlineStr"/>
+      <c r="V566" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:21:01</t>
+        </is>
+      </c>
       <c r="W566" t="inlineStr"/>
     </row>
     <row r="567">

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W572"/>
+  <dimension ref="A1:W574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51903,6 +51903,200 @@
       <c r="V572" t="inlineStr"/>
       <c r="W572" t="inlineStr"/>
     </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011059_1</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>41011059_1</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011059</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:30:21</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:30:21</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:30:21</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:10:00</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:15:00</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>47.498783</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>18.559254</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr"/>
+      <c r="P573" t="inlineStr"/>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr"/>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:55:46</t>
+        </is>
+      </c>
+      <c r="V573" t="inlineStr"/>
+      <c r="W573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011060_1</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>41011060_1</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011060</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:33:38</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:33:38</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:33:38</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:25:00</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:15:00</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>47.498783</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>18.559254</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr"/>
+      <c r="P574" t="inlineStr"/>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr"/>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>2026-03-04 22:55:46</t>
+        </is>
+      </c>
+      <c r="V574" t="inlineStr"/>
+      <c r="W574" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -26729,7 +26729,7 @@
       <c r="S295" t="inlineStr"/>
       <c r="T295" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U295" t="inlineStr">
@@ -26737,7 +26737,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V295" t="inlineStr"/>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>2026-03-04 23:38:27</t>
+        </is>
+      </c>
       <c r="W295" t="inlineStr"/>
     </row>
     <row r="296">
@@ -51205,7 +51209,7 @@
       <c r="S565" t="inlineStr"/>
       <c r="T565" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U565" t="inlineStr">
@@ -51213,7 +51217,11 @@
           <t>2026-03-04 19:55:12</t>
         </is>
       </c>
-      <c r="V565" t="inlineStr"/>
+      <c r="V565" t="inlineStr">
+        <is>
+          <t>2026-03-04 23:38:27</t>
+        </is>
+      </c>
       <c r="W565" t="inlineStr"/>
     </row>
     <row r="566">
@@ -51795,7 +51803,7 @@
       <c r="S571" t="inlineStr"/>
       <c r="T571" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U571" t="inlineStr">
@@ -51803,7 +51811,11 @@
           <t>2026-03-04 21:48:08</t>
         </is>
       </c>
-      <c r="V571" t="inlineStr"/>
+      <c r="V571" t="inlineStr">
+        <is>
+          <t>2026-03-04 23:38:27</t>
+        </is>
+      </c>
       <c r="W571" t="inlineStr"/>
     </row>
     <row r="572">

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W574"/>
+  <dimension ref="A1:W575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52109,6 +52109,103 @@
       <c r="V574" t="inlineStr"/>
       <c r="W574" t="inlineStr"/>
     </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011061_1</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>41011061_1</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011061</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>VehicleObstruction</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>2026-03-05 01:32:07</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>2026-03-05 01:32:07</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>2026-03-05 01:32:07</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>2026-03-05 01:30:00</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>M85</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>47.647743</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>17.406929</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr"/>
+      <c r="P575" t="inlineStr"/>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>630.0</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr"/>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>2026-03-05 03:50:50</t>
+        </is>
+      </c>
+      <c r="V575" t="inlineStr"/>
+      <c r="W575" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W575"/>
+  <dimension ref="A1:W576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51706,7 +51706,7 @@
       <c r="S570" t="inlineStr"/>
       <c r="T570" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U570" t="inlineStr">
@@ -51714,7 +51714,11 @@
           <t>2026-03-04 21:04:47</t>
         </is>
       </c>
-      <c r="V570" t="inlineStr"/>
+      <c r="V570" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:30:24</t>
+        </is>
+      </c>
       <c r="W570" t="inlineStr"/>
     </row>
     <row r="571">
@@ -52001,7 +52005,7 @@
       <c r="S573" t="inlineStr"/>
       <c r="T573" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U573" t="inlineStr">
@@ -52009,7 +52013,11 @@
           <t>2026-03-04 22:55:46</t>
         </is>
       </c>
-      <c r="V573" t="inlineStr"/>
+      <c r="V573" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:30:24</t>
+        </is>
+      </c>
       <c r="W573" t="inlineStr"/>
     </row>
     <row r="574">
@@ -52098,7 +52106,7 @@
       <c r="S574" t="inlineStr"/>
       <c r="T574" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U574" t="inlineStr">
@@ -52106,7 +52114,11 @@
           <t>2026-03-04 22:55:46</t>
         </is>
       </c>
-      <c r="V574" t="inlineStr"/>
+      <c r="V574" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:30:24</t>
+        </is>
+      </c>
       <c r="W574" t="inlineStr"/>
     </row>
     <row r="575">
@@ -52205,6 +52217,103 @@
       </c>
       <c r="V575" t="inlineStr"/>
       <c r="W575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011062_1</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>41011062_1</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011062</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>VehicleObstruction</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:21:38</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:17:14</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:21:38</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:00:00</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>2026-03-05 21:13:00</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>47.46775</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>18.866623</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr"/>
+      <c r="P576" t="inlineStr"/>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>750.0</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr"/>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:30:24</t>
+        </is>
+      </c>
+      <c r="V576" t="inlineStr"/>
+      <c r="W576" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W576"/>
+  <dimension ref="A1:W604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52315,6 +52315,2710 @@
       <c r="V576" t="inlineStr"/>
       <c r="W576" t="inlineStr"/>
     </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133697_1</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>3133697_1</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133697</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:08:46</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:08:46</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:08:46</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:00:00</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>47.139076</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>17.721476</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr"/>
+      <c r="P577" t="inlineStr"/>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr"/>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V577" t="inlineStr"/>
+      <c r="W577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133698_1</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>3133698_1</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133698</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:09:50</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:09:50</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:09:50</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:05:00</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>47.21251</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>18.296381</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr"/>
+      <c r="P578" t="inlineStr"/>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr"/>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V578" t="inlineStr"/>
+      <c r="W578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133699_1</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>3133699_1</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133699</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:14:52</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:14:52</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:14:52</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:05:00</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>M85</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>47.570206</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>16.816526</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr"/>
+      <c r="P579" t="inlineStr"/>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr"/>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V579" t="inlineStr"/>
+      <c r="W579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011063_1</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>41011063_1</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011063</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>VehicleObstruction</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:42:30</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:42:30</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:42:30</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:25:00</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>47.378876</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>19.065298</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr"/>
+      <c r="P580" t="inlineStr"/>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr"/>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V580" t="inlineStr"/>
+      <c r="W580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011064_1</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>41011064_1</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011064</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:43:31</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:43:31</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:43:31</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>2026-03-06 17:00:00</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>3834</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>48.13176</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>21.762642</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr"/>
+      <c r="P581" t="inlineStr"/>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S581" t="inlineStr"/>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V581" t="inlineStr"/>
+      <c r="W581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011065_1</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>41011065_1</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011065</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:45:23</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:45:23</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:45:23</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>2026-03-04 07:00:00</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>2026-05-29 17:00:00</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>48.005886</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>21.87136</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr"/>
+      <c r="P582" t="inlineStr"/>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>172.0</t>
+        </is>
+      </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S582" t="inlineStr"/>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V582" t="inlineStr"/>
+      <c r="W582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011066_1</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>41011066_1</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011066</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:47:01</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:47:01</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>2026-03-05 05:47:01</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>2026-03-02 07:00:00</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>2026-05-29 17:00:00</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>48.01366</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>21.833544</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr"/>
+      <c r="P583" t="inlineStr"/>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S583" t="inlineStr"/>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V583" t="inlineStr"/>
+      <c r="W583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011067_1</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>41011067_1</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011067</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:00:59</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:00:59</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:00:59</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:30:00</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>47.73787</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>18.133656</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr"/>
+      <c r="P584" t="inlineStr"/>
+      <c r="Q584" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S584" t="inlineStr"/>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V584" t="inlineStr"/>
+      <c r="W584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011068_1</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>41011068_1</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011068</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:01:31</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:01:31</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:01:31</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:30:00</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>47.742554</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>18.120495</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr"/>
+      <c r="P585" t="inlineStr"/>
+      <c r="Q585" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
+      </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S585" t="inlineStr"/>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V585" t="inlineStr"/>
+      <c r="W585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011069_1</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>41011069_1</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011069</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:02:15</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:02:15</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:02:15</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:30:00</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>8149</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>47.622974</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>17.9907</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr"/>
+      <c r="P586" t="inlineStr"/>
+      <c r="Q586" t="inlineStr">
+        <is>
+          <t>750.0</t>
+        </is>
+      </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S586" t="inlineStr"/>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V586" t="inlineStr"/>
+      <c r="W586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011070_1</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>41011070_1</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011070</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:02:46</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:02:46</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:02:46</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:30:00</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>8208</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>47.347664</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>18.047663</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr"/>
+      <c r="P587" t="inlineStr"/>
+      <c r="Q587" t="inlineStr">
+        <is>
+          <t>420.0</t>
+        </is>
+      </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S587" t="inlineStr"/>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V587" t="inlineStr"/>
+      <c r="W587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011071_1</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>41011071_1</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011071</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:03:35</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:03:35</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:03:35</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:30:00</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>8151</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>47.680946</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>17.973715</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr"/>
+      <c r="P588" t="inlineStr"/>
+      <c r="Q588" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S588" t="inlineStr"/>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V588" t="inlineStr"/>
+      <c r="W588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011072_1</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>41011072_1</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011072</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:04:31</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:04:31</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:04:31</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>8136</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>47.620808</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>18.149466</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr"/>
+      <c r="P589" t="inlineStr"/>
+      <c r="Q589" t="inlineStr">
+        <is>
+          <t>781.0</t>
+        </is>
+      </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S589" t="inlineStr"/>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V589" t="inlineStr"/>
+      <c r="W589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011073_1</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>41011073_1</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011073</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:06:47</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:06:47</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:06:47</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:30:00</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>8136</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>47.620426</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>18.152044</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr"/>
+      <c r="P590" t="inlineStr"/>
+      <c r="Q590" t="inlineStr">
+        <is>
+          <t>578.0</t>
+        </is>
+      </c>
+      <c r="R590" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S590" t="inlineStr"/>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V590" t="inlineStr"/>
+      <c r="W590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011074_1</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>41011074_1</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011074</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:09:52</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:09:52</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:09:52</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:00:00</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:00:00</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>47.937515</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>20.864342</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr"/>
+      <c r="P591" t="inlineStr"/>
+      <c r="Q591" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R591" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S591" t="inlineStr"/>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V591" t="inlineStr"/>
+      <c r="W591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011075_1</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>41011075_1</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011075</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:10:06</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:10:06</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:10:06</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:00:00</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:00</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>47.139114</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>17.720585</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr"/>
+      <c r="P592" t="inlineStr"/>
+      <c r="Q592" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="R592" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S592" t="inlineStr"/>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V592" t="inlineStr"/>
+      <c r="W592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011076_1</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>41011076_1</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011076</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:11:48</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:11:48</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:11:48</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:10:00</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:10:00</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>M35</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>47.79515</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>21.244772</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr"/>
+      <c r="P593" t="inlineStr"/>
+      <c r="Q593" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S593" t="inlineStr"/>
+      <c r="T593" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V593" t="inlineStr"/>
+      <c r="W593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011077_1</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>41011077_1</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011077</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:13:24</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:12:58</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:13:24</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:10:00</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:11:00</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>47.797337</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>21.231915</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr"/>
+      <c r="P594" t="inlineStr"/>
+      <c r="Q594" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R594" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S594" t="inlineStr"/>
+      <c r="T594" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V594" t="inlineStr"/>
+      <c r="W594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011078_1</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>41011078_1</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011078</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:13:17</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:13:17</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:13:17</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:05:00</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:12:00</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>47.21251</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>18.296381</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr"/>
+      <c r="P595" t="inlineStr"/>
+      <c r="Q595" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S595" t="inlineStr"/>
+      <c r="T595" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U595" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V595" t="inlineStr"/>
+      <c r="W595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011079_1</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>41011079_1</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011079</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:24:02</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:24:02</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:24:02</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:22:00</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>46.53423</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>17.221899</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr"/>
+      <c r="P596" t="inlineStr"/>
+      <c r="Q596" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S596" t="inlineStr"/>
+      <c r="T596" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U596" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V596" t="inlineStr"/>
+      <c r="W596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011080_1</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>41011080_1</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011080</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:24:49</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:24:49</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:24:49</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:24:00</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>6837</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>46.435066</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>16.907276</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr"/>
+      <c r="P597" t="inlineStr"/>
+      <c r="Q597" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S597" t="inlineStr"/>
+      <c r="T597" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U597" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V597" t="inlineStr"/>
+      <c r="W597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011081_1</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>41011081_1</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011081</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:26:47</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:26:47</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:26:47</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:00</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:25:00</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>75148</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>46.47284</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>16.729452</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr"/>
+      <c r="P598" t="inlineStr"/>
+      <c r="Q598" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R598" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S598" t="inlineStr"/>
+      <c r="T598" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U598" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V598" t="inlineStr"/>
+      <c r="W598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011082_1</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>41011082_1</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011082</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:27:56</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:27:56</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:27:56</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:00</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:27:00</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>45.957905</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>17.484158</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr"/>
+      <c r="P599" t="inlineStr"/>
+      <c r="Q599" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R599" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S599" t="inlineStr"/>
+      <c r="T599" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U599" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V599" t="inlineStr"/>
+      <c r="W599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011083_1</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>41011083_1</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011083</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:28:03</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:28:03</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:28:03</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>4613</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>47.028606</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>19.808968</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr"/>
+      <c r="P600" t="inlineStr"/>
+      <c r="Q600" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S600" t="inlineStr"/>
+      <c r="T600" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U600" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V600" t="inlineStr"/>
+      <c r="W600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011084_1</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>41011084_1</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011084</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:28:45</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:28:45</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:28:45</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:00</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:27:00</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>5825</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>45.875328</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>17.660065</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr"/>
+      <c r="P601" t="inlineStr"/>
+      <c r="Q601" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R601" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S601" t="inlineStr"/>
+      <c r="T601" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U601" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V601" t="inlineStr"/>
+      <c r="W601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011085_1</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>41011085_1</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011085</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:29:29</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:29:29</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:29:29</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:00</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:28:00</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>6802</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>46.048714</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>17.400047</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr"/>
+      <c r="P602" t="inlineStr"/>
+      <c r="Q602" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S602" t="inlineStr"/>
+      <c r="T602" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U602" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V602" t="inlineStr"/>
+      <c r="W602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011086_1</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>41011086_1</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011086</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:33:32</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:33:32</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:33:32</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:00</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>47.65119</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>18.627829</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr"/>
+      <c r="P603" t="inlineStr"/>
+      <c r="Q603" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="R603" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr"/>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V603" t="inlineStr"/>
+      <c r="W603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011087_1</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>41011087_1</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011087</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:23</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:23</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:23</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:30:00</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>47.70549</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>18.641624</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr"/>
+      <c r="P604" t="inlineStr"/>
+      <c r="Q604" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S604" t="inlineStr"/>
+      <c r="T604" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:34:57</t>
+        </is>
+      </c>
+      <c r="V604" t="inlineStr"/>
+      <c r="W604" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W604"/>
+  <dimension ref="A1:W697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52207,7 +52207,7 @@
       <c r="S575" t="inlineStr"/>
       <c r="T575" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U575" t="inlineStr">
@@ -52215,7 +52215,11 @@
           <t>2026-03-05 03:50:50</t>
         </is>
       </c>
-      <c r="V575" t="inlineStr"/>
+      <c r="V575" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
       <c r="W575" t="inlineStr"/>
     </row>
     <row r="576">
@@ -54038,7 +54042,7 @@
       <c r="S594" t="inlineStr"/>
       <c r="T594" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U594" t="inlineStr">
@@ -54046,7 +54050,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V594" t="inlineStr"/>
+      <c r="V594" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
       <c r="W594" t="inlineStr"/>
     </row>
     <row r="595">
@@ -55018,6 +55026,9015 @@
       </c>
       <c r="V604" t="inlineStr"/>
       <c r="W604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133701_1</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>3133701_1</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133701</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:46:22</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:35:46</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:46:22</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:21:00</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>47.83619</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>19.09437</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr"/>
+      <c r="P605" t="inlineStr"/>
+      <c r="Q605" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S605" t="inlineStr"/>
+      <c r="T605" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U605" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V605" t="inlineStr"/>
+      <c r="W605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133702_1</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>3133702_1</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133702</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:42</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:42</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:42</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>46.818913</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>18.973406</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr"/>
+      <c r="P606" t="inlineStr"/>
+      <c r="Q606" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="R606" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S606" t="inlineStr"/>
+      <c r="T606" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U606" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V606" t="inlineStr"/>
+      <c r="W606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133707_1</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>3133707_1</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133707</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:34</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:34</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:34</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:00</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>6231</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>46.616737</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>18.851877</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr"/>
+      <c r="P607" t="inlineStr"/>
+      <c r="Q607" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr"/>
+      <c r="T607" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U607" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V607" t="inlineStr"/>
+      <c r="W607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011088_1</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>41011088_1</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011088</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:35:39</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:35:39</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:35:39</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:30:00</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>47.814644</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>18.799677</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr"/>
+      <c r="P608" t="inlineStr"/>
+      <c r="Q608" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R608" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S608" t="inlineStr"/>
+      <c r="T608" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U608" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V608" t="inlineStr"/>
+      <c r="W608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011089_1</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>41011089_1</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011089</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:46:39</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:36:26</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:46:39</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:21:00</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:35:00</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>47.83619</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>19.09437</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr"/>
+      <c r="P609" t="inlineStr"/>
+      <c r="Q609" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S609" t="inlineStr"/>
+      <c r="T609" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U609" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V609" t="inlineStr"/>
+      <c r="W609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011090_1</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>41011090_1</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011090</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:38:59</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:38:59</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:38:59</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:00</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:20:00</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>48.329487</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>21.12839</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr"/>
+      <c r="P610" t="inlineStr"/>
+      <c r="Q610" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S610" t="inlineStr"/>
+      <c r="T610" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U610" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V610" t="inlineStr"/>
+      <c r="W610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011091_1</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>41011091_1</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011091</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:40:25</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:40:25</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:40:25</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>46.047997</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>17.786968</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr"/>
+      <c r="P611" t="inlineStr"/>
+      <c r="Q611" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S611" t="inlineStr"/>
+      <c r="T611" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U611" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V611" t="inlineStr"/>
+      <c r="W611" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011092_1</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>41011092_1</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011092</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:41:28</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:41:28</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:41:28</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:00</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:20:00</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>3707</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>48.294888</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>21.135088</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr"/>
+      <c r="P612" t="inlineStr"/>
+      <c r="Q612" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S612" t="inlineStr"/>
+      <c r="T612" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V612" t="inlineStr"/>
+      <c r="W612" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011093_1</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>41011093_1</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011093</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:05</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:05</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:05</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:20:00</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>47.935482</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>20.109013</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr"/>
+      <c r="P613" t="inlineStr"/>
+      <c r="Q613" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R613" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S613" t="inlineStr"/>
+      <c r="T613" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U613" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V613" t="inlineStr"/>
+      <c r="W613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011094_1</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>41011094_1</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011094</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:29</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:29</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:29</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>46.17253</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>17.8374</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr"/>
+      <c r="P614" t="inlineStr"/>
+      <c r="Q614" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R614" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S614" t="inlineStr"/>
+      <c r="T614" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V614" t="inlineStr"/>
+      <c r="W614" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011095_1</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>41011095_1</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011095</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:29</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:29</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:29</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:00</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:20:00</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>48.306072</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>21.103153</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr"/>
+      <c r="P615" t="inlineStr"/>
+      <c r="Q615" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S615" t="inlineStr"/>
+      <c r="T615" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V615" t="inlineStr"/>
+      <c r="W615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011096_1</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>41011096_1</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011096</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:47</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:47</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:42:47</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:20:00</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>47.81588</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>20.358507</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr"/>
+      <c r="P616" t="inlineStr"/>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S616" t="inlineStr"/>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V616" t="inlineStr"/>
+      <c r="W616" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011097_1</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>41011097_1</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011097</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:48:07</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:48:07</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:48:07</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:30:00</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>44133</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>46.25295</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>20.324284</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr"/>
+      <c r="P617" t="inlineStr"/>
+      <c r="Q617" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S617" t="inlineStr"/>
+      <c r="T617" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V617" t="inlineStr"/>
+      <c r="W617" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011098_1</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>41011098_1</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011098</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:49:26</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:49:26</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:49:26</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:30:00</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>44124</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>46.21918</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>20.326477</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr"/>
+      <c r="P618" t="inlineStr"/>
+      <c r="Q618" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S618" t="inlineStr"/>
+      <c r="T618" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U618" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V618" t="inlineStr"/>
+      <c r="W618" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011099_1</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>41011099_1</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011099</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:52:44</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:52:44</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:52:44</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:00</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:00:00</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>48.046337</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>21.886572</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr"/>
+      <c r="P619" t="inlineStr"/>
+      <c r="Q619" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S619" t="inlineStr"/>
+      <c r="T619" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V619" t="inlineStr"/>
+      <c r="W619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011100_1</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>41011100_1</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011100</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:53:34</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:53:34</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:53:34</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:00</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>48.043804</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>21.873854</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr"/>
+      <c r="P620" t="inlineStr"/>
+      <c r="Q620" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S620" t="inlineStr"/>
+      <c r="T620" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U620" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V620" t="inlineStr"/>
+      <c r="W620" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011101_1</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>41011101_1</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011101</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:56:18</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:54:43</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:56:18</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>5607</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>46.049713</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>18.599648</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr"/>
+      <c r="P621" t="inlineStr"/>
+      <c r="Q621" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="R621" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S621" t="inlineStr"/>
+      <c r="T621" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U621" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V621" t="inlineStr"/>
+      <c r="W621" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011102_1</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>41011102_1</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011102</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:54:56</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:54:56</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:54:56</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>48.14659</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>21.648844</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr"/>
+      <c r="P622" t="inlineStr"/>
+      <c r="Q622" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="R622" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S622" t="inlineStr"/>
+      <c r="T622" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U622" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V622" t="inlineStr"/>
+      <c r="W622" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011103_1</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>41011103_1</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011103</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:55:45</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:55:45</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:55:45</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:00</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>48.294674</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>22.107468</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr"/>
+      <c r="P623" t="inlineStr"/>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S623" t="inlineStr"/>
+      <c r="T623" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U623" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V623" t="inlineStr"/>
+      <c r="W623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011104_1</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>41011104_1</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011104</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:56:27</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:56:15</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:56:27</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:50:00</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:30:00</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>M35</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>47.757217</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>21.317293</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr"/>
+      <c r="P624" t="inlineStr"/>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S624" t="inlineStr"/>
+      <c r="T624" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U624" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V624" t="inlineStr"/>
+      <c r="W624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011105_1</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>41011105_1</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011105</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:56:42</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:56:42</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:56:42</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:50:00</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>22104</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>48.086155</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>19.428162</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr"/>
+      <c r="P625" t="inlineStr"/>
+      <c r="Q625" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="R625" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S625" t="inlineStr"/>
+      <c r="T625" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V625" t="inlineStr"/>
+      <c r="W625" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011106_1</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>41011106_1</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011106</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>AbnormalTraffic</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:20</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:57:55</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:20</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:55:00</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>2026-03-05 21:57:00</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>47.496502</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>18.811808</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr"/>
+      <c r="P626" t="inlineStr"/>
+      <c r="Q626" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R626" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S626" t="inlineStr"/>
+      <c r="T626" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U626" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V626" t="inlineStr"/>
+      <c r="W626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011107_1</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>41011107_1</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011107</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:58:15</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:58:15</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:58:15</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>47.566093</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>21.57559</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr"/>
+      <c r="P627" t="inlineStr"/>
+      <c r="Q627" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="R627" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S627" t="inlineStr"/>
+      <c r="T627" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U627" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V627" t="inlineStr"/>
+      <c r="W627" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011108_1</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>41011108_1</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011108</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:58:15</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:58:15</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:58:15</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>57104</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>45.930878</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>18.450018</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr"/>
+      <c r="P628" t="inlineStr"/>
+      <c r="Q628" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R628" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S628" t="inlineStr"/>
+      <c r="T628" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U628" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V628" t="inlineStr"/>
+      <c r="W628" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011109_1</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>41011109_1</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011109</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:58:59</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:58:59</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>2026-03-05 06:58:59</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:30:00</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>47.566174</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>21.575504</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr"/>
+      <c r="P629" t="inlineStr"/>
+      <c r="Q629" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="R629" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S629" t="inlineStr"/>
+      <c r="T629" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U629" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V629" t="inlineStr"/>
+      <c r="W629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011110_1</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>41011110_1</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011110</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:01:50</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:01:50</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:01:50</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:00</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>8614</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>47.448906</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>17.024914</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr"/>
+      <c r="P630" t="inlineStr"/>
+      <c r="Q630" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R630" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S630" t="inlineStr"/>
+      <c r="T630" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U630" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V630" t="inlineStr"/>
+      <c r="W630" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011111_1</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>41011111_1</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011111</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:03:17</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:03:17</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:03:17</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:00:00</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>47.895355</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>21.61861</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr"/>
+      <c r="P631" t="inlineStr"/>
+      <c r="Q631" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R631" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S631" t="inlineStr"/>
+      <c r="T631" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U631" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V631" t="inlineStr"/>
+      <c r="W631" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011112_1</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>41011112_1</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011112</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:03:24</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:03:24</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:03:24</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:00</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>8612</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>47.51803</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>16.933083</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr"/>
+      <c r="P632" t="inlineStr"/>
+      <c r="Q632" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R632" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S632" t="inlineStr"/>
+      <c r="T632" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U632" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V632" t="inlineStr"/>
+      <c r="W632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011113_1</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>41011113_1</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011113</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:04:51</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:04:51</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:04:51</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:00</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>8518</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>47.627033</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>16.740847</t>
+        </is>
+      </c>
+      <c r="O633" t="inlineStr"/>
+      <c r="P633" t="inlineStr"/>
+      <c r="Q633" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R633" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S633" t="inlineStr"/>
+      <c r="T633" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U633" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V633" t="inlineStr"/>
+      <c r="W633" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011114_1</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>41011114_1</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011114</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:05:54</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:05:54</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:05:54</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>4625</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>47.144096</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>20.160782</t>
+        </is>
+      </c>
+      <c r="O634" t="inlineStr"/>
+      <c r="P634" t="inlineStr"/>
+      <c r="Q634" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R634" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S634" t="inlineStr"/>
+      <c r="T634" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U634" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V634" t="inlineStr"/>
+      <c r="W634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011115_1</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>41011115_1</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011115</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:08:39</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:08:39</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:08:39</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:07:00</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>6508</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>46.60418</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>18.036297</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr"/>
+      <c r="P635" t="inlineStr"/>
+      <c r="Q635" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R635" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S635" t="inlineStr"/>
+      <c r="T635" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U635" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V635" t="inlineStr"/>
+      <c r="W635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011116_1</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>41011116_1</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011116</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:09:16</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:09:16</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:09:16</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:45:00</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:00:00</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>6228</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>46.83071</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>18.908077</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr"/>
+      <c r="P636" t="inlineStr"/>
+      <c r="Q636" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R636" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S636" t="inlineStr"/>
+      <c r="T636" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U636" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V636" t="inlineStr"/>
+      <c r="W636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011117_1</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>41011117_1</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011117</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:09:20</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:09:20</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:09:20</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:06:00</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:20:00</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>47.120167</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>18.373497</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr"/>
+      <c r="P637" t="inlineStr"/>
+      <c r="Q637" t="inlineStr">
+        <is>
+          <t>4553.0</t>
+        </is>
+      </c>
+      <c r="R637" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S637" t="inlineStr"/>
+      <c r="T637" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U637" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V637" t="inlineStr"/>
+      <c r="W637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011118_1</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>41011118_1</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011118</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:01</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:01</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:01</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:08:00</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>65116</t>
+        </is>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>46.8132</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>17.923168</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr"/>
+      <c r="P638" t="inlineStr"/>
+      <c r="Q638" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S638" t="inlineStr"/>
+      <c r="T638" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U638" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V638" t="inlineStr"/>
+      <c r="W638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011119_1</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>41011119_1</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011119</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:03</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:03</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:03</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:00:00</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>6407</t>
+        </is>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>46.76273</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>18.52594</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr"/>
+      <c r="P639" t="inlineStr"/>
+      <c r="Q639" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R639" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S639" t="inlineStr"/>
+      <c r="T639" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U639" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V639" t="inlineStr"/>
+      <c r="W639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011120_1</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>41011120_1</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011120</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:11</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:11</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:11</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:09:00</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:09:00</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>8707</t>
+        </is>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>47.098618</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>16.555983</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr"/>
+      <c r="P640" t="inlineStr"/>
+      <c r="Q640" t="inlineStr">
+        <is>
+          <t>697.0</t>
+        </is>
+      </c>
+      <c r="R640" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S640" t="inlineStr"/>
+      <c r="T640" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U640" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V640" t="inlineStr"/>
+      <c r="W640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011121_1</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>41011121_1</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011121</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:45</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:45</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:45</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:10:00</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>46.807365</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>18.1398</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr"/>
+      <c r="P641" t="inlineStr"/>
+      <c r="Q641" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S641" t="inlineStr"/>
+      <c r="T641" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U641" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V641" t="inlineStr"/>
+      <c r="W641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011122_1</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>41011122_1</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011122</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:00</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:00</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:00</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:09:00</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:20:00</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>6307</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>46.767693</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>18.606262</t>
+        </is>
+      </c>
+      <c r="O642" t="inlineStr"/>
+      <c r="P642" t="inlineStr"/>
+      <c r="Q642" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S642" t="inlineStr"/>
+      <c r="T642" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U642" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V642" t="inlineStr"/>
+      <c r="W642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011123_1</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>41011123_1</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011123</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:39</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:39</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:39</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:10:00</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:10:00</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>46.984142</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>16.8335</t>
+        </is>
+      </c>
+      <c r="O643" t="inlineStr"/>
+      <c r="P643" t="inlineStr"/>
+      <c r="Q643" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R643" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S643" t="inlineStr"/>
+      <c r="T643" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U643" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V643" t="inlineStr"/>
+      <c r="W643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011124_1</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>41011124_1</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011124</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:41</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:41</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:41</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:00</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>47.998024</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>22.102732</t>
+        </is>
+      </c>
+      <c r="O644" t="inlineStr"/>
+      <c r="P644" t="inlineStr"/>
+      <c r="Q644" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R644" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S644" t="inlineStr"/>
+      <c r="T644" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U644" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V644" t="inlineStr"/>
+      <c r="W644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011125_1</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>41011125_1</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011125</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:53</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:53</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:53</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:45:00</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>46.620014</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>18.860434</t>
+        </is>
+      </c>
+      <c r="O645" t="inlineStr"/>
+      <c r="P645" t="inlineStr"/>
+      <c r="Q645" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R645" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S645" t="inlineStr"/>
+      <c r="T645" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U645" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V645" t="inlineStr"/>
+      <c r="W645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011126_1</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>41011126_1</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011126</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:07</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:07</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:07</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:45:00</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>73108</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>47.00613</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>17.78865</t>
+        </is>
+      </c>
+      <c r="O646" t="inlineStr"/>
+      <c r="P646" t="inlineStr"/>
+      <c r="Q646" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R646" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S646" t="inlineStr"/>
+      <c r="T646" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U646" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V646" t="inlineStr"/>
+      <c r="W646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011127_1</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>41011127_1</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011127</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:23</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:23</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:23</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:11:00</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>48.127537</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>22.122007</t>
+        </is>
+      </c>
+      <c r="O647" t="inlineStr"/>
+      <c r="P647" t="inlineStr"/>
+      <c r="Q647" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S647" t="inlineStr"/>
+      <c r="T647" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U647" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V647" t="inlineStr"/>
+      <c r="W647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011128_1</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>41011128_1</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011128</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:50</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:50</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:50</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:45:00</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:45:00</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>46.982918</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>18.206371</t>
+        </is>
+      </c>
+      <c r="O648" t="inlineStr"/>
+      <c r="P648" t="inlineStr"/>
+      <c r="Q648" t="inlineStr">
+        <is>
+          <t>904.0</t>
+        </is>
+      </c>
+      <c r="R648" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S648" t="inlineStr"/>
+      <c r="T648" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U648" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V648" t="inlineStr"/>
+      <c r="W648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011129_1</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>41011129_1</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011129</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:54</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:54</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:54</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:12:00</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>48.13978</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>22.194824</t>
+        </is>
+      </c>
+      <c r="O649" t="inlineStr"/>
+      <c r="P649" t="inlineStr"/>
+      <c r="Q649" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R649" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S649" t="inlineStr"/>
+      <c r="T649" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U649" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V649" t="inlineStr"/>
+      <c r="W649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011130_1</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>41011130_1</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011130</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:15</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:15</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:15</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>47.313503</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>17.46052</t>
+        </is>
+      </c>
+      <c r="O650" t="inlineStr"/>
+      <c r="P650" t="inlineStr"/>
+      <c r="Q650" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R650" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S650" t="inlineStr"/>
+      <c r="T650" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U650" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V650" t="inlineStr"/>
+      <c r="W650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011131_1</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>41011131_1</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011131</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:37</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:37</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:37</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:00</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>47.61985</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>18.778503</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr"/>
+      <c r="P651" t="inlineStr"/>
+      <c r="Q651" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R651" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S651" t="inlineStr"/>
+      <c r="T651" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U651" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V651" t="inlineStr"/>
+      <c r="W651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011132_1</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>41011132_1</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011132</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:37</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:37</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:37</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:00</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:45:00</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>46.97442</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>17.82215</t>
+        </is>
+      </c>
+      <c r="O652" t="inlineStr"/>
+      <c r="P652" t="inlineStr"/>
+      <c r="Q652" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S652" t="inlineStr"/>
+      <c r="T652" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U652" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V652" t="inlineStr"/>
+      <c r="W652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011133_1</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>41011133_1</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011133</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:59</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:59</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:13:59</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>47.34152</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>17.560886</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr"/>
+      <c r="P653" t="inlineStr"/>
+      <c r="Q653" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R653" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S653" t="inlineStr"/>
+      <c r="T653" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U653" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V653" t="inlineStr"/>
+      <c r="W653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011134_1</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>41011134_1</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011134</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:14:17</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:14:17</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:14:17</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>4404</t>
+        </is>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>46.650303</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>20.668972</t>
+        </is>
+      </c>
+      <c r="O654" t="inlineStr"/>
+      <c r="P654" t="inlineStr"/>
+      <c r="Q654" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S654" t="inlineStr"/>
+      <c r="T654" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U654" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V654" t="inlineStr"/>
+      <c r="W654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011135_1</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>41011135_1</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011135</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:14:31</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:14:31</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:14:31</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>3801</t>
+        </is>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>48.26755</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>21.482092</t>
+        </is>
+      </c>
+      <c r="O655" t="inlineStr"/>
+      <c r="P655" t="inlineStr"/>
+      <c r="Q655" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R655" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S655" t="inlineStr"/>
+      <c r="T655" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U655" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V655" t="inlineStr"/>
+      <c r="W655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011136_1</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>41011136_1</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011136</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:14:45</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:14:45</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:14:45</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>47.152874</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>17.653826</t>
+        </is>
+      </c>
+      <c r="O656" t="inlineStr"/>
+      <c r="P656" t="inlineStr"/>
+      <c r="Q656" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R656" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S656" t="inlineStr"/>
+      <c r="T656" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U656" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V656" t="inlineStr"/>
+      <c r="W656" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011138_1</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>41011138_1</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011138</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:15:25</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:15:25</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:15:25</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>47.346577</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>17.471167</t>
+        </is>
+      </c>
+      <c r="O657" t="inlineStr"/>
+      <c r="P657" t="inlineStr"/>
+      <c r="Q657" t="inlineStr">
+        <is>
+          <t>974.0</t>
+        </is>
+      </c>
+      <c r="R657" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S657" t="inlineStr"/>
+      <c r="T657" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U657" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V657" t="inlineStr"/>
+      <c r="W657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011139_1</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>41011139_1</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011139</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:15:36</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:15:36</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:15:36</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:00</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>3804</t>
+        </is>
+      </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>48.325516</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>22.043747</t>
+        </is>
+      </c>
+      <c r="O658" t="inlineStr"/>
+      <c r="P658" t="inlineStr"/>
+      <c r="Q658" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R658" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S658" t="inlineStr"/>
+      <c r="T658" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U658" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V658" t="inlineStr"/>
+      <c r="W658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011140_1</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>41011140_1</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011140</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:15:59</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:15:59</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:15:59</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>47.566235</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>20.228786</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr"/>
+      <c r="P659" t="inlineStr"/>
+      <c r="Q659" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="R659" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S659" t="inlineStr"/>
+      <c r="T659" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U659" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V659" t="inlineStr"/>
+      <c r="W659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011141_1</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>41011141_1</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011141</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:16:21</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:16:21</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:16:21</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:15:00</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>4444</t>
+        </is>
+      </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>46.297966</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>21.046616</t>
+        </is>
+      </c>
+      <c r="O660" t="inlineStr"/>
+      <c r="P660" t="inlineStr"/>
+      <c r="Q660" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R660" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S660" t="inlineStr"/>
+      <c r="T660" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U660" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V660" t="inlineStr"/>
+      <c r="W660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011142_1</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>41011142_1</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011142</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:16:57</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:16:57</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:16:57</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>3207</t>
+        </is>
+      </c>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>47.712708</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>20.257654</t>
+        </is>
+      </c>
+      <c r="O661" t="inlineStr"/>
+      <c r="P661" t="inlineStr"/>
+      <c r="Q661" t="inlineStr">
+        <is>
+          <t>480.0</t>
+        </is>
+      </c>
+      <c r="R661" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S661" t="inlineStr"/>
+      <c r="T661" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U661" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V661" t="inlineStr"/>
+      <c r="W661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011143_1</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>41011143_1</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011143</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:20</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:20</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:20</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:45:00</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>46.538208</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr">
+        <is>
+          <t>18.65339</t>
+        </is>
+      </c>
+      <c r="O662" t="inlineStr"/>
+      <c r="P662" t="inlineStr"/>
+      <c r="Q662" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R662" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S662" t="inlineStr"/>
+      <c r="T662" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U662" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V662" t="inlineStr"/>
+      <c r="W662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011144_1</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>41011144_1</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011144</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:28</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:28</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:28</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>83106</t>
+        </is>
+      </c>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>47.274986</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr">
+        <is>
+          <t>17.840857</t>
+        </is>
+      </c>
+      <c r="O663" t="inlineStr"/>
+      <c r="P663" t="inlineStr"/>
+      <c r="Q663" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S663" t="inlineStr"/>
+      <c r="T663" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U663" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V663" t="inlineStr"/>
+      <c r="W663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011145_1</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>41011145_1</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011145</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:51</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:51</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:51</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>4432</t>
+        </is>
+      </c>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>46.463318</t>
+        </is>
+      </c>
+      <c r="N664" t="inlineStr">
+        <is>
+          <t>20.820507</t>
+        </is>
+      </c>
+      <c r="O664" t="inlineStr"/>
+      <c r="P664" t="inlineStr"/>
+      <c r="Q664" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R664" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S664" t="inlineStr"/>
+      <c r="T664" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U664" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V664" t="inlineStr"/>
+      <c r="W664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011146_1</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>41011146_1</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011146</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:56</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:56</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:17:56</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:15:00</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:30:00</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>M35</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>47.79486</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>21.244658</t>
+        </is>
+      </c>
+      <c r="O665" t="inlineStr"/>
+      <c r="P665" t="inlineStr"/>
+      <c r="Q665" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S665" t="inlineStr"/>
+      <c r="T665" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U665" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V665" t="inlineStr"/>
+      <c r="W665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011147_1</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>41011147_1</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011147</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:18:22</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:18:22</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:18:22</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>46.82447</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>19.215105</t>
+        </is>
+      </c>
+      <c r="O666" t="inlineStr"/>
+      <c r="P666" t="inlineStr"/>
+      <c r="Q666" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S666" t="inlineStr"/>
+      <c r="T666" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U666" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V666" t="inlineStr"/>
+      <c r="W666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011148_1</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>41011148_1</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011148</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:18:38</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:18:38</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:18:38</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:30:00</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>2026-03-06 15:00:00</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>47.99078</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>20.771671</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr"/>
+      <c r="P667" t="inlineStr"/>
+      <c r="Q667" t="inlineStr">
+        <is>
+          <t>546.0</t>
+        </is>
+      </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr"/>
+      <c r="T667" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U667" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V667" t="inlineStr"/>
+      <c r="W667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011149_1</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>41011149_1</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011149</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:19:03</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:19:03</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:19:03</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>52125</t>
+        </is>
+      </c>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>46.805714</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>19.036291</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr"/>
+      <c r="P668" t="inlineStr"/>
+      <c r="Q668" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S668" t="inlineStr"/>
+      <c r="T668" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U668" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V668" t="inlineStr"/>
+      <c r="W668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011150_1</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>41011150_1</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011150</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:19:04</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:19:04</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:19:04</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:45:00</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>46.538208</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>18.65339</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr"/>
+      <c r="P669" t="inlineStr"/>
+      <c r="Q669" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S669" t="inlineStr"/>
+      <c r="T669" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U669" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V669" t="inlineStr"/>
+      <c r="W669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011151_1</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>41011151_1</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011151</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:20</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:20</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:20</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:10:00</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>4403</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>46.710716</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>20.55589</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr"/>
+      <c r="P670" t="inlineStr"/>
+      <c r="Q670" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr"/>
+      <c r="T670" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V670" t="inlineStr"/>
+      <c r="W670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011152_1</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>41011152_1</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011152</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:30</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:30</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:30</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>46.79891</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>19.121557</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr"/>
+      <c r="P671" t="inlineStr"/>
+      <c r="Q671" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr"/>
+      <c r="T671" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U671" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V671" t="inlineStr"/>
+      <c r="W671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011153_1</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>41011153_1</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011153</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:08</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:08</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:08</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>5213</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>46.87556</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>19.221788</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr"/>
+      <c r="P672" t="inlineStr"/>
+      <c r="Q672" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr"/>
+      <c r="T672" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U672" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V672" t="inlineStr"/>
+      <c r="W672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011154_1</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>41011154_1</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011154</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:26</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:26</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:26</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>4432</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>46.56616</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>20.943933</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr"/>
+      <c r="P673" t="inlineStr"/>
+      <c r="Q673" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S673" t="inlineStr"/>
+      <c r="T673" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U673" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V673" t="inlineStr"/>
+      <c r="W673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011155_1</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>41011155_1</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011155</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:47</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:47</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:47</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>46.96314</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>19.444845</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr"/>
+      <c r="P674" t="inlineStr"/>
+      <c r="Q674" t="inlineStr">
+        <is>
+          <t>461.0</t>
+        </is>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr"/>
+      <c r="T674" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U674" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V674" t="inlineStr"/>
+      <c r="W674" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011156_1</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>41011156_1</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011156</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:55</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:55</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:21:55</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:30:00</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>47.74359</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>20.25283</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr"/>
+      <c r="P675" t="inlineStr"/>
+      <c r="Q675" t="inlineStr">
+        <is>
+          <t>704.0</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr"/>
+      <c r="T675" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V675" t="inlineStr"/>
+      <c r="W675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011157_1</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>41011157_1</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011157</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:01</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:01</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:01</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:00</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>5402</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>46.501404</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>19.741592</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr"/>
+      <c r="P676" t="inlineStr"/>
+      <c r="Q676" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr"/>
+      <c r="T676" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U676" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V676" t="inlineStr"/>
+      <c r="W676" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011158_1</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>41011158_1</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011158</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:04</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:04</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:04</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:30:00</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>32113</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>47.605904</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>20.4045</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr"/>
+      <c r="P677" t="inlineStr"/>
+      <c r="Q677" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr"/>
+      <c r="T677" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U677" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V677" t="inlineStr"/>
+      <c r="W677" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011159_1</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>41011159_1</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011159</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:11</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:11</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:11</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>4207</t>
+        </is>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>47.190865</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>20.55348</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr"/>
+      <c r="P678" t="inlineStr"/>
+      <c r="Q678" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S678" t="inlineStr"/>
+      <c r="T678" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U678" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V678" t="inlineStr"/>
+      <c r="W678" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011160_1</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>41011160_1</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011160</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:14</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:14</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:14</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>4401</t>
+        </is>
+      </c>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>46.70278</t>
+        </is>
+      </c>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>20.35051</t>
+        </is>
+      </c>
+      <c r="O679" t="inlineStr"/>
+      <c r="P679" t="inlineStr"/>
+      <c r="Q679" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R679" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S679" t="inlineStr"/>
+      <c r="T679" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U679" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V679" t="inlineStr"/>
+      <c r="W679" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011161_1</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>41011161_1</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011161</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:24:38</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:24:38</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:24:38</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>47.211765</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>20.775713</t>
+        </is>
+      </c>
+      <c r="O680" t="inlineStr"/>
+      <c r="P680" t="inlineStr"/>
+      <c r="Q680" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S680" t="inlineStr"/>
+      <c r="T680" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U680" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V680" t="inlineStr"/>
+      <c r="W680" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011162_1</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>41011162_1</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011162</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:24:55</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:24:55</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:24:55</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:00</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>5408</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>46.43307</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>19.497536</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr"/>
+      <c r="P681" t="inlineStr"/>
+      <c r="Q681" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S681" t="inlineStr"/>
+      <c r="T681" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U681" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V681" t="inlineStr"/>
+      <c r="W681" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011163_1</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>41011163_1</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011163</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:26:37</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:28</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:26:37</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:15:00</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>4517</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>46.6912</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>20.089954</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr"/>
+      <c r="P682" t="inlineStr"/>
+      <c r="Q682" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S682" t="inlineStr"/>
+      <c r="T682" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U682" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V682" t="inlineStr"/>
+      <c r="W682" t="inlineStr"/>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011164_1</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>41011164_1</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011164</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:31</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:31</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:31</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>32113</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>47.608337</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>20.3894</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr"/>
+      <c r="P683" t="inlineStr"/>
+      <c r="Q683" t="inlineStr">
+        <is>
+          <t>950.0</t>
+        </is>
+      </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S683" t="inlineStr"/>
+      <c r="T683" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U683" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V683" t="inlineStr"/>
+      <c r="W683" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011165_1</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>41011165_1</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011165</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:49</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:49</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:49</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:23:00</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>46.77024</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>17.629225</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr"/>
+      <c r="P684" t="inlineStr"/>
+      <c r="Q684" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S684" t="inlineStr"/>
+      <c r="T684" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U684" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V684" t="inlineStr"/>
+      <c r="W684" t="inlineStr"/>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011166_1</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>41011166_1</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011166</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:50</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:50</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:50</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:24:00</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>47.967945</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>21.98362</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr"/>
+      <c r="P685" t="inlineStr"/>
+      <c r="Q685" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S685" t="inlineStr"/>
+      <c r="T685" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U685" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V685" t="inlineStr"/>
+      <c r="W685" t="inlineStr"/>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011167_1</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>41011167_1</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011167</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:58</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:26:06</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:58</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:21:00</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>46.060936</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>18.575994</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr"/>
+      <c r="P686" t="inlineStr"/>
+      <c r="Q686" t="inlineStr">
+        <is>
+          <t>270.0</t>
+        </is>
+      </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S686" t="inlineStr"/>
+      <c r="T686" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U686" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V686" t="inlineStr"/>
+      <c r="W686" t="inlineStr"/>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011168_1</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>41011168_1</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011168</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:26:27</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:26:27</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:26:27</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:00</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>5412</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>46.410694</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>19.497389</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr"/>
+      <c r="P687" t="inlineStr"/>
+      <c r="Q687" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S687" t="inlineStr"/>
+      <c r="T687" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U687" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V687" t="inlineStr"/>
+      <c r="W687" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011169_1</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>41011169_1</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011169</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:26:52</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:26:52</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:26:52</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:26:00</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:26:00</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>8116</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>47.241463</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>18.62761</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr"/>
+      <c r="P688" t="inlineStr"/>
+      <c r="Q688" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S688" t="inlineStr"/>
+      <c r="T688" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U688" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V688" t="inlineStr"/>
+      <c r="W688" t="inlineStr"/>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011170_1</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>41011170_1</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011170</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:05</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:05</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:05</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:00</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>49153</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>47.98924</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>22.080982</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr"/>
+      <c r="P689" t="inlineStr"/>
+      <c r="Q689" t="inlineStr">
+        <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr"/>
+      <c r="T689" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U689" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V689" t="inlineStr"/>
+      <c r="W689" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011171_1</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>41011171_1</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011171</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:28</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:28</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:28</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:26:00</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:26:00</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>8117</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>47.230404</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>18.670921</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr"/>
+      <c r="P690" t="inlineStr"/>
+      <c r="Q690" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S690" t="inlineStr"/>
+      <c r="T690" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U690" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V690" t="inlineStr"/>
+      <c r="W690" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011172_1</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>41011172_1</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011172</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:38</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:38</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:38</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:26:00</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>46.056774</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>18.573475</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr"/>
+      <c r="P691" t="inlineStr"/>
+      <c r="Q691" t="inlineStr">
+        <is>
+          <t>770.0</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S691" t="inlineStr"/>
+      <c r="T691" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U691" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V691" t="inlineStr"/>
+      <c r="W691" t="inlineStr"/>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011173_1</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>41011173_1</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011173</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:39</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:39</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:39</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:25:00</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>46.558617</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>17.411518</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr"/>
+      <c r="P692" t="inlineStr"/>
+      <c r="Q692" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S692" t="inlineStr"/>
+      <c r="T692" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U692" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V692" t="inlineStr"/>
+      <c r="W692" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011174_1</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>41011174_1</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011174</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:55</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:55</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:55</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:30:00</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>6701</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>46.399242</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>17.744692</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr"/>
+      <c r="P693" t="inlineStr"/>
+      <c r="Q693" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S693" t="inlineStr"/>
+      <c r="T693" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U693" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V693" t="inlineStr"/>
+      <c r="W693" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011175_1</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>41011175_1</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011175</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:12</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:12</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:12</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:27:00</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>47.923798</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>22.043804</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr"/>
+      <c r="P694" t="inlineStr"/>
+      <c r="Q694" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S694" t="inlineStr"/>
+      <c r="T694" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U694" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V694" t="inlineStr"/>
+      <c r="W694" t="inlineStr"/>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011176_1</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>41011176_1</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011176</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:12</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:12</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:12</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:20:00</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:40:00</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>6231</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>46.62092</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>18.8539</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr"/>
+      <c r="P695" t="inlineStr"/>
+      <c r="Q695" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S695" t="inlineStr"/>
+      <c r="T695" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U695" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V695" t="inlineStr"/>
+      <c r="W695" t="inlineStr"/>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011177_1</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>41011177_1</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011177</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:36</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:36</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:36</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:10:00</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>4410</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>46.579327</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>20.489113</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr"/>
+      <c r="P696" t="inlineStr"/>
+      <c r="Q696" t="inlineStr">
+        <is>
+          <t>563.0</t>
+        </is>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S696" t="inlineStr"/>
+      <c r="T696" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U696" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V696" t="inlineStr"/>
+      <c r="W696" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011178_1</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>41011178_1</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011178</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:29:25</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:29:25</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:29:25</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:28:00</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>47.8646</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>21.849379</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr"/>
+      <c r="P697" t="inlineStr"/>
+      <c r="Q697" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S697" t="inlineStr"/>
+      <c r="T697" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U697" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:31:00</t>
+        </is>
+      </c>
+      <c r="V697" t="inlineStr"/>
+      <c r="W697" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W817"/>
+  <dimension ref="A1:W866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53852,7 +53852,7 @@
       <c r="S592" t="inlineStr"/>
       <c r="T592" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U592" t="inlineStr">
@@ -53860,7 +53860,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V592" t="inlineStr"/>
+      <c r="V592" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
       <c r="W592" t="inlineStr"/>
     </row>
     <row r="593">
@@ -55311,7 +55315,7 @@
       <c r="S607" t="inlineStr"/>
       <c r="T607" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U607" t="inlineStr">
@@ -55319,7 +55323,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V607" t="inlineStr"/>
+      <c r="V607" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
       <c r="W607" t="inlineStr"/>
     </row>
     <row r="608">
@@ -62978,7 +62986,7 @@
       <c r="S686" t="inlineStr"/>
       <c r="T686" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U686" t="inlineStr">
@@ -62986,7 +62994,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V686" t="inlineStr"/>
+      <c r="V686" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
       <c r="W686" t="inlineStr"/>
     </row>
     <row r="687">
@@ -63463,7 +63475,7 @@
       <c r="S691" t="inlineStr"/>
       <c r="T691" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U691" t="inlineStr">
@@ -63471,7 +63483,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V691" t="inlineStr"/>
+      <c r="V691" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
       <c r="W691" t="inlineStr"/>
     </row>
     <row r="692">
@@ -63851,7 +63867,7 @@
       <c r="S695" t="inlineStr"/>
       <c r="T695" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U695" t="inlineStr">
@@ -63859,7 +63875,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V695" t="inlineStr"/>
+      <c r="V695" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
       <c r="W695" t="inlineStr"/>
     </row>
     <row r="696">
@@ -64910,7 +64930,7 @@
       <c r="S706" t="inlineStr"/>
       <c r="T706" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U706" t="inlineStr">
@@ -64918,7 +64938,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V706" t="inlineStr"/>
+      <c r="V706" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
       <c r="W706" t="inlineStr"/>
     </row>
     <row r="707">
@@ -65686,7 +65710,7 @@
       <c r="S714" t="inlineStr"/>
       <c r="T714" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U714" t="inlineStr">
@@ -65694,7 +65718,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V714" t="inlineStr"/>
+      <c r="V714" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
       <c r="W714" t="inlineStr"/>
     </row>
     <row r="715">
@@ -71797,7 +71825,7 @@
       <c r="S777" t="inlineStr"/>
       <c r="T777" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U777" t="inlineStr">
@@ -71805,7 +71833,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V777" t="inlineStr"/>
+      <c r="V777" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
       <c r="W777" t="inlineStr"/>
     </row>
     <row r="778">
@@ -74901,7 +74933,7 @@
       <c r="S809" t="inlineStr"/>
       <c r="T809" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U809" t="inlineStr">
@@ -74909,7 +74941,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V809" t="inlineStr"/>
+      <c r="V809" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
       <c r="W809" t="inlineStr"/>
     </row>
     <row r="810">
@@ -75687,6 +75723,4759 @@
       </c>
       <c r="V817" t="inlineStr"/>
       <c r="W817" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011309_1</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>41011309_1</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011309</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:25:37</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:25:37</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:25:37</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:00</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>47.64608</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>21.532345</t>
+        </is>
+      </c>
+      <c r="O818" t="inlineStr"/>
+      <c r="P818" t="inlineStr"/>
+      <c r="Q818" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R818" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S818" t="inlineStr"/>
+      <c r="T818" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U818" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V818" t="inlineStr"/>
+      <c r="W818" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011310_1</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>41011310_1</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011310</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:13</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:13</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:13</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:15:00</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:15:00</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>3612</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>47.97843</t>
+        </is>
+      </c>
+      <c r="N819" t="inlineStr">
+        <is>
+          <t>21.52034</t>
+        </is>
+      </c>
+      <c r="O819" t="inlineStr"/>
+      <c r="P819" t="inlineStr"/>
+      <c r="Q819" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R819" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S819" t="inlineStr"/>
+      <c r="T819" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U819" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V819" t="inlineStr"/>
+      <c r="W819" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011311_1</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>41011311_1</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011311</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:18</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:18</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:18</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:00</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>47.623302</t>
+        </is>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>21.763994</t>
+        </is>
+      </c>
+      <c r="O820" t="inlineStr"/>
+      <c r="P820" t="inlineStr"/>
+      <c r="Q820" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="R820" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S820" t="inlineStr"/>
+      <c r="T820" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U820" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V820" t="inlineStr"/>
+      <c r="W820" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011312_1</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>41011312_1</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011312</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>PublicEvent</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:21</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:21</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:21</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>2026-03-26 05:00:00</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>2026-03-29 18:00:00</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>7216</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>47.09357</t>
+        </is>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>18.030972</t>
+        </is>
+      </c>
+      <c r="O821" t="inlineStr"/>
+      <c r="P821" t="inlineStr"/>
+      <c r="Q821" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="R821" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S821" t="inlineStr"/>
+      <c r="T821" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U821" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V821" t="inlineStr"/>
+      <c r="W821" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011313_1</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>41011313_1</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011313</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:40</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:40</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:26:40</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:15:00</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:25:00</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>47.193817</t>
+        </is>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>20.413218</t>
+        </is>
+      </c>
+      <c r="O822" t="inlineStr"/>
+      <c r="P822" t="inlineStr"/>
+      <c r="Q822" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R822" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S822" t="inlineStr"/>
+      <c r="T822" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U822" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V822" t="inlineStr"/>
+      <c r="W822" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011314_1</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>41011314_1</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011314</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:07</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:07</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:07</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:00</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:30:00</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>47.565086</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>21.68097</t>
+        </is>
+      </c>
+      <c r="O823" t="inlineStr"/>
+      <c r="P823" t="inlineStr"/>
+      <c r="Q823" t="inlineStr">
+        <is>
+          <t>838.0</t>
+        </is>
+      </c>
+      <c r="R823" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S823" t="inlineStr"/>
+      <c r="T823" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U823" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V823" t="inlineStr"/>
+      <c r="W823" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011315_1</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>41011315_1</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011315</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:21</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:21</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:21</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:20:00</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:20:00</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>46.997704</t>
+        </is>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>19.599226</t>
+        </is>
+      </c>
+      <c r="O824" t="inlineStr"/>
+      <c r="P824" t="inlineStr"/>
+      <c r="Q824" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R824" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S824" t="inlineStr"/>
+      <c r="T824" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U824" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V824" t="inlineStr"/>
+      <c r="W824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011316_1</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>41011316_1</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011316</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:31</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:31</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:31</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:25:00</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:15:00</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>47.142277</t>
+        </is>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>21.717215</t>
+        </is>
+      </c>
+      <c r="O825" t="inlineStr"/>
+      <c r="P825" t="inlineStr"/>
+      <c r="Q825" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R825" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S825" t="inlineStr"/>
+      <c r="T825" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U825" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V825" t="inlineStr"/>
+      <c r="W825" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011317_1</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>41011317_1</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011317</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:54</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:54</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:54</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:25:00</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:26:00</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>47.62741</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>19.442556</t>
+        </is>
+      </c>
+      <c r="O826" t="inlineStr"/>
+      <c r="P826" t="inlineStr"/>
+      <c r="Q826" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R826" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S826" t="inlineStr"/>
+      <c r="T826" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U826" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V826" t="inlineStr"/>
+      <c r="W826" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011318_1</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>41011318_1</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011318</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:55</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:55</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:27:55</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>48.01679</t>
+        </is>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>18.890041</t>
+        </is>
+      </c>
+      <c r="O827" t="inlineStr"/>
+      <c r="P827" t="inlineStr"/>
+      <c r="Q827" t="inlineStr">
+        <is>
+          <t>633.0</t>
+        </is>
+      </c>
+      <c r="R827" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S827" t="inlineStr"/>
+      <c r="T827" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U827" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V827" t="inlineStr"/>
+      <c r="W827" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011320_1</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>41011320_1</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011320</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:28:26</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:28:26</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:28:26</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:25:00</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:00:00</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>30808</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>47.887306</t>
+        </is>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>21.745922</t>
+        </is>
+      </c>
+      <c r="O828" t="inlineStr"/>
+      <c r="P828" t="inlineStr"/>
+      <c r="Q828" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R828" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S828" t="inlineStr"/>
+      <c r="T828" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U828" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V828" t="inlineStr"/>
+      <c r="W828" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011321_1</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>41011321_1</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011321</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>PublicEvent</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:29:05</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:29:05</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:29:05</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>2026-03-26 05:00:00</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>2026-03-29 18:00:00</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>8229</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>47.10213</t>
+        </is>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>17.940573</t>
+        </is>
+      </c>
+      <c r="O829" t="inlineStr"/>
+      <c r="P829" t="inlineStr"/>
+      <c r="Q829" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="R829" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S829" t="inlineStr"/>
+      <c r="T829" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U829" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V829" t="inlineStr"/>
+      <c r="W829" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011322_1</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>41011322_1</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011322</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:29:17</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:29:17</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:29:17</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:25:00</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:26:00</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>47.941063</t>
+        </is>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>22.103222</t>
+        </is>
+      </c>
+      <c r="O830" t="inlineStr"/>
+      <c r="P830" t="inlineStr"/>
+      <c r="Q830" t="inlineStr">
+        <is>
+          <t>589.0</t>
+        </is>
+      </c>
+      <c r="R830" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S830" t="inlineStr"/>
+      <c r="T830" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U830" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V830" t="inlineStr"/>
+      <c r="W830" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011323_1</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>41011323_1</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011323</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>PublicEvent</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:29:22</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:29:22</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:29:22</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:30:00</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:30:00</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>48.109493</t>
+        </is>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>21.40912</t>
+        </is>
+      </c>
+      <c r="O831" t="inlineStr"/>
+      <c r="P831" t="inlineStr"/>
+      <c r="Q831" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="R831" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S831" t="inlineStr"/>
+      <c r="T831" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U831" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V831" t="inlineStr"/>
+      <c r="W831" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011324_1</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>41011324_1</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011324</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:58</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:58</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:58</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:20:00</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>70833</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>46.478596</t>
+        </is>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>16.973803</t>
+        </is>
+      </c>
+      <c r="O832" t="inlineStr"/>
+      <c r="P832" t="inlineStr"/>
+      <c r="Q832" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R832" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S832" t="inlineStr"/>
+      <c r="T832" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U832" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V832" t="inlineStr"/>
+      <c r="W832" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011325_1</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>41011325_1</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011325</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:31:59</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:31:59</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:31:59</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:25:00</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>47.77495</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>20.575747</t>
+        </is>
+      </c>
+      <c r="O833" t="inlineStr"/>
+      <c r="P833" t="inlineStr"/>
+      <c r="Q833" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R833" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S833" t="inlineStr"/>
+      <c r="T833" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U833" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V833" t="inlineStr"/>
+      <c r="W833" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011326_1</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>41011326_1</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011326</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:32:18</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:32:18</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:32:18</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:28:00</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>47.65993</t>
+        </is>
+      </c>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>18.180779</t>
+        </is>
+      </c>
+      <c r="O834" t="inlineStr"/>
+      <c r="P834" t="inlineStr"/>
+      <c r="Q834" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R834" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S834" t="inlineStr"/>
+      <c r="T834" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U834" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V834" t="inlineStr"/>
+      <c r="W834" t="inlineStr"/>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011327_1</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>41011327_1</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011327</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:33:21</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:33:21</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:33:21</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:00</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:30:00</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>47.14351</t>
+        </is>
+      </c>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>21.482582</t>
+        </is>
+      </c>
+      <c r="O835" t="inlineStr"/>
+      <c r="P835" t="inlineStr"/>
+      <c r="Q835" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R835" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S835" t="inlineStr"/>
+      <c r="T835" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U835" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V835" t="inlineStr"/>
+      <c r="W835" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011328_1</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>41011328_1</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011328</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:14</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:34:20</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:14</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:15:00</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>47.88469</t>
+        </is>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>20.832762</t>
+        </is>
+      </c>
+      <c r="O836" t="inlineStr"/>
+      <c r="P836" t="inlineStr"/>
+      <c r="Q836" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="R836" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S836" t="inlineStr"/>
+      <c r="T836" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U836" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V836" t="inlineStr"/>
+      <c r="W836" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011329_1</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>41011329_1</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011329</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:34:37</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:34:37</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:34:37</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:00</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>47.212696</t>
+        </is>
+      </c>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>18.298275</t>
+        </is>
+      </c>
+      <c r="O837" t="inlineStr"/>
+      <c r="P837" t="inlineStr"/>
+      <c r="Q837" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="R837" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S837" t="inlineStr"/>
+      <c r="T837" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U837" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V837" t="inlineStr"/>
+      <c r="W837" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011330_1</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>41011330_1</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011330</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:36:01</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:36:01</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:36:01</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:00</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:30:00</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>47.331394</t>
+        </is>
+      </c>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>18.777708</t>
+        </is>
+      </c>
+      <c r="O838" t="inlineStr"/>
+      <c r="P838" t="inlineStr"/>
+      <c r="Q838" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R838" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S838" t="inlineStr"/>
+      <c r="T838" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U838" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V838" t="inlineStr"/>
+      <c r="W838" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011331_1</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>41011331_1</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011331</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:36:37</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:36:37</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:36:37</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:36:00</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:00:00</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>7317</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>47.010845</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>17.45524</t>
+        </is>
+      </c>
+      <c r="O839" t="inlineStr"/>
+      <c r="P839" t="inlineStr"/>
+      <c r="Q839" t="inlineStr">
+        <is>
+          <t>392.0</t>
+        </is>
+      </c>
+      <c r="R839" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S839" t="inlineStr"/>
+      <c r="T839" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U839" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V839" t="inlineStr"/>
+      <c r="W839" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011332_1</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>41011332_1</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011332</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:37:02</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:37:02</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:37:02</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:15:00</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>47.88469</t>
+        </is>
+      </c>
+      <c r="N840" t="inlineStr">
+        <is>
+          <t>20.832762</t>
+        </is>
+      </c>
+      <c r="O840" t="inlineStr"/>
+      <c r="P840" t="inlineStr"/>
+      <c r="Q840" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="R840" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S840" t="inlineStr"/>
+      <c r="T840" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U840" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V840" t="inlineStr"/>
+      <c r="W840" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011333_1</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>41011333_1</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011333</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:37:24</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:37:24</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:37:24</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:00</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:33:00</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>47.66835</t>
+        </is>
+      </c>
+      <c r="N841" t="inlineStr">
+        <is>
+          <t>17.769842</t>
+        </is>
+      </c>
+      <c r="O841" t="inlineStr"/>
+      <c r="P841" t="inlineStr"/>
+      <c r="Q841" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="R841" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S841" t="inlineStr"/>
+      <c r="T841" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U841" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V841" t="inlineStr"/>
+      <c r="W841" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011334_1</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>41011334_1</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011334</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:38:06</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:38:06</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:38:06</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:35:00</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>47.69996</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>19.775734</t>
+        </is>
+      </c>
+      <c r="O842" t="inlineStr"/>
+      <c r="P842" t="inlineStr"/>
+      <c r="Q842" t="inlineStr">
+        <is>
+          <t>450.0</t>
+        </is>
+      </c>
+      <c r="R842" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S842" t="inlineStr"/>
+      <c r="T842" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U842" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V842" t="inlineStr"/>
+      <c r="W842" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011335_1</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>41011335_1</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011335</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:12</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:12</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:12</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:35:00</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:39:00</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>47.500355</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>18.790218</t>
+        </is>
+      </c>
+      <c r="O843" t="inlineStr"/>
+      <c r="P843" t="inlineStr"/>
+      <c r="Q843" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="R843" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S843" t="inlineStr"/>
+      <c r="T843" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U843" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V843" t="inlineStr"/>
+      <c r="W843" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011336_1</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>41011336_1</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011336</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:42</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:42</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:42</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:00</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>58117</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>45.869568</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>18.143677</t>
+        </is>
+      </c>
+      <c r="O844" t="inlineStr"/>
+      <c r="P844" t="inlineStr"/>
+      <c r="Q844" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R844" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S844" t="inlineStr"/>
+      <c r="T844" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U844" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V844" t="inlineStr"/>
+      <c r="W844" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011337_1</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>41011337_1</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011337</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:41:03</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:41:03</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:41:03</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:35:00</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:55:00</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>47.59405</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>19.241274</t>
+        </is>
+      </c>
+      <c r="O845" t="inlineStr"/>
+      <c r="P845" t="inlineStr"/>
+      <c r="Q845" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R845" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S845" t="inlineStr"/>
+      <c r="T845" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U845" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V845" t="inlineStr"/>
+      <c r="W845" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011338_1</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>41011338_1</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011338</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:41:24</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:41:24</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:41:24</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:00</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:40:00</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>47.57785</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>18.417128</t>
+        </is>
+      </c>
+      <c r="O846" t="inlineStr"/>
+      <c r="P846" t="inlineStr"/>
+      <c r="Q846" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="R846" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S846" t="inlineStr"/>
+      <c r="T846" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U846" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V846" t="inlineStr"/>
+      <c r="W846" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011339_1</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>41011339_1</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011339</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:43:04</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:43:04</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:43:04</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:25:00</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>47.859577</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>21.047897</t>
+        </is>
+      </c>
+      <c r="O847" t="inlineStr"/>
+      <c r="P847" t="inlineStr"/>
+      <c r="Q847" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="R847" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S847" t="inlineStr"/>
+      <c r="T847" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U847" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V847" t="inlineStr"/>
+      <c r="W847" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011340_1</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>41011340_1</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011340</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:44:35</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:44:35</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:44:35</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:00:00</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>47.371895</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>20.091146</t>
+        </is>
+      </c>
+      <c r="O848" t="inlineStr"/>
+      <c r="P848" t="inlineStr"/>
+      <c r="Q848" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="R848" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S848" t="inlineStr"/>
+      <c r="T848" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U848" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V848" t="inlineStr"/>
+      <c r="W848" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011341_1</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>41011341_1</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011341</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:44:57</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:44:57</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:44:57</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:00</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:44:00</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>47.193817</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>20.413218</t>
+        </is>
+      </c>
+      <c r="O849" t="inlineStr"/>
+      <c r="P849" t="inlineStr"/>
+      <c r="Q849" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R849" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S849" t="inlineStr"/>
+      <c r="T849" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U849" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V849" t="inlineStr"/>
+      <c r="W849" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011342_1</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>41011342_1</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011342</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:46:05</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:46:05</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:46:05</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:00</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:45:00</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>47.210968</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>20.55615</t>
+        </is>
+      </c>
+      <c r="O850" t="inlineStr"/>
+      <c r="P850" t="inlineStr"/>
+      <c r="Q850" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R850" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S850" t="inlineStr"/>
+      <c r="T850" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U850" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V850" t="inlineStr"/>
+      <c r="W850" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011343_1</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>41011343_1</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011343</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:46:20</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:46:20</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:46:20</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:30:00</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>47.873924</t>
+        </is>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>20.945864</t>
+        </is>
+      </c>
+      <c r="O851" t="inlineStr"/>
+      <c r="P851" t="inlineStr"/>
+      <c r="Q851" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="R851" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S851" t="inlineStr"/>
+      <c r="T851" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U851" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V851" t="inlineStr"/>
+      <c r="W851" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011344_1</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>41011344_1</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011344</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:46:48</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:46:48</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:46:48</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:00:00</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>47.502193</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>20.153767</t>
+        </is>
+      </c>
+      <c r="O852" t="inlineStr"/>
+      <c r="P852" t="inlineStr"/>
+      <c r="Q852" t="inlineStr">
+        <is>
+          <t>260.0</t>
+        </is>
+      </c>
+      <c r="R852" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S852" t="inlineStr"/>
+      <c r="T852" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U852" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V852" t="inlineStr"/>
+      <c r="W852" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011345_1</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>41011345_1</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011345</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:48:09</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:48:09</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:48:09</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:00:00</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>47.513844</t>
+        </is>
+      </c>
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>20.140047</t>
+        </is>
+      </c>
+      <c r="O853" t="inlineStr"/>
+      <c r="P853" t="inlineStr"/>
+      <c r="Q853" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="R853" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S853" t="inlineStr"/>
+      <c r="T853" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U853" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V853" t="inlineStr"/>
+      <c r="W853" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011346_1</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>41011346_1</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011346</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:48:29</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:48:29</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:48:29</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:35:00</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:47:00</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>47.403847</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>19.328453</t>
+        </is>
+      </c>
+      <c r="O854" t="inlineStr"/>
+      <c r="P854" t="inlineStr"/>
+      <c r="Q854" t="inlineStr">
+        <is>
+          <t>940.0</t>
+        </is>
+      </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S854" t="inlineStr"/>
+      <c r="T854" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U854" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V854" t="inlineStr"/>
+      <c r="W854" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011347_1</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>41011347_1</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011347</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:49:33</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:49:33</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:49:33</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>2026-07-31 12:00:00</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>4633</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>46.99494</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>20.24812</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr"/>
+      <c r="P855" t="inlineStr"/>
+      <c r="Q855" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="R855" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S855" t="inlineStr"/>
+      <c r="T855" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U855" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V855" t="inlineStr"/>
+      <c r="W855" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011348_1</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>41011348_1</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011348</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:49:55</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:49:55</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:49:55</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:45:00</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:47:00</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>47.68355</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>17.8868</t>
+        </is>
+      </c>
+      <c r="O856" t="inlineStr"/>
+      <c r="P856" t="inlineStr"/>
+      <c r="Q856" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R856" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S856" t="inlineStr"/>
+      <c r="T856" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U856" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V856" t="inlineStr"/>
+      <c r="W856" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011349_1</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>41011349_1</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011349</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:51:05</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:51:05</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:51:05</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:50:00</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:50:00</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>3708</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>48.474705</t>
+        </is>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>21.465284</t>
+        </is>
+      </c>
+      <c r="O857" t="inlineStr"/>
+      <c r="P857" t="inlineStr"/>
+      <c r="Q857" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R857" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S857" t="inlineStr"/>
+      <c r="T857" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U857" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V857" t="inlineStr"/>
+      <c r="W857" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011350_1</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>41011350_1</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011350</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:53:09</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:53:09</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:53:09</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>2026-07-24 12:00:00</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>4514</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>46.88552</t>
+        </is>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>20.119484</t>
+        </is>
+      </c>
+      <c r="O858" t="inlineStr"/>
+      <c r="P858" t="inlineStr"/>
+      <c r="Q858" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="R858" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S858" t="inlineStr"/>
+      <c r="T858" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U858" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V858" t="inlineStr"/>
+      <c r="W858" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011351_1</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>41011351_1</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011351</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:53:19</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:53:19</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:53:19</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:35:00</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:50:00</t>
+        </is>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>47.40536</t>
+        </is>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>19.30299</t>
+        </is>
+      </c>
+      <c r="O859" t="inlineStr"/>
+      <c r="P859" t="inlineStr"/>
+      <c r="Q859" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R859" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S859" t="inlineStr"/>
+      <c r="T859" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U859" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V859" t="inlineStr"/>
+      <c r="W859" t="inlineStr"/>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011352_1</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>41011352_1</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011352</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:53:42</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:53:42</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:53:42</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:35:00</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:00:00</t>
+        </is>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>46.150997</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>18.643095</t>
+        </is>
+      </c>
+      <c r="O860" t="inlineStr"/>
+      <c r="P860" t="inlineStr"/>
+      <c r="Q860" t="inlineStr">
+        <is>
+          <t>202.0</t>
+        </is>
+      </c>
+      <c r="R860" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S860" t="inlineStr"/>
+      <c r="T860" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U860" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V860" t="inlineStr"/>
+      <c r="W860" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011353_1</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>41011353_1</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011353</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:55:48</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:55:48</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:55:48</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:50:00</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:50:00</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>47.4348</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>18.893534</t>
+        </is>
+      </c>
+      <c r="O861" t="inlineStr"/>
+      <c r="P861" t="inlineStr"/>
+      <c r="Q861" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="R861" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S861" t="inlineStr"/>
+      <c r="T861" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U861" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V861" t="inlineStr"/>
+      <c r="W861" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011354_1</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>41011354_1</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011354</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:55:57</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:55:57</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:55:57</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:00</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:55:00</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>47.222153</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>19.693459</t>
+        </is>
+      </c>
+      <c r="O862" t="inlineStr"/>
+      <c r="P862" t="inlineStr"/>
+      <c r="Q862" t="inlineStr">
+        <is>
+          <t>875.0</t>
+        </is>
+      </c>
+      <c r="R862" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S862" t="inlineStr"/>
+      <c r="T862" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U862" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V862" t="inlineStr"/>
+      <c r="W862" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011355_1</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>41011355_1</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011355</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:56:03</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:56:03</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:56:03</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:00:00</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>47.016857</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>20.626305</t>
+        </is>
+      </c>
+      <c r="O863" t="inlineStr"/>
+      <c r="P863" t="inlineStr"/>
+      <c r="Q863" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="R863" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S863" t="inlineStr"/>
+      <c r="T863" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U863" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V863" t="inlineStr"/>
+      <c r="W863" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011356_1</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>41011356_1</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011356</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:58:20</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:58:20</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:58:20</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:00:00</t>
+        </is>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>4629</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>47.130035</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>20.378502</t>
+        </is>
+      </c>
+      <c r="O864" t="inlineStr"/>
+      <c r="P864" t="inlineStr"/>
+      <c r="Q864" t="inlineStr">
+        <is>
+          <t>833.0</t>
+        </is>
+      </c>
+      <c r="R864" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S864" t="inlineStr"/>
+      <c r="T864" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U864" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V864" t="inlineStr"/>
+      <c r="W864" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011357_1</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>41011357_1</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011357</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:58:39</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:58:39</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:58:39</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:40:00</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:58:00</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>47.349163</t>
+        </is>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>19.493057</t>
+        </is>
+      </c>
+      <c r="O865" t="inlineStr"/>
+      <c r="P865" t="inlineStr"/>
+      <c r="Q865" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R865" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S865" t="inlineStr"/>
+      <c r="T865" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U865" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V865" t="inlineStr"/>
+      <c r="W865" t="inlineStr"/>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011358_1</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>41011358_1</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011358</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:59:50</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:59:50</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:59:50</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:55:00</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>47.696518</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>19.765566</t>
+        </is>
+      </c>
+      <c r="O866" t="inlineStr"/>
+      <c r="P866" t="inlineStr"/>
+      <c r="Q866" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="R866" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S866" t="inlineStr"/>
+      <c r="T866" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U866" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:05</t>
+        </is>
+      </c>
+      <c r="V866" t="inlineStr"/>
+      <c r="W866" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W866"/>
+  <dimension ref="A1:W900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31182,7 +31182,7 @@
       <c r="S344" t="inlineStr"/>
       <c r="T344" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U344" t="inlineStr">
@@ -31190,7 +31190,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V344" t="inlineStr"/>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W344" t="inlineStr"/>
     </row>
     <row r="345">
@@ -52401,7 +52405,7 @@
       <c r="S577" t="inlineStr"/>
       <c r="T577" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U577" t="inlineStr">
@@ -52409,7 +52413,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V577" t="inlineStr"/>
+      <c r="V577" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W577" t="inlineStr"/>
     </row>
     <row r="578">
@@ -52591,7 +52599,7 @@
       <c r="S579" t="inlineStr"/>
       <c r="T579" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U579" t="inlineStr">
@@ -52599,7 +52607,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V579" t="inlineStr"/>
+      <c r="V579" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W579" t="inlineStr"/>
     </row>
     <row r="580">
@@ -64251,7 +64263,7 @@
       <c r="S699" t="inlineStr"/>
       <c r="T699" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U699" t="inlineStr">
@@ -64259,7 +64271,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V699" t="inlineStr"/>
+      <c r="V699" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W699" t="inlineStr"/>
     </row>
     <row r="700">
@@ -66781,7 +66797,7 @@
       <c r="S725" t="inlineStr"/>
       <c r="T725" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U725" t="inlineStr">
@@ -66789,7 +66805,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V725" t="inlineStr"/>
+      <c r="V725" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W725" t="inlineStr"/>
     </row>
     <row r="726">
@@ -67363,7 +67383,7 @@
       <c r="S731" t="inlineStr"/>
       <c r="T731" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U731" t="inlineStr">
@@ -67371,7 +67391,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V731" t="inlineStr"/>
+      <c r="V731" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W731" t="inlineStr"/>
     </row>
     <row r="732">
@@ -69012,7 +69036,7 @@
       <c r="S748" t="inlineStr"/>
       <c r="T748" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U748" t="inlineStr">
@@ -69020,7 +69044,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V748" t="inlineStr"/>
+      <c r="V748" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W748" t="inlineStr"/>
     </row>
     <row r="749">
@@ -71926,7 +71954,7 @@
       <c r="S778" t="inlineStr"/>
       <c r="T778" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U778" t="inlineStr">
@@ -71934,7 +71962,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V778" t="inlineStr"/>
+      <c r="V778" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W778" t="inlineStr"/>
     </row>
     <row r="779">
@@ -73090,7 +73122,7 @@
       <c r="S790" t="inlineStr"/>
       <c r="T790" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U790" t="inlineStr">
@@ -73098,7 +73130,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V790" t="inlineStr"/>
+      <c r="V790" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W790" t="inlineStr"/>
     </row>
     <row r="791">
@@ -77265,7 +77301,7 @@
       <c r="S833" t="inlineStr"/>
       <c r="T833" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U833" t="inlineStr">
@@ -77273,7 +77309,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V833" t="inlineStr"/>
+      <c r="V833" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W833" t="inlineStr"/>
     </row>
     <row r="834">
@@ -77556,7 +77596,7 @@
       <c r="S836" t="inlineStr"/>
       <c r="T836" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U836" t="inlineStr">
@@ -77564,7 +77604,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V836" t="inlineStr"/>
+      <c r="V836" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W836" t="inlineStr"/>
     </row>
     <row r="837">
@@ -77847,7 +77891,7 @@
       <c r="S839" t="inlineStr"/>
       <c r="T839" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U839" t="inlineStr">
@@ -77855,7 +77899,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V839" t="inlineStr"/>
+      <c r="V839" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W839" t="inlineStr"/>
     </row>
     <row r="840">
@@ -77944,7 +77992,7 @@
       <c r="S840" t="inlineStr"/>
       <c r="T840" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U840" t="inlineStr">
@@ -77952,7 +78000,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V840" t="inlineStr"/>
+      <c r="V840" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W840" t="inlineStr"/>
     </row>
     <row r="841">
@@ -79496,7 +79548,7 @@
       <c r="S856" t="inlineStr"/>
       <c r="T856" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U856" t="inlineStr">
@@ -79504,7 +79556,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V856" t="inlineStr"/>
+      <c r="V856" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W856" t="inlineStr"/>
     </row>
     <row r="857">
@@ -80369,7 +80425,7 @@
       <c r="S865" t="inlineStr"/>
       <c r="T865" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U865" t="inlineStr">
@@ -80377,7 +80433,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V865" t="inlineStr"/>
+      <c r="V865" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
       <c r="W865" t="inlineStr"/>
     </row>
     <row r="866">
@@ -80476,6 +80536,3304 @@
       </c>
       <c r="V866" t="inlineStr"/>
       <c r="W866" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133712_1</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>3133712_1</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133712</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:18</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:18</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:18</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:30:00</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr"/>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>46.36914</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>18.665224</t>
+        </is>
+      </c>
+      <c r="O867" t="inlineStr"/>
+      <c r="P867" t="inlineStr"/>
+      <c r="Q867" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="R867" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S867" t="inlineStr"/>
+      <c r="T867" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U867" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V867" t="inlineStr"/>
+      <c r="W867" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011359_1</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>41011359_1</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011359</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:37</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:37</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:37</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:00</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>M70</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>46.41483</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>16.741856</t>
+        </is>
+      </c>
+      <c r="O868" t="inlineStr"/>
+      <c r="P868" t="inlineStr"/>
+      <c r="Q868" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R868" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S868" t="inlineStr"/>
+      <c r="T868" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U868" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V868" t="inlineStr"/>
+      <c r="W868" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011360_1</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>41011360_1</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011360</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:58</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:58</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:58</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>2026-05-18 13:00:00</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>47.33275</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>20.127357</t>
+        </is>
+      </c>
+      <c r="O869" t="inlineStr"/>
+      <c r="P869" t="inlineStr"/>
+      <c r="Q869" t="inlineStr">
+        <is>
+          <t>475.0</t>
+        </is>
+      </c>
+      <c r="R869" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S869" t="inlineStr"/>
+      <c r="T869" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U869" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V869" t="inlineStr"/>
+      <c r="W869" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011361_1</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>41011361_1</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011361</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:01:18</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:01:18</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:01:18</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:00</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>70402</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>47.452003</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>18.952606</t>
+        </is>
+      </c>
+      <c r="O870" t="inlineStr"/>
+      <c r="P870" t="inlineStr"/>
+      <c r="Q870" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="R870" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S870" t="inlineStr"/>
+      <c r="T870" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U870" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V870" t="inlineStr"/>
+      <c r="W870" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011363_1</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>41011363_1</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011363</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:02</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:02</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:02</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:50:00</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:50:00</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>47.233017</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>20.680641</t>
+        </is>
+      </c>
+      <c r="O871" t="inlineStr"/>
+      <c r="P871" t="inlineStr"/>
+      <c r="Q871" t="inlineStr">
+        <is>
+          <t>305.0</t>
+        </is>
+      </c>
+      <c r="R871" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S871" t="inlineStr"/>
+      <c r="T871" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U871" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V871" t="inlineStr"/>
+      <c r="W871" t="inlineStr"/>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011364_1</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>41011364_1</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011364</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:04:36</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:04:36</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:04:36</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:03:00</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:03:00</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>48.50647</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>21.027914</t>
+        </is>
+      </c>
+      <c r="O872" t="inlineStr"/>
+      <c r="P872" t="inlineStr"/>
+      <c r="Q872" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R872" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S872" t="inlineStr"/>
+      <c r="T872" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U872" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V872" t="inlineStr"/>
+      <c r="W872" t="inlineStr"/>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011365_1</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>41011365_1</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011365</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:05:41</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:05:41</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:05:41</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:04:00</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:04:00</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>48.319126</t>
+        </is>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>20.913033</t>
+        </is>
+      </c>
+      <c r="O873" t="inlineStr"/>
+      <c r="P873" t="inlineStr"/>
+      <c r="Q873" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R873" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S873" t="inlineStr"/>
+      <c r="T873" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U873" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V873" t="inlineStr"/>
+      <c r="W873" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011366_1</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>41011366_1</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011366</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:07:52</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:07:52</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:07:52</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:00</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>47.84647</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>17.255772</t>
+        </is>
+      </c>
+      <c r="O874" t="inlineStr"/>
+      <c r="P874" t="inlineStr"/>
+      <c r="Q874" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="R874" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S874" t="inlineStr"/>
+      <c r="T874" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U874" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V874" t="inlineStr"/>
+      <c r="W874" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011367_1</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>41011367_1</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011367</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:08:30</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:08:30</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:08:30</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:00</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:05:00</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>M86</t>
+        </is>
+      </c>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>47.259125</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>16.731407</t>
+        </is>
+      </c>
+      <c r="O875" t="inlineStr"/>
+      <c r="P875" t="inlineStr"/>
+      <c r="Q875" t="inlineStr">
+        <is>
+          <t>870.0</t>
+        </is>
+      </c>
+      <c r="R875" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S875" t="inlineStr"/>
+      <c r="T875" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U875" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V875" t="inlineStr"/>
+      <c r="W875" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011368_1</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>41011368_1</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011368</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:09:24</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:09:24</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:09:24</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>2026-03-06 07:00:00</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>2026-03-06 17:00:00</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>8139</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>47.644817</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>18.308254</t>
+        </is>
+      </c>
+      <c r="O876" t="inlineStr"/>
+      <c r="P876" t="inlineStr"/>
+      <c r="Q876" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="R876" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S876" t="inlineStr"/>
+      <c r="T876" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U876" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V876" t="inlineStr"/>
+      <c r="W876" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011369_1</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>41011369_1</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011369</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:16:16</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:16:16</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:16:16</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:15:00</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:15:00</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>47.420452</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>18.884647</t>
+        </is>
+      </c>
+      <c r="O877" t="inlineStr"/>
+      <c r="P877" t="inlineStr"/>
+      <c r="Q877" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R877" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S877" t="inlineStr"/>
+      <c r="T877" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U877" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V877" t="inlineStr"/>
+      <c r="W877" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011370_1</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>41011370_1</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011370</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:16:37</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:16:37</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:16:37</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:00</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>47.83045</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>17.276243</t>
+        </is>
+      </c>
+      <c r="O878" t="inlineStr"/>
+      <c r="P878" t="inlineStr"/>
+      <c r="Q878" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R878" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S878" t="inlineStr"/>
+      <c r="T878" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U878" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V878" t="inlineStr"/>
+      <c r="W878" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011371_1</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>41011371_1</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011371</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:17:10</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:17:10</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:17:10</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:00</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:16:00</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>47.44311</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>19.33272</t>
+        </is>
+      </c>
+      <c r="O879" t="inlineStr"/>
+      <c r="P879" t="inlineStr"/>
+      <c r="Q879" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="R879" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S879" t="inlineStr"/>
+      <c r="T879" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U879" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V879" t="inlineStr"/>
+      <c r="W879" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011372_1</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>41011372_1</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011372</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:20:44</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:20:44</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:20:44</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:20:00</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:30:00</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>66168</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>46.300144</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>17.652044</t>
+        </is>
+      </c>
+      <c r="O880" t="inlineStr"/>
+      <c r="P880" t="inlineStr"/>
+      <c r="Q880" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R880" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S880" t="inlineStr"/>
+      <c r="T880" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U880" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V880" t="inlineStr"/>
+      <c r="W880" t="inlineStr"/>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011373_1</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>41011373_1</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011373</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:22:22</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:22:22</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:22:22</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>6616</t>
+        </is>
+      </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>46.35356</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>17.688541</t>
+        </is>
+      </c>
+      <c r="O881" t="inlineStr"/>
+      <c r="P881" t="inlineStr"/>
+      <c r="Q881" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R881" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S881" t="inlineStr">
+        <is>
+          <t>Oszlopok, táblák igazítása.</t>
+        </is>
+      </c>
+      <c r="T881" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U881" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V881" t="inlineStr"/>
+      <c r="W881" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011374_1</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>41011374_1</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011374</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>AbnormalTraffic</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:25:23</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:25:23</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:25:23</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:20:00</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:22:00</t>
+        </is>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>47.62363</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>18.31977</t>
+        </is>
+      </c>
+      <c r="O882" t="inlineStr"/>
+      <c r="P882" t="inlineStr"/>
+      <c r="Q882" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R882" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S882" t="inlineStr"/>
+      <c r="T882" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U882" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V882" t="inlineStr"/>
+      <c r="W882" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011375_1</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>41011375_1</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011375</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:26:28</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:26:28</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:26:28</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:25:00</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:00:00</t>
+        </is>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>47.63763</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>18.231943</t>
+        </is>
+      </c>
+      <c r="O883" t="inlineStr"/>
+      <c r="P883" t="inlineStr"/>
+      <c r="Q883" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="R883" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S883" t="inlineStr"/>
+      <c r="T883" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U883" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V883" t="inlineStr"/>
+      <c r="W883" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011376_1</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>41011376_1</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011376</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:28:29</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:28:29</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:28:29</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:25:00</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:27:00</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>47.205982</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>19.959896</t>
+        </is>
+      </c>
+      <c r="O884" t="inlineStr"/>
+      <c r="P884" t="inlineStr"/>
+      <c r="Q884" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R884" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S884" t="inlineStr"/>
+      <c r="T884" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U884" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V884" t="inlineStr"/>
+      <c r="W884" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011377_1</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>41011377_1</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011377</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:29:40</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:28:35</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:29:40</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:20:00</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:00</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>47.77508</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>20.57639</t>
+        </is>
+      </c>
+      <c r="O885" t="inlineStr"/>
+      <c r="P885" t="inlineStr"/>
+      <c r="Q885" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="R885" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S885" t="inlineStr"/>
+      <c r="T885" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U885" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V885" t="inlineStr"/>
+      <c r="W885" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011379_1</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>41011379_1</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011379</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:31:54</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:31:54</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:31:54</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:25:00</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:25:00</t>
+        </is>
+      </c>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>47.797432</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>21.231974</t>
+        </is>
+      </c>
+      <c r="O886" t="inlineStr"/>
+      <c r="P886" t="inlineStr"/>
+      <c r="Q886" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R886" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S886" t="inlineStr"/>
+      <c r="T886" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U886" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V886" t="inlineStr"/>
+      <c r="W886" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011380_1</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>41011380_1</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011380</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:32:10</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:32:10</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:32:10</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:31:00</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>7317</t>
+        </is>
+      </c>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>47.010845</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>17.45524</t>
+        </is>
+      </c>
+      <c r="O887" t="inlineStr"/>
+      <c r="P887" t="inlineStr"/>
+      <c r="Q887" t="inlineStr">
+        <is>
+          <t>392.0</t>
+        </is>
+      </c>
+      <c r="R887" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S887" t="inlineStr"/>
+      <c r="T887" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U887" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V887" t="inlineStr"/>
+      <c r="W887" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011381_1</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>41011381_1</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011381</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:32:46</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:32:46</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:32:46</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:00:00</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>46.927773</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>17.834663</t>
+        </is>
+      </c>
+      <c r="O888" t="inlineStr"/>
+      <c r="P888" t="inlineStr"/>
+      <c r="Q888" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R888" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S888" t="inlineStr"/>
+      <c r="T888" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U888" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V888" t="inlineStr"/>
+      <c r="W888" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011382_1</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>41011382_1</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011382</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:36:59</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:36:59</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:36:59</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:10:00</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>M35</t>
+        </is>
+      </c>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>47.500675</t>
+        </is>
+      </c>
+      <c r="N889" t="inlineStr">
+        <is>
+          <t>21.54742</t>
+        </is>
+      </c>
+      <c r="O889" t="inlineStr"/>
+      <c r="P889" t="inlineStr"/>
+      <c r="Q889" t="inlineStr">
+        <is>
+          <t>505.0</t>
+        </is>
+      </c>
+      <c r="R889" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S889" t="inlineStr"/>
+      <c r="T889" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U889" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V889" t="inlineStr"/>
+      <c r="W889" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011383_1</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>41011383_1</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011383</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:38:00</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:38:00</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:38:00</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:37:00</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:37:00</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>73152</t>
+        </is>
+      </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>46.94172</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>17.426882</t>
+        </is>
+      </c>
+      <c r="O890" t="inlineStr"/>
+      <c r="P890" t="inlineStr"/>
+      <c r="Q890" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R890" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S890" t="inlineStr"/>
+      <c r="T890" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U890" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V890" t="inlineStr"/>
+      <c r="W890" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011384_1</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>41011384_1</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011384</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:38:30</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:38:30</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:38:30</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:30:00</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:37:00</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>47.91823</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>20.84468</t>
+        </is>
+      </c>
+      <c r="O891" t="inlineStr"/>
+      <c r="P891" t="inlineStr"/>
+      <c r="Q891" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="R891" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S891" t="inlineStr"/>
+      <c r="T891" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U891" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V891" t="inlineStr"/>
+      <c r="W891" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011385_1</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>41011385_1</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011385</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:41:28</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:41:28</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:41:28</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:40:00</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>47.102757</t>
+        </is>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>18.378744</t>
+        </is>
+      </c>
+      <c r="O892" t="inlineStr"/>
+      <c r="P892" t="inlineStr"/>
+      <c r="Q892" t="inlineStr">
+        <is>
+          <t>499.0</t>
+        </is>
+      </c>
+      <c r="R892" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S892" t="inlineStr"/>
+      <c r="T892" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U892" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V892" t="inlineStr"/>
+      <c r="W892" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011386_1</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>41011386_1</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011386</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>AnimalPresenceObstruction</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:44:58</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:44:58</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:44:58</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:00</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:43:00</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>47.903545</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>19.678268</t>
+        </is>
+      </c>
+      <c r="O893" t="inlineStr"/>
+      <c r="P893" t="inlineStr"/>
+      <c r="Q893" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R893" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S893" t="inlineStr"/>
+      <c r="T893" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U893" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V893" t="inlineStr"/>
+      <c r="W893" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011388_1</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>41011388_1</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011388</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:46:21</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:46:21</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:46:21</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:40:00</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:44:00</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>47.68355</t>
+        </is>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>17.8868</t>
+        </is>
+      </c>
+      <c r="O894" t="inlineStr"/>
+      <c r="P894" t="inlineStr"/>
+      <c r="Q894" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R894" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S894" t="inlineStr"/>
+      <c r="T894" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U894" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V894" t="inlineStr"/>
+      <c r="W894" t="inlineStr"/>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011390_1</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>41011390_1</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011390</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:46:38</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:46:38</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:46:38</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:45:00</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:45:00</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="M895" t="inlineStr">
+        <is>
+          <t>47.41772</t>
+        </is>
+      </c>
+      <c r="N895" t="inlineStr">
+        <is>
+          <t>18.882406</t>
+        </is>
+      </c>
+      <c r="O895" t="inlineStr"/>
+      <c r="P895" t="inlineStr"/>
+      <c r="Q895" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="R895" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S895" t="inlineStr"/>
+      <c r="T895" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U895" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V895" t="inlineStr"/>
+      <c r="W895" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011391_1</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>41011391_1</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011391</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:46:58</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:46:58</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:46:58</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:40:00</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:46:00</t>
+        </is>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>M35</t>
+        </is>
+      </c>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>47.611256</t>
+        </is>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>21.52026</t>
+        </is>
+      </c>
+      <c r="O896" t="inlineStr"/>
+      <c r="P896" t="inlineStr"/>
+      <c r="Q896" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="R896" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S896" t="inlineStr"/>
+      <c r="T896" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U896" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V896" t="inlineStr"/>
+      <c r="W896" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011392_1</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>41011392_1</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011392</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:01</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:01</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:01</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:50:00</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:05:00</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>47.888844</t>
+        </is>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>17.18493</t>
+        </is>
+      </c>
+      <c r="O897" t="inlineStr"/>
+      <c r="P897" t="inlineStr"/>
+      <c r="Q897" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R897" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S897" t="inlineStr"/>
+      <c r="T897" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U897" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V897" t="inlineStr"/>
+      <c r="W897" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011393_1</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>41011393_1</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011393</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:07</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:07</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:07</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>47.749603</t>
+        </is>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>18.49161</t>
+        </is>
+      </c>
+      <c r="O898" t="inlineStr"/>
+      <c r="P898" t="inlineStr"/>
+      <c r="Q898" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="R898" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S898" t="inlineStr"/>
+      <c r="T898" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U898" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V898" t="inlineStr"/>
+      <c r="W898" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011394_1</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>41011394_1</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011394</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:08</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:08</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:08</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:45:00</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:48:00</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>M85</t>
+        </is>
+      </c>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>47.705425</t>
+        </is>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>16.607347</t>
+        </is>
+      </c>
+      <c r="O899" t="inlineStr"/>
+      <c r="P899" t="inlineStr"/>
+      <c r="Q899" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="R899" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S899" t="inlineStr"/>
+      <c r="T899" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U899" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V899" t="inlineStr"/>
+      <c r="W899" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011395_1</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>41011395_1</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011395</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:44</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:44</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:52:44</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:45:00</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:45:00</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>47.390804</t>
+        </is>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>18.850647</t>
+        </is>
+      </c>
+      <c r="O900" t="inlineStr"/>
+      <c r="P900" t="inlineStr"/>
+      <c r="Q900" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="R900" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S900" t="inlineStr"/>
+      <c r="T900" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U900" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:58:26</t>
+        </is>
+      </c>
+      <c r="V900" t="inlineStr"/>
+      <c r="W900" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W900"/>
+  <dimension ref="A1:W926"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31898,7 +31898,7 @@
       <c r="S352" t="inlineStr"/>
       <c r="T352" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U352" t="inlineStr">
@@ -31906,7 +31906,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V352" t="inlineStr"/>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W352" t="inlineStr"/>
     </row>
     <row r="353">
@@ -53282,7 +53286,7 @@
       <c r="S586" t="inlineStr"/>
       <c r="T586" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U586" t="inlineStr">
@@ -53290,7 +53294,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V586" t="inlineStr"/>
+      <c r="V586" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W586" t="inlineStr"/>
     </row>
     <row r="587">
@@ -53476,7 +53484,7 @@
       <c r="S588" t="inlineStr"/>
       <c r="T588" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U588" t="inlineStr">
@@ -53484,7 +53492,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V588" t="inlineStr"/>
+      <c r="V588" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W588" t="inlineStr"/>
     </row>
     <row r="589">
@@ -59118,7 +59130,7 @@
       <c r="S646" t="inlineStr"/>
       <c r="T646" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U646" t="inlineStr">
@@ -59126,7 +59138,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V646" t="inlineStr"/>
+      <c r="V646" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W646" t="inlineStr"/>
     </row>
     <row r="647">
@@ -63685,7 +63701,7 @@
       <c r="S693" t="inlineStr"/>
       <c r="T693" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U693" t="inlineStr">
@@ -63693,7 +63709,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V693" t="inlineStr"/>
+      <c r="V693" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W693" t="inlineStr"/>
     </row>
     <row r="694">
@@ -66409,7 +66429,7 @@
       <c r="S721" t="inlineStr"/>
       <c r="T721" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U721" t="inlineStr">
@@ -66417,7 +66437,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V721" t="inlineStr"/>
+      <c r="V721" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W721" t="inlineStr"/>
     </row>
     <row r="722">
@@ -67969,7 +67993,7 @@
       <c r="S737" t="inlineStr"/>
       <c r="T737" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U737" t="inlineStr">
@@ -67977,7 +68001,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V737" t="inlineStr"/>
+      <c r="V737" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W737" t="inlineStr"/>
     </row>
     <row r="738">
@@ -69913,7 +69941,7 @@
       <c r="S757" t="inlineStr"/>
       <c r="T757" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U757" t="inlineStr">
@@ -69921,7 +69949,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V757" t="inlineStr"/>
+      <c r="V757" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W757" t="inlineStr"/>
     </row>
     <row r="758">
@@ -72637,7 +72669,7 @@
       <c r="S785" t="inlineStr"/>
       <c r="T785" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U785" t="inlineStr">
@@ -72645,7 +72677,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V785" t="inlineStr"/>
+      <c r="V785" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W785" t="inlineStr"/>
     </row>
     <row r="786">
@@ -72928,7 +72964,7 @@
       <c r="S788" t="inlineStr"/>
       <c r="T788" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U788" t="inlineStr">
@@ -72936,7 +72972,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V788" t="inlineStr"/>
+      <c r="V788" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W788" t="inlineStr"/>
     </row>
     <row r="789">
@@ -73320,7 +73360,7 @@
       <c r="S792" t="inlineStr"/>
       <c r="T792" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U792" t="inlineStr">
@@ -73328,7 +73368,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V792" t="inlineStr"/>
+      <c r="V792" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W792" t="inlineStr"/>
     </row>
     <row r="793">
@@ -73611,7 +73655,7 @@
       <c r="S795" t="inlineStr"/>
       <c r="T795" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U795" t="inlineStr">
@@ -73619,7 +73663,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V795" t="inlineStr"/>
+      <c r="V795" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W795" t="inlineStr"/>
     </row>
     <row r="796">
@@ -77697,7 +77745,7 @@
       <c r="S837" t="inlineStr"/>
       <c r="T837" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U837" t="inlineStr">
@@ -77705,7 +77753,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V837" t="inlineStr"/>
+      <c r="V837" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W837" t="inlineStr"/>
     </row>
     <row r="838">
@@ -79940,7 +79992,7 @@
       <c r="S860" t="inlineStr"/>
       <c r="T860" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U860" t="inlineStr">
@@ -79948,7 +80000,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V860" t="inlineStr"/>
+      <c r="V860" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W860" t="inlineStr"/>
     </row>
     <row r="861">
@@ -80037,7 +80093,7 @@
       <c r="S861" t="inlineStr"/>
       <c r="T861" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U861" t="inlineStr">
@@ -80045,7 +80101,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V861" t="inlineStr"/>
+      <c r="V861" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W861" t="inlineStr"/>
     </row>
     <row r="862">
@@ -80619,7 +80679,7 @@
       <c r="S867" t="inlineStr"/>
       <c r="T867" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U867" t="inlineStr">
@@ -80627,7 +80687,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V867" t="inlineStr"/>
+      <c r="V867" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W867" t="inlineStr"/>
     </row>
     <row r="868">
@@ -80716,7 +80780,7 @@
       <c r="S868" t="inlineStr"/>
       <c r="T868" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U868" t="inlineStr">
@@ -80724,7 +80788,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V868" t="inlineStr"/>
+      <c r="V868" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W868" t="inlineStr"/>
     </row>
     <row r="869">
@@ -82369,7 +82437,7 @@
       <c r="S885" t="inlineStr"/>
       <c r="T885" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U885" t="inlineStr">
@@ -82377,7 +82445,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V885" t="inlineStr"/>
+      <c r="V885" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W885" t="inlineStr"/>
     </row>
     <row r="886">
@@ -82466,7 +82538,7 @@
       <c r="S886" t="inlineStr"/>
       <c r="T886" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U886" t="inlineStr">
@@ -82474,7 +82546,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V886" t="inlineStr"/>
+      <c r="V886" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W886" t="inlineStr"/>
     </row>
     <row r="887">
@@ -82757,7 +82833,7 @@
       <c r="S889" t="inlineStr"/>
       <c r="T889" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U889" t="inlineStr">
@@ -82765,7 +82841,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V889" t="inlineStr"/>
+      <c r="V889" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W889" t="inlineStr"/>
     </row>
     <row r="890">
@@ -82854,7 +82934,7 @@
       <c r="S890" t="inlineStr"/>
       <c r="T890" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U890" t="inlineStr">
@@ -82862,7 +82942,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V890" t="inlineStr"/>
+      <c r="V890" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W890" t="inlineStr"/>
     </row>
     <row r="891">
@@ -83242,7 +83326,7 @@
       <c r="S894" t="inlineStr"/>
       <c r="T894" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U894" t="inlineStr">
@@ -83250,7 +83334,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V894" t="inlineStr"/>
+      <c r="V894" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W894" t="inlineStr"/>
     </row>
     <row r="895">
@@ -83339,7 +83427,7 @@
       <c r="S895" t="inlineStr"/>
       <c r="T895" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U895" t="inlineStr">
@@ -83347,7 +83435,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V895" t="inlineStr"/>
+      <c r="V895" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W895" t="inlineStr"/>
     </row>
     <row r="896">
@@ -83533,7 +83625,7 @@
       <c r="S897" t="inlineStr"/>
       <c r="T897" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U897" t="inlineStr">
@@ -83541,7 +83633,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V897" t="inlineStr"/>
+      <c r="V897" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W897" t="inlineStr"/>
     </row>
     <row r="898">
@@ -83727,7 +83823,7 @@
       <c r="S899" t="inlineStr"/>
       <c r="T899" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U899" t="inlineStr">
@@ -83735,7 +83831,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V899" t="inlineStr"/>
+      <c r="V899" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
       <c r="W899" t="inlineStr"/>
     </row>
     <row r="900">
@@ -83834,6 +83934,2524 @@
       </c>
       <c r="V900" t="inlineStr"/>
       <c r="W900" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133713_1</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>3133713_1</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133713</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:17:35</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:17:35</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:17:35</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:17:00</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>47.976326</t>
+        </is>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>20.34219</t>
+        </is>
+      </c>
+      <c r="O901" t="inlineStr"/>
+      <c r="P901" t="inlineStr"/>
+      <c r="Q901" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R901" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S901" t="inlineStr"/>
+      <c r="T901" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U901" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V901" t="inlineStr"/>
+      <c r="W901" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011387_1</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>41011387_1</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011387</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:13:12</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:45:08</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:13:12</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:40:00</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:44:00</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M902" t="inlineStr">
+        <is>
+          <t>47.370457</t>
+        </is>
+      </c>
+      <c r="N902" t="inlineStr">
+        <is>
+          <t>19.47632</t>
+        </is>
+      </c>
+      <c r="O902" t="inlineStr"/>
+      <c r="P902" t="inlineStr"/>
+      <c r="Q902" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="R902" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S902" t="inlineStr"/>
+      <c r="T902" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U902" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V902" t="inlineStr"/>
+      <c r="W902" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011397_1</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>41011397_1</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011397</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:56:15</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:56:15</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:56:15</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>2026-03-06 20:00:00</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="M903" t="inlineStr">
+        <is>
+          <t>47.79535</t>
+        </is>
+      </c>
+      <c r="N903" t="inlineStr">
+        <is>
+          <t>18.744263</t>
+        </is>
+      </c>
+      <c r="O903" t="inlineStr"/>
+      <c r="P903" t="inlineStr"/>
+      <c r="Q903" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="R903" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S903" t="inlineStr"/>
+      <c r="T903" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U903" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V903" t="inlineStr"/>
+      <c r="W903" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011398_1</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>41011398_1</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011398</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>VehicleObstruction</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:56:44</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:56:44</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:56:44</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:55:00</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:55:00</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>47.399536</t>
+        </is>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>19.164831</t>
+        </is>
+      </c>
+      <c r="O904" t="inlineStr"/>
+      <c r="P904" t="inlineStr"/>
+      <c r="Q904" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
+      </c>
+      <c r="R904" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S904" t="inlineStr"/>
+      <c r="T904" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U904" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V904" t="inlineStr"/>
+      <c r="W904" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011399_1</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>41011399_1</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011399</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:57:59</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:57:59</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:57:59</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:50:00</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:55:00</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>M86</t>
+        </is>
+      </c>
+      <c r="M905" t="inlineStr">
+        <is>
+          <t>47.41039</t>
+        </is>
+      </c>
+      <c r="N905" t="inlineStr">
+        <is>
+          <t>17.017849</t>
+        </is>
+      </c>
+      <c r="O905" t="inlineStr"/>
+      <c r="P905" t="inlineStr"/>
+      <c r="Q905" t="inlineStr">
+        <is>
+          <t>595.0</t>
+        </is>
+      </c>
+      <c r="R905" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S905" t="inlineStr"/>
+      <c r="T905" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U905" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V905" t="inlineStr"/>
+      <c r="W905" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011401_1</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>41011401_1</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011401</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:21</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:21</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:21</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:00:00</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>5801</t>
+        </is>
+      </c>
+      <c r="M906" t="inlineStr">
+        <is>
+          <t>45.978718</t>
+        </is>
+      </c>
+      <c r="N906" t="inlineStr">
+        <is>
+          <t>18.144913</t>
+        </is>
+      </c>
+      <c r="O906" t="inlineStr"/>
+      <c r="P906" t="inlineStr"/>
+      <c r="Q906" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="R906" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S906" t="inlineStr"/>
+      <c r="T906" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U906" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V906" t="inlineStr"/>
+      <c r="W906" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011402_1</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>41011402_1</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011402</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:48</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:48</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:48</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:00:00</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="M907" t="inlineStr">
+        <is>
+          <t>47.41235</t>
+        </is>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>18.878899</t>
+        </is>
+      </c>
+      <c r="O907" t="inlineStr"/>
+      <c r="P907" t="inlineStr"/>
+      <c r="Q907" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R907" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S907" t="inlineStr"/>
+      <c r="T907" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U907" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V907" t="inlineStr"/>
+      <c r="W907" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011403_1</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>41011403_1</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011403</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:04:29</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:04:29</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:04:29</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:55:00</t>
+        </is>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>86418</t>
+        </is>
+      </c>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>47.25591</t>
+        </is>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>16.720484</t>
+        </is>
+      </c>
+      <c r="O908" t="inlineStr"/>
+      <c r="P908" t="inlineStr"/>
+      <c r="Q908" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="R908" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S908" t="inlineStr"/>
+      <c r="T908" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U908" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V908" t="inlineStr"/>
+      <c r="W908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011404_1</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>41011404_1</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011404</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:04:46</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:04:46</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:04:46</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:00:00</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>46.35658</t>
+        </is>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>20.00454</t>
+        </is>
+      </c>
+      <c r="O909" t="inlineStr"/>
+      <c r="P909" t="inlineStr"/>
+      <c r="Q909" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="R909" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S909" t="inlineStr"/>
+      <c r="T909" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U909" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V909" t="inlineStr"/>
+      <c r="W909" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011405_1</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>41011405_1</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011405</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:05:00</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:05:00</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:05:00</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:59:00</t>
+        </is>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>47.750275</t>
+        </is>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>17.416687</t>
+        </is>
+      </c>
+      <c r="O910" t="inlineStr"/>
+      <c r="P910" t="inlineStr"/>
+      <c r="Q910" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R910" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S910" t="inlineStr"/>
+      <c r="T910" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U910" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V910" t="inlineStr"/>
+      <c r="W910" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011406_1</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>41011406_1</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011406</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:07:47</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:07:47</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:07:47</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:05:00</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>48.110218</t>
+        </is>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>20.843489</t>
+        </is>
+      </c>
+      <c r="O911" t="inlineStr"/>
+      <c r="P911" t="inlineStr"/>
+      <c r="Q911" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="R911" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S911" t="inlineStr"/>
+      <c r="T911" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U911" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V911" t="inlineStr"/>
+      <c r="W911" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011407_1</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>41011407_1</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011407</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:09:06</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:09:06</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:09:06</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:07:00</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:07:00</t>
+        </is>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>21115</t>
+        </is>
+      </c>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>47.646988</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>19.453148</t>
+        </is>
+      </c>
+      <c r="O912" t="inlineStr"/>
+      <c r="P912" t="inlineStr"/>
+      <c r="Q912" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="R912" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S912" t="inlineStr"/>
+      <c r="T912" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U912" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V912" t="inlineStr"/>
+      <c r="W912" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011408_1</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>41011408_1</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011408</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:11:48</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:11:48</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:11:48</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:10:00</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M913" t="inlineStr">
+        <is>
+          <t>47.87035</t>
+        </is>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>20.793661</t>
+        </is>
+      </c>
+      <c r="O913" t="inlineStr"/>
+      <c r="P913" t="inlineStr"/>
+      <c r="Q913" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="R913" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S913" t="inlineStr"/>
+      <c r="T913" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U913" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V913" t="inlineStr"/>
+      <c r="W913" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011409_1</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>41011409_1</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011409</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:17:14</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:17:14</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:17:14</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:11:00</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>46.150997</t>
+        </is>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>18.643095</t>
+        </is>
+      </c>
+      <c r="O914" t="inlineStr"/>
+      <c r="P914" t="inlineStr"/>
+      <c r="Q914" t="inlineStr">
+        <is>
+          <t>202.0</t>
+        </is>
+      </c>
+      <c r="R914" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S914" t="inlineStr"/>
+      <c r="T914" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U914" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V914" t="inlineStr"/>
+      <c r="W914" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011410_1</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>41011410_1</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011410</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:18:52</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:18:52</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:18:52</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:17:00</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:30:00</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>47.96863</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>20.348179</t>
+        </is>
+      </c>
+      <c r="O915" t="inlineStr"/>
+      <c r="P915" t="inlineStr"/>
+      <c r="Q915" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R915" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S915" t="inlineStr"/>
+      <c r="T915" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U915" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V915" t="inlineStr"/>
+      <c r="W915" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011411_1</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>41011411_1</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011411</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:20:21</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:20:21</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:20:21</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:15:00</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M916" t="inlineStr">
+        <is>
+          <t>47.807457</t>
+        </is>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>21.167055</t>
+        </is>
+      </c>
+      <c r="O916" t="inlineStr"/>
+      <c r="P916" t="inlineStr"/>
+      <c r="Q916" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R916" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S916" t="inlineStr"/>
+      <c r="T916" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U916" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V916" t="inlineStr"/>
+      <c r="W916" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011412_1</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>41011412_1</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011412</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:24:11</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:24:11</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:24:11</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:20:00</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M917" t="inlineStr">
+        <is>
+          <t>47.19099</t>
+        </is>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>20.450134</t>
+        </is>
+      </c>
+      <c r="O917" t="inlineStr"/>
+      <c r="P917" t="inlineStr"/>
+      <c r="Q917" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R917" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S917" t="inlineStr"/>
+      <c r="T917" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U917" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V917" t="inlineStr"/>
+      <c r="W917" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011413_1</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>41011413_1</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011413</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:31:24</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:31:24</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:31:24</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:30:00</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M918" t="inlineStr">
+        <is>
+          <t>47.77495</t>
+        </is>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>20.575747</t>
+        </is>
+      </c>
+      <c r="O918" t="inlineStr"/>
+      <c r="P918" t="inlineStr"/>
+      <c r="Q918" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R918" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S918" t="inlineStr"/>
+      <c r="T918" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U918" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V918" t="inlineStr"/>
+      <c r="W918" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011414_1</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>41011414_1</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011414</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:33:48</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:33:48</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:33:48</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:30:00</t>
+        </is>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:30:00</t>
+        </is>
+      </c>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="M919" t="inlineStr">
+        <is>
+          <t>47.428192</t>
+        </is>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>19.324139</t>
+        </is>
+      </c>
+      <c r="O919" t="inlineStr"/>
+      <c r="P919" t="inlineStr"/>
+      <c r="Q919" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R919" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S919" t="inlineStr"/>
+      <c r="T919" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U919" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V919" t="inlineStr"/>
+      <c r="W919" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011415_1</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>41011415_1</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011415</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:43:18</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:43:18</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:43:18</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:40:00</t>
+        </is>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:30:00</t>
+        </is>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>M35</t>
+        </is>
+      </c>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>47.500683</t>
+        </is>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>21.547272</t>
+        </is>
+      </c>
+      <c r="O920" t="inlineStr"/>
+      <c r="P920" t="inlineStr"/>
+      <c r="Q920" t="inlineStr">
+        <is>
+          <t>505.0</t>
+        </is>
+      </c>
+      <c r="R920" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S920" t="inlineStr"/>
+      <c r="T920" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U920" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V920" t="inlineStr"/>
+      <c r="W920" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011416_1</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>41011416_1</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011416</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:43:29</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:43:29</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:43:29</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:25:00</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:35:00</t>
+        </is>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>47.886635</t>
+        </is>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>17.187704</t>
+        </is>
+      </c>
+      <c r="O921" t="inlineStr"/>
+      <c r="P921" t="inlineStr"/>
+      <c r="Q921" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R921" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S921" t="inlineStr"/>
+      <c r="T921" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U921" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V921" t="inlineStr"/>
+      <c r="W921" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011417_1</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>41011417_1</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011417</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:51:04</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:51:04</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:51:04</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:45:00</t>
+        </is>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>47.778843</t>
+        </is>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>20.589437</t>
+        </is>
+      </c>
+      <c r="O922" t="inlineStr"/>
+      <c r="P922" t="inlineStr"/>
+      <c r="Q922" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="R922" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S922" t="inlineStr"/>
+      <c r="T922" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U922" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V922" t="inlineStr"/>
+      <c r="W922" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011418_1</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>41011418_1</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011418</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:53:05</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:53:05</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:53:05</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:40:00</t>
+        </is>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>30821</t>
+        </is>
+      </c>
+      <c r="M923" t="inlineStr">
+        <is>
+          <t>47.842644</t>
+        </is>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>20.744663</t>
+        </is>
+      </c>
+      <c r="O923" t="inlineStr"/>
+      <c r="P923" t="inlineStr"/>
+      <c r="Q923" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="R923" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S923" t="inlineStr"/>
+      <c r="T923" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U923" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V923" t="inlineStr"/>
+      <c r="W923" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011419_1</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>41011419_1</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011419</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:55:37</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:55:37</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:55:37</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>5303</t>
+        </is>
+      </c>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>46.654423</t>
+        </is>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>19.348423</t>
+        </is>
+      </c>
+      <c r="O924" t="inlineStr"/>
+      <c r="P924" t="inlineStr"/>
+      <c r="Q924" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="R924" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S924" t="inlineStr"/>
+      <c r="T924" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U924" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V924" t="inlineStr"/>
+      <c r="W924" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011420_1</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>41011420_1</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011420</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:56:15</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:56:15</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:56:15</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:00:00</t>
+        </is>
+      </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>66164</t>
+        </is>
+      </c>
+      <c r="M925" t="inlineStr">
+        <is>
+          <t>46.198643</t>
+        </is>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>17.622873</t>
+        </is>
+      </c>
+      <c r="O925" t="inlineStr"/>
+      <c r="P925" t="inlineStr"/>
+      <c r="Q925" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R925" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S925" t="inlineStr"/>
+      <c r="T925" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U925" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V925" t="inlineStr"/>
+      <c r="W925" t="inlineStr"/>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011421_1</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>41011421_1</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011421</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:56:49</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:56:49</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:56:49</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>53107</t>
+        </is>
+      </c>
+      <c r="M926" t="inlineStr">
+        <is>
+          <t>46.622967</t>
+        </is>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>19.276636</t>
+        </is>
+      </c>
+      <c r="O926" t="inlineStr"/>
+      <c r="P926" t="inlineStr"/>
+      <c r="Q926" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R926" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S926" t="inlineStr"/>
+      <c r="T926" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U926" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:21</t>
+        </is>
+      </c>
+      <c r="V926" t="inlineStr"/>
+      <c r="W926" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W926"/>
+  <dimension ref="A1:W946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31542,7 +31542,7 @@
       <c r="S348" t="inlineStr"/>
       <c r="T348" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U348" t="inlineStr">
@@ -31550,7 +31550,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V348" t="inlineStr"/>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W348" t="inlineStr"/>
     </row>
     <row r="349">
@@ -64190,7 +64194,7 @@
       <c r="S698" t="inlineStr"/>
       <c r="T698" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U698" t="inlineStr">
@@ -64198,7 +64202,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V698" t="inlineStr"/>
+      <c r="V698" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W698" t="inlineStr"/>
     </row>
     <row r="699">
@@ -64675,7 +64683,7 @@
       <c r="S703" t="inlineStr"/>
       <c r="T703" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U703" t="inlineStr">
@@ -64683,7 +64691,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V703" t="inlineStr"/>
+      <c r="V703" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W703" t="inlineStr"/>
     </row>
     <row r="704">
@@ -69359,7 +69371,7 @@
       <c r="S751" t="inlineStr"/>
       <c r="T751" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U751" t="inlineStr">
@@ -69367,7 +69379,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V751" t="inlineStr"/>
+      <c r="V751" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W751" t="inlineStr"/>
     </row>
     <row r="752">
@@ -70915,7 +70931,7 @@
       <c r="S767" t="inlineStr"/>
       <c r="T767" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U767" t="inlineStr">
@@ -70923,7 +70939,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V767" t="inlineStr"/>
+      <c r="V767" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W767" t="inlineStr"/>
     </row>
     <row r="768">
@@ -72572,7 +72592,7 @@
       <c r="S784" t="inlineStr"/>
       <c r="T784" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U784" t="inlineStr">
@@ -72580,7 +72600,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V784" t="inlineStr"/>
+      <c r="V784" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W784" t="inlineStr"/>
     </row>
     <row r="785">
@@ -73461,7 +73485,7 @@
       <c r="S793" t="inlineStr"/>
       <c r="T793" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U793" t="inlineStr">
@@ -73469,7 +73493,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V793" t="inlineStr"/>
+      <c r="V793" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W793" t="inlineStr"/>
     </row>
     <row r="794">
@@ -78339,7 +78367,7 @@
       <c r="S843" t="inlineStr"/>
       <c r="T843" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U843" t="inlineStr">
@@ -78347,7 +78375,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V843" t="inlineStr"/>
+      <c r="V843" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W843" t="inlineStr"/>
     </row>
     <row r="844">
@@ -78533,7 +78565,7 @@
       <c r="S845" t="inlineStr"/>
       <c r="T845" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U845" t="inlineStr">
@@ -78541,7 +78573,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V845" t="inlineStr"/>
+      <c r="V845" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W845" t="inlineStr"/>
     </row>
     <row r="846">
@@ -78921,7 +78957,7 @@
       <c r="S849" t="inlineStr"/>
       <c r="T849" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U849" t="inlineStr">
@@ -78929,7 +78965,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V849" t="inlineStr"/>
+      <c r="V849" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W849" t="inlineStr"/>
     </row>
     <row r="850">
@@ -80194,7 +80234,7 @@
       <c r="S862" t="inlineStr"/>
       <c r="T862" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U862" t="inlineStr">
@@ -80202,7 +80242,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V862" t="inlineStr"/>
+      <c r="V862" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W862" t="inlineStr"/>
     </row>
     <row r="863">
@@ -80978,7 +81022,7 @@
       <c r="S870" t="inlineStr"/>
       <c r="T870" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U870" t="inlineStr">
@@ -80986,7 +81030,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V870" t="inlineStr"/>
+      <c r="V870" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W870" t="inlineStr"/>
     </row>
     <row r="871">
@@ -81948,7 +81996,7 @@
       <c r="S880" t="inlineStr"/>
       <c r="T880" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U880" t="inlineStr">
@@ -81956,7 +82004,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V880" t="inlineStr"/>
+      <c r="V880" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W880" t="inlineStr"/>
     </row>
     <row r="881">
@@ -82340,7 +82392,7 @@
       <c r="S884" t="inlineStr"/>
       <c r="T884" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U884" t="inlineStr">
@@ -82348,7 +82400,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V884" t="inlineStr"/>
+      <c r="V884" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W884" t="inlineStr"/>
     </row>
     <row r="885">
@@ -83528,7 +83584,7 @@
       <c r="S896" t="inlineStr"/>
       <c r="T896" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U896" t="inlineStr">
@@ -83536,7 +83592,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V896" t="inlineStr"/>
+      <c r="V896" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W896" t="inlineStr"/>
     </row>
     <row r="897">
@@ -84017,7 +84077,7 @@
       <c r="S901" t="inlineStr"/>
       <c r="T901" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U901" t="inlineStr">
@@ -84025,7 +84085,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V901" t="inlineStr"/>
+      <c r="V901" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W901" t="inlineStr"/>
     </row>
     <row r="902">
@@ -84114,7 +84178,7 @@
       <c r="S902" t="inlineStr"/>
       <c r="T902" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U902" t="inlineStr">
@@ -84122,7 +84186,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V902" t="inlineStr"/>
+      <c r="V902" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W902" t="inlineStr"/>
     </row>
     <row r="903">
@@ -84599,7 +84667,7 @@
       <c r="S907" t="inlineStr"/>
       <c r="T907" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U907" t="inlineStr">
@@ -84607,7 +84675,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V907" t="inlineStr"/>
+      <c r="V907" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W907" t="inlineStr"/>
     </row>
     <row r="908">
@@ -85278,7 +85350,7 @@
       <c r="S914" t="inlineStr"/>
       <c r="T914" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U914" t="inlineStr">
@@ -85286,7 +85358,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V914" t="inlineStr"/>
+      <c r="V914" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W914" t="inlineStr"/>
     </row>
     <row r="915">
@@ -85375,7 +85451,7 @@
       <c r="S915" t="inlineStr"/>
       <c r="T915" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U915" t="inlineStr">
@@ -85383,7 +85459,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V915" t="inlineStr"/>
+      <c r="V915" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W915" t="inlineStr"/>
     </row>
     <row r="916">
@@ -85957,7 +86037,7 @@
       <c r="S921" t="inlineStr"/>
       <c r="T921" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U921" t="inlineStr">
@@ -85965,7 +86045,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V921" t="inlineStr"/>
+      <c r="V921" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W921" t="inlineStr"/>
     </row>
     <row r="922">
@@ -86054,7 +86138,7 @@
       <c r="S922" t="inlineStr"/>
       <c r="T922" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U922" t="inlineStr">
@@ -86062,7 +86146,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V922" t="inlineStr"/>
+      <c r="V922" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
       <c r="W922" t="inlineStr"/>
     </row>
     <row r="923">
@@ -86452,6 +86540,1942 @@
       </c>
       <c r="V926" t="inlineStr"/>
       <c r="W926" t="inlineStr"/>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133715_1</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>3133715_1</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133715</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:25:18</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:25:01</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:25:18</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:20:00</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr"/>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="M927" t="inlineStr">
+        <is>
+          <t>46.95973</t>
+        </is>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>16.630402</t>
+        </is>
+      </c>
+      <c r="O927" t="inlineStr"/>
+      <c r="P927" t="inlineStr"/>
+      <c r="Q927" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R927" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S927" t="inlineStr"/>
+      <c r="T927" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U927" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V927" t="inlineStr"/>
+      <c r="W927" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011422_1</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>41011422_1</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011422</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:42</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:42</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:42</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:57:00</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:57:00</t>
+        </is>
+      </c>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>73158</t>
+        </is>
+      </c>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>46.978764</t>
+        </is>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>17.376492</t>
+        </is>
+      </c>
+      <c r="O928" t="inlineStr"/>
+      <c r="P928" t="inlineStr"/>
+      <c r="Q928" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R928" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S928" t="inlineStr"/>
+      <c r="T928" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U928" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V928" t="inlineStr"/>
+      <c r="W928" t="inlineStr"/>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011424_1</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>41011424_1</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011424</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:59:20</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:59:20</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:59:20</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:15:00</t>
+        </is>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:20:00</t>
+        </is>
+      </c>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>33115</t>
+        </is>
+      </c>
+      <c r="M929" t="inlineStr">
+        <is>
+          <t>47.591232</t>
+        </is>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>21.07782</t>
+        </is>
+      </c>
+      <c r="O929" t="inlineStr"/>
+      <c r="P929" t="inlineStr"/>
+      <c r="Q929" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R929" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S929" t="inlineStr"/>
+      <c r="T929" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U929" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V929" t="inlineStr"/>
+      <c r="W929" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011426_1</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>41011426_1</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011426</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:01:29</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:01:29</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:01:29</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:55:00</t>
+        </is>
+      </c>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:45:00</t>
+        </is>
+      </c>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>50422</t>
+        </is>
+      </c>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>47.396587</t>
+        </is>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>19.169134</t>
+        </is>
+      </c>
+      <c r="O930" t="inlineStr"/>
+      <c r="P930" t="inlineStr"/>
+      <c r="Q930" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R930" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S930" t="inlineStr"/>
+      <c r="T930" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U930" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V930" t="inlineStr"/>
+      <c r="W930" t="inlineStr"/>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011427_1</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>41011427_1</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011427</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:03:43</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:03:43</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:03:43</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:50:00</t>
+        </is>
+      </c>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:00:00</t>
+        </is>
+      </c>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M931" t="inlineStr">
+        <is>
+          <t>47.843204</t>
+        </is>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>21.341553</t>
+        </is>
+      </c>
+      <c r="O931" t="inlineStr"/>
+      <c r="P931" t="inlineStr"/>
+      <c r="Q931" t="inlineStr">
+        <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="R931" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S931" t="inlineStr"/>
+      <c r="T931" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U931" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V931" t="inlineStr"/>
+      <c r="W931" t="inlineStr"/>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011428_1</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>41011428_1</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011428</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:08:38</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:08:38</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:08:38</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:00:00</t>
+        </is>
+      </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:08:00</t>
+        </is>
+      </c>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>47.206055</t>
+        </is>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>19.959797</t>
+        </is>
+      </c>
+      <c r="O932" t="inlineStr"/>
+      <c r="P932" t="inlineStr"/>
+      <c r="Q932" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R932" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S932" t="inlineStr"/>
+      <c r="T932" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U932" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V932" t="inlineStr"/>
+      <c r="W932" t="inlineStr"/>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011429_1</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>41011429_1</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011429</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:09:10</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:09:10</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:09:10</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:05:00</t>
+        </is>
+      </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:10:00</t>
+        </is>
+      </c>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>86456</t>
+        </is>
+      </c>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>47.383102</t>
+        </is>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>16.970177</t>
+        </is>
+      </c>
+      <c r="O933" t="inlineStr"/>
+      <c r="P933" t="inlineStr"/>
+      <c r="Q933" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R933" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S933" t="inlineStr"/>
+      <c r="T933" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U933" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V933" t="inlineStr"/>
+      <c r="W933" t="inlineStr"/>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011430_1</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>41011430_1</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011430</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:13:41</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:13:41</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:13:41</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:15:00</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M934" t="inlineStr">
+        <is>
+          <t>47.706135</t>
+        </is>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>19.799934</t>
+        </is>
+      </c>
+      <c r="O934" t="inlineStr"/>
+      <c r="P934" t="inlineStr"/>
+      <c r="Q934" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="R934" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S934" t="inlineStr"/>
+      <c r="T934" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U934" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V934" t="inlineStr"/>
+      <c r="W934" t="inlineStr"/>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011431_1</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>41011431_1</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011431</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:16:16</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:16:16</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:16:16</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:15:00</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:00</t>
+        </is>
+      </c>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>46.91593</t>
+        </is>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>17.677555</t>
+        </is>
+      </c>
+      <c r="O935" t="inlineStr"/>
+      <c r="P935" t="inlineStr"/>
+      <c r="Q935" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R935" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S935" t="inlineStr"/>
+      <c r="T935" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U935" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V935" t="inlineStr"/>
+      <c r="W935" t="inlineStr"/>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011432_1</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>41011432_1</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011432</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>VehicleObstruction</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:17:01</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:17:01</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:17:01</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:10:00</t>
+        </is>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:15:00</t>
+        </is>
+      </c>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="M936" t="inlineStr">
+        <is>
+          <t>47.359566</t>
+        </is>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>19.216682</t>
+        </is>
+      </c>
+      <c r="O936" t="inlineStr"/>
+      <c r="P936" t="inlineStr"/>
+      <c r="Q936" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="R936" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S936" t="inlineStr"/>
+      <c r="T936" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U936" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V936" t="inlineStr"/>
+      <c r="W936" t="inlineStr"/>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011433_1</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>41011433_1</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011433</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:19:06</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:19:06</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:19:06</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:10:00</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:14:00</t>
+        </is>
+      </c>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>85482</t>
+        </is>
+      </c>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>47.71318</t>
+        </is>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>16.563683</t>
+        </is>
+      </c>
+      <c r="O937" t="inlineStr"/>
+      <c r="P937" t="inlineStr"/>
+      <c r="Q937" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
+      <c r="R937" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S937" t="inlineStr"/>
+      <c r="T937" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U937" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V937" t="inlineStr"/>
+      <c r="W937" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011434_1</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>41011434_1</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011434</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>PublicEvent</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:23:03</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:23:03</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:23:03</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>2026-04-26 07:00:00</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>2026-04-26 14:00:00</t>
+        </is>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="M938" t="inlineStr">
+        <is>
+          <t>47.37097</t>
+        </is>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>19.032455</t>
+        </is>
+      </c>
+      <c r="O938" t="inlineStr"/>
+      <c r="P938" t="inlineStr"/>
+      <c r="Q938" t="inlineStr">
+        <is>
+          <t>627.0</t>
+        </is>
+      </c>
+      <c r="R938" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S938" t="inlineStr"/>
+      <c r="T938" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U938" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V938" t="inlineStr"/>
+      <c r="W938" t="inlineStr"/>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011435_1</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>41011435_1</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011435</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:26:09</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:26:09</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:26:09</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:20:00</t>
+        </is>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:25:00</t>
+        </is>
+      </c>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="M939" t="inlineStr">
+        <is>
+          <t>46.95507</t>
+        </is>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>16.641903</t>
+        </is>
+      </c>
+      <c r="O939" t="inlineStr"/>
+      <c r="P939" t="inlineStr"/>
+      <c r="Q939" t="inlineStr">
+        <is>
+          <t>950.0</t>
+        </is>
+      </c>
+      <c r="R939" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S939" t="inlineStr"/>
+      <c r="T939" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U939" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V939" t="inlineStr"/>
+      <c r="W939" t="inlineStr"/>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011437_1</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>41011437_1</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011437</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:29:03</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:29:03</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:29:03</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:25:00</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:25:00</t>
+        </is>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>48.210575</t>
+        </is>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>20.91743</t>
+        </is>
+      </c>
+      <c r="O940" t="inlineStr"/>
+      <c r="P940" t="inlineStr"/>
+      <c r="Q940" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="R940" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S940" t="inlineStr"/>
+      <c r="T940" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U940" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V940" t="inlineStr"/>
+      <c r="W940" t="inlineStr"/>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011438_1</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>41011438_1</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011438</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:33:05</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:33:05</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:33:05</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:25:00</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>47.77875</t>
+        </is>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>20.589533</t>
+        </is>
+      </c>
+      <c r="O941" t="inlineStr"/>
+      <c r="P941" t="inlineStr"/>
+      <c r="Q941" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="R941" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S941" t="inlineStr"/>
+      <c r="T941" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U941" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V941" t="inlineStr"/>
+      <c r="W941" t="inlineStr"/>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011439_1</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>41011439_1</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011439</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:34:25</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:34:25</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:34:25</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:28:00</t>
+        </is>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="M942" t="inlineStr">
+        <is>
+          <t>46.09823</t>
+        </is>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>18.587269</t>
+        </is>
+      </c>
+      <c r="O942" t="inlineStr"/>
+      <c r="P942" t="inlineStr"/>
+      <c r="Q942" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="R942" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S942" t="inlineStr"/>
+      <c r="T942" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U942" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V942" t="inlineStr"/>
+      <c r="W942" t="inlineStr"/>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011440_1</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>41011440_1</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011440</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:35:16</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:35:16</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:35:16</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:30:00</t>
+        </is>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>47.801807</t>
+        </is>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>21.199131</t>
+        </is>
+      </c>
+      <c r="O943" t="inlineStr"/>
+      <c r="P943" t="inlineStr"/>
+      <c r="Q943" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R943" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S943" t="inlineStr"/>
+      <c r="T943" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U943" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V943" t="inlineStr"/>
+      <c r="W943" t="inlineStr"/>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011441_1</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>41011441_1</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011441</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:40:20</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:38:32</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:40:20</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:35:00</t>
+        </is>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:37:00</t>
+        </is>
+      </c>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="M944" t="inlineStr">
+        <is>
+          <t>47.456795</t>
+        </is>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>18.98054</t>
+        </is>
+      </c>
+      <c r="O944" t="inlineStr"/>
+      <c r="P944" t="inlineStr"/>
+      <c r="Q944" t="inlineStr">
+        <is>
+          <t>770.0</t>
+        </is>
+      </c>
+      <c r="R944" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S944" t="inlineStr"/>
+      <c r="T944" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U944" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V944" t="inlineStr"/>
+      <c r="W944" t="inlineStr"/>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011442_1</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>41011442_1</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011442</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>PublicEvent</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:42:15</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:42:15</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:42:15</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>2026-03-29 08:00:00</t>
+        </is>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>2026-03-29 16:00:00</t>
+        </is>
+      </c>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>12125</t>
+        </is>
+      </c>
+      <c r="M945" t="inlineStr">
+        <is>
+          <t>47.83605</t>
+        </is>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>18.833424</t>
+        </is>
+      </c>
+      <c r="O945" t="inlineStr"/>
+      <c r="P945" t="inlineStr"/>
+      <c r="Q945" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="R945" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S945" t="inlineStr"/>
+      <c r="T945" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U945" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V945" t="inlineStr"/>
+      <c r="W945" t="inlineStr"/>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011443_1</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>41011443_1</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011443</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:46:47</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:46:47</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:46:47</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:40:00</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:46:00</t>
+        </is>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M946" t="inlineStr">
+        <is>
+          <t>47.18352</t>
+        </is>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>20.362919</t>
+        </is>
+      </c>
+      <c r="O946" t="inlineStr"/>
+      <c r="P946" t="inlineStr"/>
+      <c r="Q946" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R946" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S946" t="inlineStr"/>
+      <c r="T946" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U946" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:53:49</t>
+        </is>
+      </c>
+      <c r="V946" t="inlineStr"/>
+      <c r="W946" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W946"/>
+  <dimension ref="A1:W957"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58164,7 +58164,7 @@
       <c r="S636" t="inlineStr"/>
       <c r="T636" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U636" t="inlineStr">
@@ -58172,7 +58172,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V636" t="inlineStr"/>
+      <c r="V636" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W636" t="inlineStr"/>
     </row>
     <row r="637">
@@ -61563,7 +61567,7 @@
       <c r="S671" t="inlineStr"/>
       <c r="T671" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U671" t="inlineStr">
@@ -61571,7 +61575,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V671" t="inlineStr"/>
+      <c r="V671" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W671" t="inlineStr"/>
     </row>
     <row r="672">
@@ -61951,7 +61959,7 @@
       <c r="S675" t="inlineStr"/>
       <c r="T675" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U675" t="inlineStr">
@@ -61959,7 +61967,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V675" t="inlineStr"/>
+      <c r="V675" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W675" t="inlineStr"/>
     </row>
     <row r="676">
@@ -66247,7 +66259,7 @@
       <c r="S719" t="inlineStr"/>
       <c r="T719" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U719" t="inlineStr">
@@ -66255,7 +66267,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V719" t="inlineStr"/>
+      <c r="V719" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W719" t="inlineStr"/>
     </row>
     <row r="720">
@@ -73089,7 +73105,7 @@
       <c r="S789" t="inlineStr"/>
       <c r="T789" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U789" t="inlineStr">
@@ -73097,7 +73113,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V789" t="inlineStr"/>
+      <c r="V789" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W789" t="inlineStr"/>
     </row>
     <row r="790">
@@ -74560,7 +74580,7 @@
       <c r="S804" t="inlineStr"/>
       <c r="T804" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U804" t="inlineStr">
@@ -74568,7 +74588,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V804" t="inlineStr"/>
+      <c r="V804" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W804" t="inlineStr"/>
     </row>
     <row r="805">
@@ -83091,7 +83115,7 @@
       <c r="S891" t="inlineStr"/>
       <c r="T891" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U891" t="inlineStr">
@@ -83099,7 +83123,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V891" t="inlineStr"/>
+      <c r="V891" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W891" t="inlineStr"/>
     </row>
     <row r="892">
@@ -83285,7 +83313,7 @@
       <c r="S893" t="inlineStr"/>
       <c r="T893" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U893" t="inlineStr">
@@ -83293,7 +83321,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V893" t="inlineStr"/>
+      <c r="V893" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W893" t="inlineStr"/>
     </row>
     <row r="894">
@@ -84376,7 +84408,7 @@
       <c r="S904" t="inlineStr"/>
       <c r="T904" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U904" t="inlineStr">
@@ -84384,7 +84416,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V904" t="inlineStr"/>
+      <c r="V904" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W904" t="inlineStr"/>
     </row>
     <row r="905">
@@ -84768,7 +84804,7 @@
       <c r="S908" t="inlineStr"/>
       <c r="T908" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U908" t="inlineStr">
@@ -84776,7 +84812,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V908" t="inlineStr"/>
+      <c r="V908" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W908" t="inlineStr"/>
     </row>
     <row r="909">
@@ -85156,7 +85196,7 @@
       <c r="S912" t="inlineStr"/>
       <c r="T912" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U912" t="inlineStr">
@@ -85164,7 +85204,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V912" t="inlineStr"/>
+      <c r="V912" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W912" t="inlineStr"/>
     </row>
     <row r="913">
@@ -85253,7 +85297,7 @@
       <c r="S913" t="inlineStr"/>
       <c r="T913" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U913" t="inlineStr">
@@ -85261,7 +85305,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V913" t="inlineStr"/>
+      <c r="V913" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W913" t="inlineStr"/>
     </row>
     <row r="914">
@@ -86623,7 +86671,7 @@
       <c r="S927" t="inlineStr"/>
       <c r="T927" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U927" t="inlineStr">
@@ -86631,7 +86679,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V927" t="inlineStr"/>
+      <c r="V927" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W927" t="inlineStr"/>
     </row>
     <row r="928">
@@ -86914,7 +86966,7 @@
       <c r="S930" t="inlineStr"/>
       <c r="T930" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U930" t="inlineStr">
@@ -86922,7 +86974,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V930" t="inlineStr"/>
+      <c r="V930" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W930" t="inlineStr"/>
     </row>
     <row r="931">
@@ -87205,7 +87261,7 @@
       <c r="S933" t="inlineStr"/>
       <c r="T933" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U933" t="inlineStr">
@@ -87213,7 +87269,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V933" t="inlineStr"/>
+      <c r="V933" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W933" t="inlineStr"/>
     </row>
     <row r="934">
@@ -87302,7 +87362,7 @@
       <c r="S934" t="inlineStr"/>
       <c r="T934" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U934" t="inlineStr">
@@ -87310,7 +87370,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V934" t="inlineStr"/>
+      <c r="V934" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W934" t="inlineStr"/>
     </row>
     <row r="935">
@@ -87496,7 +87560,7 @@
       <c r="S936" t="inlineStr"/>
       <c r="T936" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U936" t="inlineStr">
@@ -87504,7 +87568,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V936" t="inlineStr"/>
+      <c r="V936" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W936" t="inlineStr"/>
     </row>
     <row r="937">
@@ -87787,7 +87855,7 @@
       <c r="S939" t="inlineStr"/>
       <c r="T939" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U939" t="inlineStr">
@@ -87795,7 +87863,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V939" t="inlineStr"/>
+      <c r="V939" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W939" t="inlineStr"/>
     </row>
     <row r="940">
@@ -87884,7 +87956,7 @@
       <c r="S940" t="inlineStr"/>
       <c r="T940" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U940" t="inlineStr">
@@ -87892,7 +87964,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V940" t="inlineStr"/>
+      <c r="V940" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
       <c r="W940" t="inlineStr"/>
     </row>
     <row r="941">
@@ -88476,6 +88552,1073 @@
       </c>
       <c r="V946" t="inlineStr"/>
       <c r="W946" t="inlineStr"/>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011444_1</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>41011444_1</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011444</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:47:13</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:47:13</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:47:13</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:45:00</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:45:00</t>
+        </is>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="M947" t="inlineStr">
+        <is>
+          <t>48.42278</t>
+        </is>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>21.17978</t>
+        </is>
+      </c>
+      <c r="O947" t="inlineStr"/>
+      <c r="P947" t="inlineStr"/>
+      <c r="Q947" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R947" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S947" t="inlineStr"/>
+      <c r="T947" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U947" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
+      <c r="V947" t="inlineStr"/>
+      <c r="W947" t="inlineStr"/>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011445_1</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>41011445_1</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011445</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>PublicEvent</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:48:11</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:48:11</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>2026-03-05 11:48:11</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>2026-03-29 08:00:00</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>2026-03-29 16:00:00</t>
+        </is>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>97821</t>
+        </is>
+      </c>
+      <c r="M948" t="inlineStr">
+        <is>
+          <t>47.834938</t>
+        </is>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>18.831348</t>
+        </is>
+      </c>
+      <c r="O948" t="inlineStr"/>
+      <c r="P948" t="inlineStr"/>
+      <c r="Q948" t="inlineStr">
+        <is>
+          <t>206.0</t>
+        </is>
+      </c>
+      <c r="R948" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="S948" t="inlineStr"/>
+      <c r="T948" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U948" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
+      <c r="V948" t="inlineStr"/>
+      <c r="W948" t="inlineStr"/>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011446_1</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>41011446_1</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011446</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:00:29</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:00:29</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:00:29</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:00:00</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:00</t>
+        </is>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M949" t="inlineStr">
+        <is>
+          <t>47.706135</t>
+        </is>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>19.799934</t>
+        </is>
+      </c>
+      <c r="O949" t="inlineStr"/>
+      <c r="P949" t="inlineStr"/>
+      <c r="Q949" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="R949" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S949" t="inlineStr"/>
+      <c r="T949" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U949" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
+      <c r="V949" t="inlineStr"/>
+      <c r="W949" t="inlineStr"/>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011447_1</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>41011447_1</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011447</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:03:04</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:02:38</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:03:04</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:00:00</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="M950" t="inlineStr">
+        <is>
+          <t>47.338707</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>18.785765</t>
+        </is>
+      </c>
+      <c r="O950" t="inlineStr"/>
+      <c r="P950" t="inlineStr"/>
+      <c r="Q950" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R950" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S950" t="inlineStr"/>
+      <c r="T950" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U950" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
+      <c r="V950" t="inlineStr"/>
+      <c r="W950" t="inlineStr"/>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011448_1</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>41011448_1</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011448</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:05:16</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:04:23</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:05:16</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:01:00</t>
+        </is>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:01:00</t>
+        </is>
+      </c>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="M951" t="inlineStr">
+        <is>
+          <t>47.869724</t>
+        </is>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>19.001623</t>
+        </is>
+      </c>
+      <c r="O951" t="inlineStr"/>
+      <c r="P951" t="inlineStr"/>
+      <c r="Q951" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R951" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S951" t="inlineStr"/>
+      <c r="T951" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U951" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
+      <c r="V951" t="inlineStr"/>
+      <c r="W951" t="inlineStr"/>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011449_1</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>41011449_1</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011449</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:06:11</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:05:18</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:06:11</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:05:00</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>90860</t>
+        </is>
+      </c>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>47.57337</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>19.159061</t>
+        </is>
+      </c>
+      <c r="O952" t="inlineStr"/>
+      <c r="P952" t="inlineStr"/>
+      <c r="Q952" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="R952" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S952" t="inlineStr"/>
+      <c r="T952" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U952" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
+      <c r="V952" t="inlineStr"/>
+      <c r="W952" t="inlineStr"/>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011450_1</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>41011450_1</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011450</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:14:55</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:14:55</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:14:55</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:15:00</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>46.86807</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>18.981007</t>
+        </is>
+      </c>
+      <c r="O953" t="inlineStr"/>
+      <c r="P953" t="inlineStr"/>
+      <c r="Q953" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="R953" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S953" t="inlineStr"/>
+      <c r="T953" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U953" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
+      <c r="V953" t="inlineStr"/>
+      <c r="W953" t="inlineStr"/>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011451_1</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>41011451_1</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011451</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:27:43</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:27:43</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:27:43</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>2026-03-17 08:00:00</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>2026-03-20 16:00:00</t>
+        </is>
+      </c>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>4809</t>
+        </is>
+      </c>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>47.388634</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>21.77359</t>
+        </is>
+      </c>
+      <c r="O954" t="inlineStr"/>
+      <c r="P954" t="inlineStr"/>
+      <c r="Q954" t="inlineStr">
+        <is>
+          <t>795.0</t>
+        </is>
+      </c>
+      <c r="R954" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S954" t="inlineStr"/>
+      <c r="T954" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U954" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
+      <c r="V954" t="inlineStr"/>
+      <c r="W954" t="inlineStr"/>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011452_1</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>41011452_1</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011452</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:29:39</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:29:39</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:29:39</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>2026-03-17 08:00:00</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>2026-03-20 16:00:00</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>48105</t>
+        </is>
+      </c>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>47.391388</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>21.772747</t>
+        </is>
+      </c>
+      <c r="O955" t="inlineStr"/>
+      <c r="P955" t="inlineStr"/>
+      <c r="Q955" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
+      </c>
+      <c r="R955" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S955" t="inlineStr"/>
+      <c r="T955" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U955" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
+      <c r="V955" t="inlineStr"/>
+      <c r="W955" t="inlineStr"/>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011453_1</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>41011453_1</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011453</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:29:44</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:29:44</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:29:44</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:25:00</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:28:00</t>
+        </is>
+      </c>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>47.41864</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>18.951082</t>
+        </is>
+      </c>
+      <c r="O956" t="inlineStr"/>
+      <c r="P956" t="inlineStr"/>
+      <c r="Q956" t="inlineStr">
+        <is>
+          <t>450.0</t>
+        </is>
+      </c>
+      <c r="R956" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S956" t="inlineStr"/>
+      <c r="T956" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U956" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
+      <c r="V956" t="inlineStr"/>
+      <c r="W956" t="inlineStr"/>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011454_1</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>41011454_1</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011454</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:31:42</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:31:42</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:31:42</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:00:00</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>2026-03-12 16:00:00</t>
+        </is>
+      </c>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>47.685825</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>21.894484</t>
+        </is>
+      </c>
+      <c r="O957" t="inlineStr"/>
+      <c r="P957" t="inlineStr"/>
+      <c r="Q957" t="inlineStr">
+        <is>
+          <t>867.0</t>
+        </is>
+      </c>
+      <c r="R957" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S957" t="inlineStr"/>
+      <c r="T957" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U957" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:34:44</t>
+        </is>
+      </c>
+      <c r="V957" t="inlineStr"/>
+      <c r="W957" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W957"/>
+  <dimension ref="A1:W964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32084,7 +32084,7 @@
       <c r="S354" t="inlineStr"/>
       <c r="T354" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U354" t="inlineStr">
@@ -32092,7 +32092,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V354" t="inlineStr"/>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
       <c r="W354" t="inlineStr"/>
     </row>
     <row r="355">
@@ -45532,7 +45536,7 @@
       <c r="S504" t="inlineStr"/>
       <c r="T504" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U504" t="inlineStr">
@@ -45540,7 +45544,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V504" t="inlineStr"/>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
       <c r="W504" t="inlineStr"/>
     </row>
     <row r="505">
@@ -50542,7 +50550,7 @@
       <c r="S558" t="inlineStr"/>
       <c r="T558" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U558" t="inlineStr">
@@ -50550,7 +50558,11 @@
           <t>2026-03-04 19:55:12</t>
         </is>
       </c>
-      <c r="V558" t="inlineStr"/>
+      <c r="V558" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
       <c r="W558" t="inlineStr"/>
     </row>
     <row r="559">
@@ -54959,7 +54971,7 @@
       <c r="S603" t="inlineStr"/>
       <c r="T603" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U603" t="inlineStr">
@@ -54967,7 +54979,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V603" t="inlineStr"/>
+      <c r="V603" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
       <c r="W603" t="inlineStr"/>
     </row>
     <row r="604">
@@ -81535,7 +81551,7 @@
       <c r="S875" t="inlineStr"/>
       <c r="T875" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U875" t="inlineStr">
@@ -81543,7 +81559,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V875" t="inlineStr"/>
+      <c r="V875" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
       <c r="W875" t="inlineStr"/>
     </row>
     <row r="876">
@@ -81826,7 +81846,7 @@
       <c r="S878" t="inlineStr"/>
       <c r="T878" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U878" t="inlineStr">
@@ -81834,7 +81854,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V878" t="inlineStr"/>
+      <c r="V878" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
       <c r="W878" t="inlineStr"/>
     </row>
     <row r="879">
@@ -84509,7 +84533,7 @@
       <c r="S905" t="inlineStr"/>
       <c r="T905" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U905" t="inlineStr">
@@ -84517,7 +84541,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V905" t="inlineStr"/>
+      <c r="V905" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
       <c r="W905" t="inlineStr"/>
     </row>
     <row r="906">
@@ -86772,7 +86800,7 @@
       <c r="S928" t="inlineStr"/>
       <c r="T928" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U928" t="inlineStr">
@@ -86780,7 +86808,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V928" t="inlineStr"/>
+      <c r="V928" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
       <c r="W928" t="inlineStr"/>
     </row>
     <row r="929">
@@ -87463,7 +87495,7 @@
       <c r="S935" t="inlineStr"/>
       <c r="T935" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U935" t="inlineStr">
@@ -87471,7 +87503,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V935" t="inlineStr"/>
+      <c r="V935" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
       <c r="W935" t="inlineStr"/>
     </row>
     <row r="936">
@@ -88833,7 +88869,7 @@
       <c r="S949" t="inlineStr"/>
       <c r="T949" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U949" t="inlineStr">
@@ -88841,7 +88877,11 @@
           <t>2026-03-05 12:34:44</t>
         </is>
       </c>
-      <c r="V949" t="inlineStr"/>
+      <c r="V949" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
       <c r="W949" t="inlineStr"/>
     </row>
     <row r="950">
@@ -89619,6 +89659,685 @@
       </c>
       <c r="V957" t="inlineStr"/>
       <c r="W957" t="inlineStr"/>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011456_1</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>41011456_1</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011456</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:45:08</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:45:08</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:45:08</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:45:00</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>47.879044</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>20.825638</t>
+        </is>
+      </c>
+      <c r="O958" t="inlineStr"/>
+      <c r="P958" t="inlineStr"/>
+      <c r="Q958" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R958" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S958" t="inlineStr"/>
+      <c r="T958" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U958" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
+      <c r="V958" t="inlineStr"/>
+      <c r="W958" t="inlineStr"/>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011457_1</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>41011457_1</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011457</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:46:22</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:46:22</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:46:22</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:45:00</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:45:00</t>
+        </is>
+      </c>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>47.707424</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>19.807695</t>
+        </is>
+      </c>
+      <c r="O959" t="inlineStr"/>
+      <c r="P959" t="inlineStr"/>
+      <c r="Q959" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R959" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S959" t="inlineStr"/>
+      <c r="T959" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U959" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
+      <c r="V959" t="inlineStr"/>
+      <c r="W959" t="inlineStr"/>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011458_1</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>41011458_1</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011458</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:50:29</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:50:29</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:50:29</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:50:00</t>
+        </is>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:50:00</t>
+        </is>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>66163</t>
+        </is>
+      </c>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>46.35659</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>17.647116</t>
+        </is>
+      </c>
+      <c r="O960" t="inlineStr"/>
+      <c r="P960" t="inlineStr"/>
+      <c r="Q960" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R960" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S960" t="inlineStr"/>
+      <c r="T960" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U960" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
+      <c r="V960" t="inlineStr"/>
+      <c r="W960" t="inlineStr"/>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011459_1</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>41011459_1</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011459</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:51:48</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:51:48</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:51:48</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:55:00</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:50:00</t>
+        </is>
+      </c>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>66168</t>
+        </is>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>46.300144</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>17.652044</t>
+        </is>
+      </c>
+      <c r="O961" t="inlineStr"/>
+      <c r="P961" t="inlineStr"/>
+      <c r="Q961" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R961" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S961" t="inlineStr"/>
+      <c r="T961" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U961" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
+      <c r="V961" t="inlineStr"/>
+      <c r="W961" t="inlineStr"/>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011460_1</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>41011460_1</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011460</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:56:04</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:56:04</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:56:04</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:40:00</t>
+        </is>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:30:00</t>
+        </is>
+      </c>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>47.83045</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>17.276243</t>
+        </is>
+      </c>
+      <c r="O962" t="inlineStr"/>
+      <c r="P962" t="inlineStr"/>
+      <c r="Q962" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R962" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S962" t="inlineStr"/>
+      <c r="T962" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U962" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
+      <c r="V962" t="inlineStr"/>
+      <c r="W962" t="inlineStr"/>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011461_1</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>41011461_1</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011461</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>VehicleObstruction</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:57:55</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:57:55</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:57:55</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:55:00</t>
+        </is>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>2026-03-06 12:55:00</t>
+        </is>
+      </c>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="M963" t="inlineStr">
+        <is>
+          <t>47.607056</t>
+        </is>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>19.197678</t>
+        </is>
+      </c>
+      <c r="O963" t="inlineStr"/>
+      <c r="P963" t="inlineStr"/>
+      <c r="Q963" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="R963" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S963" t="inlineStr"/>
+      <c r="T963" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U963" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
+      <c r="V963" t="inlineStr"/>
+      <c r="W963" t="inlineStr"/>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011462_1</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>41011462_1</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011462</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:58:27</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:58:27</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:58:27</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:40:00</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:37:00</t>
+        </is>
+      </c>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>M85</t>
+        </is>
+      </c>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>47.611263</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>16.665451</t>
+        </is>
+      </c>
+      <c r="O964" t="inlineStr"/>
+      <c r="P964" t="inlineStr"/>
+      <c r="Q964" t="inlineStr">
+        <is>
+          <t>650.0</t>
+        </is>
+      </c>
+      <c r="R964" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S964" t="inlineStr"/>
+      <c r="T964" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U964" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
+      <c r="V964" t="inlineStr"/>
+      <c r="W964" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W964"/>
+  <dimension ref="A1:W980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4988,7 +4988,7 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -4996,7 +4996,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -24674,7 +24678,7 @@
       <c r="S272" t="inlineStr"/>
       <c r="T272" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U272" t="inlineStr">
@@ -24682,7 +24686,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V272" t="inlineStr"/>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W272" t="inlineStr"/>
     </row>
     <row r="273">
@@ -52332,7 +52340,7 @@
       <c r="S576" t="inlineStr"/>
       <c r="T576" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U576" t="inlineStr">
@@ -52340,7 +52348,11 @@
           <t>2026-03-05 05:30:24</t>
         </is>
       </c>
-      <c r="V576" t="inlineStr"/>
+      <c r="V576" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W576" t="inlineStr"/>
     </row>
     <row r="577">
@@ -53108,7 +53120,7 @@
       <c r="S584" t="inlineStr"/>
       <c r="T584" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U584" t="inlineStr">
@@ -53116,7 +53128,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V584" t="inlineStr"/>
+      <c r="V584" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W584" t="inlineStr"/>
     </row>
     <row r="585">
@@ -53205,7 +53221,7 @@
       <c r="S585" t="inlineStr"/>
       <c r="T585" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U585" t="inlineStr">
@@ -53213,7 +53229,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V585" t="inlineStr"/>
+      <c r="V585" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W585" t="inlineStr"/>
     </row>
     <row r="586">
@@ -53403,7 +53423,7 @@
       <c r="S587" t="inlineStr"/>
       <c r="T587" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U587" t="inlineStr">
@@ -53411,7 +53431,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V587" t="inlineStr"/>
+      <c r="V587" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W587" t="inlineStr"/>
     </row>
     <row r="588">
@@ -53601,7 +53625,7 @@
       <c r="S589" t="inlineStr"/>
       <c r="T589" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U589" t="inlineStr">
@@ -53609,7 +53633,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V589" t="inlineStr"/>
+      <c r="V589" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W589" t="inlineStr"/>
     </row>
     <row r="590">
@@ -53698,7 +53726,7 @@
       <c r="S590" t="inlineStr"/>
       <c r="T590" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U590" t="inlineStr">
@@ -53706,7 +53734,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V590" t="inlineStr"/>
+      <c r="V590" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W590" t="inlineStr"/>
     </row>
     <row r="591">
@@ -53795,7 +53827,7 @@
       <c r="S591" t="inlineStr"/>
       <c r="T591" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U591" t="inlineStr">
@@ -53803,7 +53835,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V591" t="inlineStr"/>
+      <c r="V591" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W591" t="inlineStr"/>
     </row>
     <row r="592">
@@ -55072,7 +55108,7 @@
       <c r="S604" t="inlineStr"/>
       <c r="T604" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U604" t="inlineStr">
@@ -55080,7 +55116,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V604" t="inlineStr"/>
+      <c r="V604" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W604" t="inlineStr"/>
     </row>
     <row r="605">
@@ -55460,7 +55500,7 @@
       <c r="S608" t="inlineStr"/>
       <c r="T608" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U608" t="inlineStr">
@@ -55468,7 +55508,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V608" t="inlineStr"/>
+      <c r="V608" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W608" t="inlineStr"/>
     </row>
     <row r="609">
@@ -55658,7 +55702,7 @@
       <c r="S610" t="inlineStr"/>
       <c r="T610" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U610" t="inlineStr">
@@ -55666,7 +55710,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V610" t="inlineStr"/>
+      <c r="V610" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W610" t="inlineStr"/>
     </row>
     <row r="611">
@@ -55852,7 +55900,7 @@
       <c r="S612" t="inlineStr"/>
       <c r="T612" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U612" t="inlineStr">
@@ -55860,7 +55908,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V612" t="inlineStr"/>
+      <c r="V612" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W612" t="inlineStr"/>
     </row>
     <row r="613">
@@ -56143,7 +56195,7 @@
       <c r="S615" t="inlineStr"/>
       <c r="T615" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U615" t="inlineStr">
@@ -56151,7 +56203,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V615" t="inlineStr"/>
+      <c r="V615" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W615" t="inlineStr"/>
     </row>
     <row r="616">
@@ -56434,7 +56490,7 @@
       <c r="S618" t="inlineStr"/>
       <c r="T618" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U618" t="inlineStr">
@@ -56442,7 +56498,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V618" t="inlineStr"/>
+      <c r="V618" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W618" t="inlineStr"/>
     </row>
     <row r="619">
@@ -56725,7 +56785,7 @@
       <c r="S621" t="inlineStr"/>
       <c r="T621" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U621" t="inlineStr">
@@ -56733,7 +56793,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V621" t="inlineStr"/>
+      <c r="V621" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W621" t="inlineStr"/>
     </row>
     <row r="622">
@@ -57404,7 +57468,7 @@
       <c r="S628" t="inlineStr"/>
       <c r="T628" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U628" t="inlineStr">
@@ -57412,7 +57476,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V628" t="inlineStr"/>
+      <c r="V628" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W628" t="inlineStr"/>
     </row>
     <row r="629">
@@ -64909,7 +64977,7 @@
       <c r="S705" t="inlineStr"/>
       <c r="T705" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U705" t="inlineStr">
@@ -64917,7 +64985,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V705" t="inlineStr"/>
+      <c r="V705" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W705" t="inlineStr"/>
     </row>
     <row r="706">
@@ -65204,7 +65276,7 @@
       <c r="S708" t="inlineStr"/>
       <c r="T708" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U708" t="inlineStr">
@@ -65212,7 +65284,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V708" t="inlineStr"/>
+      <c r="V708" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W708" t="inlineStr"/>
     </row>
     <row r="709">
@@ -65689,7 +65765,7 @@
       <c r="S713" t="inlineStr"/>
       <c r="T713" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U713" t="inlineStr">
@@ -65697,7 +65773,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V713" t="inlineStr"/>
+      <c r="V713" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W713" t="inlineStr"/>
     </row>
     <row r="714">
@@ -66081,7 +66161,7 @@
       <c r="S717" t="inlineStr"/>
       <c r="T717" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U717" t="inlineStr">
@@ -66089,7 +66169,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V717" t="inlineStr"/>
+      <c r="V717" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W717" t="inlineStr"/>
     </row>
     <row r="718">
@@ -66178,7 +66262,7 @@
       <c r="S718" t="inlineStr"/>
       <c r="T718" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U718" t="inlineStr">
@@ -66186,7 +66270,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V718" t="inlineStr"/>
+      <c r="V718" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W718" t="inlineStr"/>
     </row>
     <row r="719">
@@ -66376,7 +66464,7 @@
       <c r="S720" t="inlineStr"/>
       <c r="T720" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U720" t="inlineStr">
@@ -66384,7 +66472,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V720" t="inlineStr"/>
+      <c r="V720" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W720" t="inlineStr"/>
     </row>
     <row r="721">
@@ -66768,7 +66860,7 @@
       <c r="S724" t="inlineStr"/>
       <c r="T724" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U724" t="inlineStr">
@@ -66776,7 +66868,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V724" t="inlineStr"/>
+      <c r="V724" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W724" t="inlineStr"/>
     </row>
     <row r="725">
@@ -67257,7 +67353,7 @@
       <c r="S729" t="inlineStr"/>
       <c r="T729" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U729" t="inlineStr">
@@ -67265,7 +67361,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V729" t="inlineStr"/>
+      <c r="V729" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W729" t="inlineStr"/>
     </row>
     <row r="730">
@@ -68914,7 +69014,7 @@
       <c r="S746" t="inlineStr"/>
       <c r="T746" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U746" t="inlineStr">
@@ -68922,7 +69022,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V746" t="inlineStr"/>
+      <c r="V746" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W746" t="inlineStr"/>
     </row>
     <row r="747">
@@ -69209,7 +69313,7 @@
       <c r="S749" t="inlineStr"/>
       <c r="T749" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U749" t="inlineStr">
@@ -69217,7 +69321,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V749" t="inlineStr"/>
+      <c r="V749" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W749" t="inlineStr"/>
     </row>
     <row r="750">
@@ -69504,7 +69612,7 @@
       <c r="S752" t="inlineStr"/>
       <c r="T752" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U752" t="inlineStr">
@@ -69512,7 +69620,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V752" t="inlineStr"/>
+      <c r="V752" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W752" t="inlineStr"/>
     </row>
     <row r="753">
@@ -70187,7 +70299,7 @@
       <c r="S759" t="inlineStr"/>
       <c r="T759" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U759" t="inlineStr">
@@ -70195,7 +70307,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V759" t="inlineStr"/>
+      <c r="V759" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W759" t="inlineStr"/>
     </row>
     <row r="760">
@@ -70284,7 +70400,7 @@
       <c r="S760" t="inlineStr"/>
       <c r="T760" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U760" t="inlineStr">
@@ -70292,7 +70408,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V760" t="inlineStr"/>
+      <c r="V760" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W760" t="inlineStr"/>
     </row>
     <row r="761">
@@ -70381,7 +70501,7 @@
       <c r="S761" t="inlineStr"/>
       <c r="T761" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U761" t="inlineStr">
@@ -70389,7 +70509,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V761" t="inlineStr"/>
+      <c r="V761" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W761" t="inlineStr"/>
     </row>
     <row r="762">
@@ -70478,7 +70602,7 @@
       <c r="S762" t="inlineStr"/>
       <c r="T762" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U762" t="inlineStr">
@@ -70486,7 +70610,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V762" t="inlineStr"/>
+      <c r="V762" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W762" t="inlineStr"/>
     </row>
     <row r="763">
@@ -70575,7 +70703,7 @@
       <c r="S763" t="inlineStr"/>
       <c r="T763" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U763" t="inlineStr">
@@ -70583,7 +70711,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V763" t="inlineStr"/>
+      <c r="V763" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W763" t="inlineStr"/>
     </row>
     <row r="764">
@@ -70672,7 +70804,7 @@
       <c r="S764" t="inlineStr"/>
       <c r="T764" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U764" t="inlineStr">
@@ -70680,7 +70812,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V764" t="inlineStr"/>
+      <c r="V764" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W764" t="inlineStr"/>
     </row>
     <row r="765">
@@ -71258,7 +71394,7 @@
       <c r="S770" t="inlineStr"/>
       <c r="T770" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U770" t="inlineStr">
@@ -71266,7 +71402,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V770" t="inlineStr"/>
+      <c r="V770" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W770" t="inlineStr"/>
     </row>
     <row r="771">
@@ -71355,7 +71495,7 @@
       <c r="S771" t="inlineStr"/>
       <c r="T771" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U771" t="inlineStr">
@@ -71363,7 +71503,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V771" t="inlineStr"/>
+      <c r="V771" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W771" t="inlineStr"/>
     </row>
     <row r="772">
@@ -71743,7 +71887,7 @@
       <c r="S775" t="inlineStr"/>
       <c r="T775" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U775" t="inlineStr">
@@ -71751,7 +71895,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V775" t="inlineStr"/>
+      <c r="V775" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W775" t="inlineStr"/>
     </row>
     <row r="776">
@@ -72139,7 +72287,7 @@
       <c r="S779" t="inlineStr"/>
       <c r="T779" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U779" t="inlineStr">
@@ -72147,7 +72295,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V779" t="inlineStr"/>
+      <c r="V779" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W779" t="inlineStr"/>
     </row>
     <row r="780">
@@ -72333,7 +72485,7 @@
       <c r="S781" t="inlineStr"/>
       <c r="T781" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U781" t="inlineStr">
@@ -72341,7 +72493,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V781" t="inlineStr"/>
+      <c r="V781" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W781" t="inlineStr"/>
     </row>
     <row r="782">
@@ -72430,7 +72586,7 @@
       <c r="S782" t="inlineStr"/>
       <c r="T782" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U782" t="inlineStr">
@@ -72438,7 +72594,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V782" t="inlineStr"/>
+      <c r="V782" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W782" t="inlineStr"/>
     </row>
     <row r="783">
@@ -72527,7 +72687,7 @@
       <c r="S783" t="inlineStr"/>
       <c r="T783" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U783" t="inlineStr">
@@ -72535,7 +72695,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V783" t="inlineStr"/>
+      <c r="V783" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W783" t="inlineStr"/>
     </row>
     <row r="784">
@@ -72826,7 +72990,7 @@
       <c r="S786" t="inlineStr"/>
       <c r="T786" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U786" t="inlineStr">
@@ -72834,7 +72998,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V786" t="inlineStr"/>
+      <c r="V786" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W786" t="inlineStr"/>
     </row>
     <row r="787">
@@ -73323,7 +73491,7 @@
       <c r="S791" t="inlineStr"/>
       <c r="T791" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U791" t="inlineStr">
@@ -73331,7 +73499,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V791" t="inlineStr"/>
+      <c r="V791" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W791" t="inlineStr"/>
     </row>
     <row r="792">
@@ -73820,7 +73992,7 @@
       <c r="S796" t="inlineStr"/>
       <c r="T796" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U796" t="inlineStr">
@@ -73828,7 +74000,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V796" t="inlineStr"/>
+      <c r="V796" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W796" t="inlineStr"/>
     </row>
     <row r="797">
@@ -74014,7 +74190,7 @@
       <c r="S798" t="inlineStr"/>
       <c r="T798" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U798" t="inlineStr">
@@ -74022,7 +74198,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V798" t="inlineStr"/>
+      <c r="V798" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W798" t="inlineStr"/>
     </row>
     <row r="799">
@@ -74697,7 +74877,7 @@
       <c r="S805" t="inlineStr"/>
       <c r="T805" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U805" t="inlineStr">
@@ -74705,7 +74885,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V805" t="inlineStr"/>
+      <c r="V805" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W805" t="inlineStr"/>
     </row>
     <row r="806">
@@ -74794,7 +74978,7 @@
       <c r="S806" t="inlineStr"/>
       <c r="T806" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U806" t="inlineStr">
@@ -74802,7 +74986,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V806" t="inlineStr"/>
+      <c r="V806" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W806" t="inlineStr"/>
     </row>
     <row r="807">
@@ -75283,7 +75471,7 @@
       <c r="S811" t="inlineStr"/>
       <c r="T811" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U811" t="inlineStr">
@@ -75291,7 +75479,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V811" t="inlineStr"/>
+      <c r="V811" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W811" t="inlineStr"/>
     </row>
     <row r="812">
@@ -75865,7 +76057,7 @@
       <c r="S817" t="inlineStr"/>
       <c r="T817" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U817" t="inlineStr">
@@ -75873,7 +76065,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V817" t="inlineStr"/>
+      <c r="V817" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W817" t="inlineStr"/>
     </row>
     <row r="818">
@@ -75962,7 +76158,7 @@
       <c r="S818" t="inlineStr"/>
       <c r="T818" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U818" t="inlineStr">
@@ -75970,7 +76166,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V818" t="inlineStr"/>
+      <c r="V818" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W818" t="inlineStr"/>
     </row>
     <row r="819">
@@ -76059,7 +76259,7 @@
       <c r="S819" t="inlineStr"/>
       <c r="T819" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U819" t="inlineStr">
@@ -76067,7 +76267,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V819" t="inlineStr"/>
+      <c r="V819" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W819" t="inlineStr"/>
     </row>
     <row r="820">
@@ -76156,7 +76360,7 @@
       <c r="S820" t="inlineStr"/>
       <c r="T820" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U820" t="inlineStr">
@@ -76164,7 +76368,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V820" t="inlineStr"/>
+      <c r="V820" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W820" t="inlineStr"/>
     </row>
     <row r="821">
@@ -76350,7 +76558,7 @@
       <c r="S822" t="inlineStr"/>
       <c r="T822" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U822" t="inlineStr">
@@ -76358,7 +76566,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V822" t="inlineStr"/>
+      <c r="V822" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W822" t="inlineStr"/>
     </row>
     <row r="823">
@@ -76738,7 +76950,7 @@
       <c r="S826" t="inlineStr"/>
       <c r="T826" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U826" t="inlineStr">
@@ -76746,7 +76958,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V826" t="inlineStr"/>
+      <c r="V826" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W826" t="inlineStr"/>
     </row>
     <row r="827">
@@ -76932,7 +77148,7 @@
       <c r="S828" t="inlineStr"/>
       <c r="T828" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U828" t="inlineStr">
@@ -76940,7 +77156,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V828" t="inlineStr"/>
+      <c r="V828" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W828" t="inlineStr"/>
     </row>
     <row r="829">
@@ -77914,7 +78134,7 @@
       <c r="S838" t="inlineStr"/>
       <c r="T838" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U838" t="inlineStr">
@@ -77922,7 +78142,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V838" t="inlineStr"/>
+      <c r="V838" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W838" t="inlineStr"/>
     </row>
     <row r="839">
@@ -78213,7 +78437,7 @@
       <c r="S841" t="inlineStr"/>
       <c r="T841" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U841" t="inlineStr">
@@ -78221,7 +78445,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V841" t="inlineStr"/>
+      <c r="V841" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W841" t="inlineStr"/>
     </row>
     <row r="842">
@@ -78310,7 +78538,7 @@
       <c r="S842" t="inlineStr"/>
       <c r="T842" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U842" t="inlineStr">
@@ -78318,7 +78546,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V842" t="inlineStr"/>
+      <c r="V842" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W842" t="inlineStr"/>
     </row>
     <row r="843">
@@ -78508,7 +78740,7 @@
       <c r="S844" t="inlineStr"/>
       <c r="T844" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U844" t="inlineStr">
@@ -78516,7 +78748,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V844" t="inlineStr"/>
+      <c r="V844" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W844" t="inlineStr"/>
     </row>
     <row r="845">
@@ -78706,7 +78942,7 @@
       <c r="S846" t="inlineStr"/>
       <c r="T846" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U846" t="inlineStr">
@@ -78714,7 +78950,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V846" t="inlineStr"/>
+      <c r="V846" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W846" t="inlineStr"/>
     </row>
     <row r="847">
@@ -78803,7 +79043,7 @@
       <c r="S847" t="inlineStr"/>
       <c r="T847" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U847" t="inlineStr">
@@ -78811,7 +79051,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V847" t="inlineStr"/>
+      <c r="V847" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W847" t="inlineStr"/>
     </row>
     <row r="848">
@@ -79098,7 +79342,7 @@
       <c r="S850" t="inlineStr"/>
       <c r="T850" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U850" t="inlineStr">
@@ -79106,7 +79350,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V850" t="inlineStr"/>
+      <c r="V850" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W850" t="inlineStr"/>
     </row>
     <row r="851">
@@ -79195,7 +79443,7 @@
       <c r="S851" t="inlineStr"/>
       <c r="T851" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U851" t="inlineStr">
@@ -79203,7 +79451,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V851" t="inlineStr"/>
+      <c r="V851" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W851" t="inlineStr"/>
     </row>
     <row r="852">
@@ -79486,7 +79738,7 @@
       <c r="S854" t="inlineStr"/>
       <c r="T854" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U854" t="inlineStr">
@@ -79494,7 +79746,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V854" t="inlineStr"/>
+      <c r="V854" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W854" t="inlineStr"/>
     </row>
     <row r="855">
@@ -79781,7 +80037,7 @@
       <c r="S857" t="inlineStr"/>
       <c r="T857" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U857" t="inlineStr">
@@ -79789,7 +80045,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V857" t="inlineStr"/>
+      <c r="V857" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W857" t="inlineStr"/>
     </row>
     <row r="858">
@@ -80670,7 +80930,7 @@
       <c r="S866" t="inlineStr"/>
       <c r="T866" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U866" t="inlineStr">
@@ -80678,7 +80938,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V866" t="inlineStr"/>
+      <c r="V866" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W866" t="inlineStr"/>
     </row>
     <row r="867">
@@ -81163,7 +81427,7 @@
       <c r="S871" t="inlineStr"/>
       <c r="T871" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U871" t="inlineStr">
@@ -81171,7 +81435,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V871" t="inlineStr"/>
+      <c r="V871" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W871" t="inlineStr"/>
     </row>
     <row r="872">
@@ -81454,7 +81722,7 @@
       <c r="S874" t="inlineStr"/>
       <c r="T874" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U874" t="inlineStr">
@@ -81462,7 +81730,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V874" t="inlineStr"/>
+      <c r="V874" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W874" t="inlineStr"/>
     </row>
     <row r="875">
@@ -81749,7 +82021,7 @@
       <c r="S877" t="inlineStr"/>
       <c r="T877" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U877" t="inlineStr">
@@ -81757,7 +82029,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V877" t="inlineStr"/>
+      <c r="V877" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W877" t="inlineStr"/>
     </row>
     <row r="878">
@@ -82149,7 +82425,7 @@
       </c>
       <c r="T881" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U881" t="inlineStr">
@@ -82157,7 +82433,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V881" t="inlineStr"/>
+      <c r="V881" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W881" t="inlineStr"/>
     </row>
     <row r="882">
@@ -83842,7 +84122,7 @@
       <c r="S898" t="inlineStr"/>
       <c r="T898" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U898" t="inlineStr">
@@ -83850,7 +84130,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V898" t="inlineStr"/>
+      <c r="V898" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W898" t="inlineStr"/>
     </row>
     <row r="899">
@@ -84040,7 +84324,7 @@
       <c r="S900" t="inlineStr"/>
       <c r="T900" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U900" t="inlineStr">
@@ -84048,7 +84332,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V900" t="inlineStr"/>
+      <c r="V900" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W900" t="inlineStr"/>
     </row>
     <row r="901">
@@ -85030,7 +85318,7 @@
       <c r="S910" t="inlineStr"/>
       <c r="T910" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U910" t="inlineStr">
@@ -85038,7 +85326,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V910" t="inlineStr"/>
+      <c r="V910" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W910" t="inlineStr"/>
     </row>
     <row r="911">
@@ -85127,7 +85419,7 @@
       <c r="S911" t="inlineStr"/>
       <c r="T911" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U911" t="inlineStr">
@@ -85135,7 +85427,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V911" t="inlineStr"/>
+      <c r="V911" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W911" t="inlineStr"/>
     </row>
     <row r="912">
@@ -85628,7 +85924,7 @@
       <c r="S916" t="inlineStr"/>
       <c r="T916" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U916" t="inlineStr">
@@ -85636,7 +85932,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V916" t="inlineStr"/>
+      <c r="V916" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W916" t="inlineStr"/>
     </row>
     <row r="917">
@@ -85725,7 +86025,7 @@
       <c r="S917" t="inlineStr"/>
       <c r="T917" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U917" t="inlineStr">
@@ -85733,7 +86033,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V917" t="inlineStr"/>
+      <c r="V917" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W917" t="inlineStr"/>
     </row>
     <row r="918">
@@ -86315,7 +86619,7 @@
       <c r="S923" t="inlineStr"/>
       <c r="T923" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U923" t="inlineStr">
@@ -86323,7 +86627,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V923" t="inlineStr"/>
+      <c r="V923" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W923" t="inlineStr"/>
     </row>
     <row r="924">
@@ -87099,7 +87407,7 @@
       <c r="S931" t="inlineStr"/>
       <c r="T931" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U931" t="inlineStr">
@@ -87107,7 +87415,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V931" t="inlineStr"/>
+      <c r="V931" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W931" t="inlineStr"/>
     </row>
     <row r="932">
@@ -87196,7 +87508,7 @@
       <c r="S932" t="inlineStr"/>
       <c r="T932" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U932" t="inlineStr">
@@ -87204,7 +87516,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V932" t="inlineStr"/>
+      <c r="V932" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W932" t="inlineStr"/>
     </row>
     <row r="933">
@@ -87697,7 +88013,7 @@
       <c r="S937" t="inlineStr"/>
       <c r="T937" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U937" t="inlineStr">
@@ -87705,7 +88021,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V937" t="inlineStr"/>
+      <c r="V937" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W937" t="inlineStr"/>
     </row>
     <row r="938">
@@ -88093,7 +88413,7 @@
       <c r="S941" t="inlineStr"/>
       <c r="T941" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U941" t="inlineStr">
@@ -88101,7 +88421,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V941" t="inlineStr"/>
+      <c r="V941" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W941" t="inlineStr"/>
     </row>
     <row r="942">
@@ -88190,7 +88514,7 @@
       <c r="S942" t="inlineStr"/>
       <c r="T942" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U942" t="inlineStr">
@@ -88198,7 +88522,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V942" t="inlineStr"/>
+      <c r="V942" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W942" t="inlineStr"/>
     </row>
     <row r="943">
@@ -88287,7 +88615,7 @@
       <c r="S943" t="inlineStr"/>
       <c r="T943" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U943" t="inlineStr">
@@ -88295,7 +88623,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V943" t="inlineStr"/>
+      <c r="V943" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W943" t="inlineStr"/>
     </row>
     <row r="944">
@@ -88384,7 +88716,7 @@
       <c r="S944" t="inlineStr"/>
       <c r="T944" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U944" t="inlineStr">
@@ -88392,7 +88724,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V944" t="inlineStr"/>
+      <c r="V944" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W944" t="inlineStr"/>
     </row>
     <row r="945">
@@ -88578,7 +88914,7 @@
       <c r="S946" t="inlineStr"/>
       <c r="T946" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U946" t="inlineStr">
@@ -88586,7 +88922,11 @@
           <t>2026-03-05 11:53:49</t>
         </is>
       </c>
-      <c r="V946" t="inlineStr"/>
+      <c r="V946" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W946" t="inlineStr"/>
     </row>
     <row r="947">
@@ -88675,7 +89015,7 @@
       <c r="S947" t="inlineStr"/>
       <c r="T947" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U947" t="inlineStr">
@@ -88683,7 +89023,11 @@
           <t>2026-03-05 12:34:44</t>
         </is>
       </c>
-      <c r="V947" t="inlineStr"/>
+      <c r="V947" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W947" t="inlineStr"/>
     </row>
     <row r="948">
@@ -88970,7 +89314,7 @@
       <c r="S950" t="inlineStr"/>
       <c r="T950" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U950" t="inlineStr">
@@ -88978,7 +89322,11 @@
           <t>2026-03-05 12:34:44</t>
         </is>
       </c>
-      <c r="V950" t="inlineStr"/>
+      <c r="V950" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W950" t="inlineStr"/>
     </row>
     <row r="951">
@@ -89552,7 +89900,7 @@
       <c r="S956" t="inlineStr"/>
       <c r="T956" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U956" t="inlineStr">
@@ -89560,7 +89908,11 @@
           <t>2026-03-05 12:34:44</t>
         </is>
       </c>
-      <c r="V956" t="inlineStr"/>
+      <c r="V956" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W956" t="inlineStr"/>
     </row>
     <row r="957">
@@ -89746,7 +90098,7 @@
       <c r="S958" t="inlineStr"/>
       <c r="T958" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U958" t="inlineStr">
@@ -89754,7 +90106,11 @@
           <t>2026-03-05 13:00:52</t>
         </is>
       </c>
-      <c r="V958" t="inlineStr"/>
+      <c r="V958" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W958" t="inlineStr"/>
     </row>
     <row r="959">
@@ -89843,7 +90199,7 @@
       <c r="S959" t="inlineStr"/>
       <c r="T959" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U959" t="inlineStr">
@@ -89851,7 +90207,11 @@
           <t>2026-03-05 13:00:52</t>
         </is>
       </c>
-      <c r="V959" t="inlineStr"/>
+      <c r="V959" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
       <c r="W959" t="inlineStr"/>
     </row>
     <row r="960">
@@ -90328,16 +90688,1572 @@
       <c r="S964" t="inlineStr"/>
       <c r="T964" t="inlineStr">
         <is>
+          <t>LEZART</t>
+        </is>
+      </c>
+      <c r="U964" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:00:52</t>
+        </is>
+      </c>
+      <c r="V964" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="W964" t="inlineStr"/>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011463_1</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>41011463_1</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011463</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:08:57</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:08:57</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:08:57</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:10:00</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:50:00</t>
+        </is>
+      </c>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>47.452057</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>19.331224</t>
+        </is>
+      </c>
+      <c r="O965" t="inlineStr"/>
+      <c r="P965" t="inlineStr"/>
+      <c r="Q965" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="R965" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S965" t="inlineStr"/>
+      <c r="T965" t="inlineStr">
+        <is>
           <t>AKTIV</t>
         </is>
       </c>
-      <c r="U964" t="inlineStr">
-        <is>
-          <t>2026-03-05 13:00:52</t>
-        </is>
-      </c>
-      <c r="V964" t="inlineStr"/>
-      <c r="W964" t="inlineStr"/>
+      <c r="U965" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V965" t="inlineStr"/>
+      <c r="W965" t="inlineStr"/>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011466_1</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>41011466_1</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011466</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:13:49</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:13:49</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:13:49</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:54:00</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="M966" t="inlineStr">
+        <is>
+          <t>46.09823</t>
+        </is>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>18.587269</t>
+        </is>
+      </c>
+      <c r="O966" t="inlineStr"/>
+      <c r="P966" t="inlineStr"/>
+      <c r="Q966" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="R966" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S966" t="inlineStr"/>
+      <c r="T966" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U966" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V966" t="inlineStr"/>
+      <c r="W966" t="inlineStr"/>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011467_1</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>41011467_1</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011467</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:14:30</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:14:30</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:14:30</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:30:00</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>4432</t>
+        </is>
+      </c>
+      <c r="M967" t="inlineStr">
+        <is>
+          <t>46.29049</t>
+        </is>
+      </c>
+      <c r="N967" t="inlineStr">
+        <is>
+          <t>20.571445</t>
+        </is>
+      </c>
+      <c r="O967" t="inlineStr"/>
+      <c r="P967" t="inlineStr"/>
+      <c r="Q967" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R967" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S967" t="inlineStr"/>
+      <c r="T967" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U967" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V967" t="inlineStr"/>
+      <c r="W967" t="inlineStr"/>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011468_1</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>41011468_1</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011468</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:34:37</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:15:11</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:34:37</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:15:00</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M968" t="inlineStr">
+        <is>
+          <t>47.879044</t>
+        </is>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>20.825638</t>
+        </is>
+      </c>
+      <c r="O968" t="inlineStr"/>
+      <c r="P968" t="inlineStr"/>
+      <c r="Q968" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R968" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S968" t="inlineStr"/>
+      <c r="T968" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U968" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V968" t="inlineStr"/>
+      <c r="W968" t="inlineStr"/>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011469_1</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>41011469_1</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011469</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:19:53</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:19:53</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:19:53</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:20:00</t>
+        </is>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M969" t="inlineStr">
+        <is>
+          <t>46.510662</t>
+        </is>
+      </c>
+      <c r="N969" t="inlineStr">
+        <is>
+          <t>18.405485</t>
+        </is>
+      </c>
+      <c r="O969" t="inlineStr"/>
+      <c r="P969" t="inlineStr"/>
+      <c r="Q969" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R969" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S969" t="inlineStr"/>
+      <c r="T969" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U969" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V969" t="inlineStr"/>
+      <c r="W969" t="inlineStr"/>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011470_1</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>41011470_1</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011470</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:22:57</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:22:57</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:22:57</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>2026-03-06 07:30:00</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>2026-03-06 15:00:00</t>
+        </is>
+      </c>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M970" t="inlineStr">
+        <is>
+          <t>47.19125</t>
+        </is>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>19.333088</t>
+        </is>
+      </c>
+      <c r="O970" t="inlineStr"/>
+      <c r="P970" t="inlineStr"/>
+      <c r="Q970" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="R970" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S970" t="inlineStr"/>
+      <c r="T970" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U970" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V970" t="inlineStr"/>
+      <c r="W970" t="inlineStr"/>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011472_1</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>41011472_1</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011472</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:26:02</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:26:02</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:26:02</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>2026-03-06 07:30:00</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>2026-03-06 15:00:00</t>
+        </is>
+      </c>
+      <c r="K971" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>4601</t>
+        </is>
+      </c>
+      <c r="M971" t="inlineStr">
+        <is>
+          <t>47.372063</t>
+        </is>
+      </c>
+      <c r="N971" t="inlineStr">
+        <is>
+          <t>19.228436</t>
+        </is>
+      </c>
+      <c r="O971" t="inlineStr"/>
+      <c r="P971" t="inlineStr"/>
+      <c r="Q971" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R971" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S971" t="inlineStr"/>
+      <c r="T971" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U971" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V971" t="inlineStr"/>
+      <c r="W971" t="inlineStr"/>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011474_1</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>41011474_1</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011474</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:32:12</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:32:12</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:32:12</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:31:00</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:00</t>
+        </is>
+      </c>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>7318</t>
+        </is>
+      </c>
+      <c r="M972" t="inlineStr">
+        <is>
+          <t>46.81138</t>
+        </is>
+      </c>
+      <c r="N972" t="inlineStr">
+        <is>
+          <t>17.447548</t>
+        </is>
+      </c>
+      <c r="O972" t="inlineStr"/>
+      <c r="P972" t="inlineStr"/>
+      <c r="Q972" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R972" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S972" t="inlineStr"/>
+      <c r="T972" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U972" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V972" t="inlineStr"/>
+      <c r="W972" t="inlineStr"/>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011480_1</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>41011480_1</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011480</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:41:20</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:41:20</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:41:20</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>2026-03-06 08:30:00</t>
+        </is>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>2026-03-06 14:30:00</t>
+        </is>
+      </c>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>11104</t>
+        </is>
+      </c>
+      <c r="M973" t="inlineStr">
+        <is>
+          <t>47.548145</t>
+        </is>
+      </c>
+      <c r="N973" t="inlineStr">
+        <is>
+          <t>18.93623</t>
+        </is>
+      </c>
+      <c r="O973" t="inlineStr"/>
+      <c r="P973" t="inlineStr"/>
+      <c r="Q973" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="R973" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S973" t="inlineStr"/>
+      <c r="T973" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U973" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V973" t="inlineStr"/>
+      <c r="W973" t="inlineStr"/>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011484_1</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>41011484_1</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011484</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:54:20</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:54:20</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:54:20</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:50:00</t>
+        </is>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:00:00</t>
+        </is>
+      </c>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M974" t="inlineStr">
+        <is>
+          <t>47.801723</t>
+        </is>
+      </c>
+      <c r="N974" t="inlineStr">
+        <is>
+          <t>21.19898</t>
+        </is>
+      </c>
+      <c r="O974" t="inlineStr"/>
+      <c r="P974" t="inlineStr"/>
+      <c r="Q974" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="R974" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S974" t="inlineStr"/>
+      <c r="T974" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U974" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V974" t="inlineStr"/>
+      <c r="W974" t="inlineStr"/>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011485_1</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>41011485_1</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011485</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:56:24</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:56:24</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:56:24</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>2026-03-06 08:00:00</t>
+        </is>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>2026-03-06 14:00:00</t>
+        </is>
+      </c>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M975" t="inlineStr">
+        <is>
+          <t>47.122437</t>
+        </is>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>17.323627</t>
+        </is>
+      </c>
+      <c r="O975" t="inlineStr"/>
+      <c r="P975" t="inlineStr"/>
+      <c r="Q975" t="inlineStr">
+        <is>
+          <t>690.0</t>
+        </is>
+      </c>
+      <c r="R975" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S975" t="inlineStr"/>
+      <c r="T975" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U975" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V975" t="inlineStr"/>
+      <c r="W975" t="inlineStr"/>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011486_1</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>41011486_1</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011486</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:57:55</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:57:55</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:57:55</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>2026-03-06 08:00:00</t>
+        </is>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>2026-03-06 14:00:00</t>
+        </is>
+      </c>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M976" t="inlineStr">
+        <is>
+          <t>47.13744</t>
+        </is>
+      </c>
+      <c r="N976" t="inlineStr">
+        <is>
+          <t>17.526262</t>
+        </is>
+      </c>
+      <c r="O976" t="inlineStr"/>
+      <c r="P976" t="inlineStr"/>
+      <c r="Q976" t="inlineStr">
+        <is>
+          <t>980.0</t>
+        </is>
+      </c>
+      <c r="R976" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S976" t="inlineStr"/>
+      <c r="T976" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U976" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V976" t="inlineStr"/>
+      <c r="W976" t="inlineStr"/>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011487_1</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>41011487_1</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011487</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:59:20</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:59:20</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:59:20</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>2026-03-06 08:00:00</t>
+        </is>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>2026-03-06 15:00:00</t>
+        </is>
+      </c>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="M977" t="inlineStr">
+        <is>
+          <t>47.101765</t>
+        </is>
+      </c>
+      <c r="N977" t="inlineStr">
+        <is>
+          <t>17.57007</t>
+        </is>
+      </c>
+      <c r="O977" t="inlineStr"/>
+      <c r="P977" t="inlineStr"/>
+      <c r="Q977" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R977" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S977" t="inlineStr"/>
+      <c r="T977" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U977" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V977" t="inlineStr"/>
+      <c r="W977" t="inlineStr"/>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011488_1</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>41011488_1</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011488</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:46</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:46</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:00:46</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>2026-03-06 08:00:00</t>
+        </is>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>2026-03-06 15:00:00</t>
+        </is>
+      </c>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>73129</t>
+        </is>
+      </c>
+      <c r="M978" t="inlineStr">
+        <is>
+          <t>47.083237</t>
+        </is>
+      </c>
+      <c r="N978" t="inlineStr">
+        <is>
+          <t>17.522036</t>
+        </is>
+      </c>
+      <c r="O978" t="inlineStr"/>
+      <c r="P978" t="inlineStr"/>
+      <c r="Q978" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R978" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S978" t="inlineStr"/>
+      <c r="T978" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U978" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V978" t="inlineStr"/>
+      <c r="W978" t="inlineStr"/>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011491_1</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>41011491_1</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011491</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:16:34</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:12:00</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:16:34</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:10:00</t>
+        </is>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:10:00</t>
+        </is>
+      </c>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="M979" t="inlineStr">
+        <is>
+          <t>47.388344</t>
+        </is>
+      </c>
+      <c r="N979" t="inlineStr">
+        <is>
+          <t>18.84515</t>
+        </is>
+      </c>
+      <c r="O979" t="inlineStr"/>
+      <c r="P979" t="inlineStr"/>
+      <c r="Q979" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="R979" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S979" t="inlineStr"/>
+      <c r="T979" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U979" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V979" t="inlineStr"/>
+      <c r="W979" t="inlineStr"/>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011492_1</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>41011492_1</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011492</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:12:29</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:12:29</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:12:29</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:10:00</t>
+        </is>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:10:00</t>
+        </is>
+      </c>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M980" t="inlineStr">
+        <is>
+          <t>47.8113</t>
+        </is>
+      </c>
+      <c r="N980" t="inlineStr">
+        <is>
+          <t>21.159636</t>
+        </is>
+      </c>
+      <c r="O980" t="inlineStr"/>
+      <c r="P980" t="inlineStr"/>
+      <c r="Q980" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="R980" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S980" t="inlineStr"/>
+      <c r="T980" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U980" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V980" t="inlineStr"/>
+      <c r="W980" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W980"/>
+  <dimension ref="A1:W993"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26923,7 +26923,7 @@
       <c r="S297" t="inlineStr"/>
       <c r="T297" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U297" t="inlineStr">
@@ -26931,7 +26931,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V297" t="inlineStr"/>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W297" t="inlineStr"/>
     </row>
     <row r="298">
@@ -27101,7 +27105,7 @@
       <c r="S299" t="inlineStr"/>
       <c r="T299" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U299" t="inlineStr">
@@ -27109,7 +27113,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V299" t="inlineStr"/>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W299" t="inlineStr"/>
     </row>
     <row r="300">
@@ -30191,7 +30199,7 @@
       <c r="S333" t="inlineStr"/>
       <c r="T333" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U333" t="inlineStr">
@@ -30199,7 +30207,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V333" t="inlineStr"/>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W333" t="inlineStr"/>
     </row>
     <row r="334">
@@ -30280,7 +30292,7 @@
       <c r="S334" t="inlineStr"/>
       <c r="T334" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U334" t="inlineStr">
@@ -30288,7 +30300,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V334" t="inlineStr"/>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W334" t="inlineStr"/>
     </row>
     <row r="335">
@@ -30458,7 +30474,7 @@
       <c r="S336" t="inlineStr"/>
       <c r="T336" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U336" t="inlineStr">
@@ -30466,7 +30482,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V336" t="inlineStr"/>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W336" t="inlineStr"/>
     </row>
     <row r="337">
@@ -31101,7 +31121,7 @@
       <c r="S343" t="inlineStr"/>
       <c r="T343" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U343" t="inlineStr">
@@ -31109,7 +31129,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V343" t="inlineStr"/>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W343" t="inlineStr"/>
     </row>
     <row r="344">
@@ -31283,7 +31307,7 @@
       <c r="S345" t="inlineStr"/>
       <c r="T345" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U345" t="inlineStr">
@@ -31291,7 +31315,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V345" t="inlineStr"/>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W345" t="inlineStr"/>
     </row>
     <row r="346">
@@ -31372,7 +31400,7 @@
       <c r="S346" t="inlineStr"/>
       <c r="T346" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U346" t="inlineStr">
@@ -31380,7 +31408,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V346" t="inlineStr"/>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W346" t="inlineStr"/>
     </row>
     <row r="347">
@@ -31461,7 +31493,7 @@
       <c r="S347" t="inlineStr"/>
       <c r="T347" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U347" t="inlineStr">
@@ -31469,7 +31501,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V347" t="inlineStr"/>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W347" t="inlineStr"/>
     </row>
     <row r="348">
@@ -31643,7 +31679,7 @@
       <c r="S349" t="inlineStr"/>
       <c r="T349" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U349" t="inlineStr">
@@ -31651,7 +31687,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V349" t="inlineStr"/>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W349" t="inlineStr"/>
     </row>
     <row r="350">
@@ -31732,7 +31772,7 @@
       <c r="S350" t="inlineStr"/>
       <c r="T350" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U350" t="inlineStr">
@@ -31740,7 +31780,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V350" t="inlineStr"/>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W350" t="inlineStr"/>
     </row>
     <row r="351">
@@ -31821,7 +31865,7 @@
       <c r="S351" t="inlineStr"/>
       <c r="T351" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U351" t="inlineStr">
@@ -31829,7 +31873,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V351" t="inlineStr"/>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W351" t="inlineStr"/>
     </row>
     <row r="352">
@@ -43222,7 +43270,7 @@
       <c r="S478" t="inlineStr"/>
       <c r="T478" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U478" t="inlineStr">
@@ -43230,7 +43278,11 @@
           <t>2026-03-04 16:02:32</t>
         </is>
       </c>
-      <c r="V478" t="inlineStr"/>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W478" t="inlineStr"/>
     </row>
     <row r="479">
@@ -50073,7 +50125,7 @@
       </c>
       <c r="T553" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U553" t="inlineStr">
@@ -50081,7 +50133,11 @@
           <t>2026-03-04 18:54:25</t>
         </is>
       </c>
-      <c r="V553" t="inlineStr"/>
+      <c r="V553" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W553" t="inlineStr"/>
     </row>
     <row r="554">
@@ -50170,7 +50226,7 @@
       <c r="S554" t="inlineStr"/>
       <c r="T554" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U554" t="inlineStr">
@@ -50178,7 +50234,11 @@
           <t>2026-03-04 18:54:25</t>
         </is>
       </c>
-      <c r="V554" t="inlineStr"/>
+      <c r="V554" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W554" t="inlineStr"/>
     </row>
     <row r="555">
@@ -50461,7 +50521,7 @@
       <c r="S557" t="inlineStr"/>
       <c r="T557" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U557" t="inlineStr">
@@ -50469,7 +50529,11 @@
           <t>2026-03-04 18:54:25</t>
         </is>
       </c>
-      <c r="V557" t="inlineStr"/>
+      <c r="V557" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W557" t="inlineStr"/>
     </row>
     <row r="558">
@@ -54029,7 +54093,7 @@
       <c r="S593" t="inlineStr"/>
       <c r="T593" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U593" t="inlineStr">
@@ -54037,7 +54101,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V593" t="inlineStr"/>
+      <c r="V593" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W593" t="inlineStr"/>
     </row>
     <row r="594">
@@ -54328,7 +54396,7 @@
       <c r="S596" t="inlineStr"/>
       <c r="T596" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U596" t="inlineStr">
@@ -54336,7 +54404,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V596" t="inlineStr"/>
+      <c r="V596" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W596" t="inlineStr"/>
     </row>
     <row r="597">
@@ -54425,7 +54497,7 @@
       <c r="S597" t="inlineStr"/>
       <c r="T597" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U597" t="inlineStr">
@@ -54433,7 +54505,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V597" t="inlineStr"/>
+      <c r="V597" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W597" t="inlineStr"/>
     </row>
     <row r="598">
@@ -54619,7 +54695,7 @@
       <c r="S599" t="inlineStr"/>
       <c r="T599" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U599" t="inlineStr">
@@ -54627,7 +54703,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V599" t="inlineStr"/>
+      <c r="V599" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W599" t="inlineStr"/>
     </row>
     <row r="600">
@@ -54716,7 +54796,7 @@
       <c r="S600" t="inlineStr"/>
       <c r="T600" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U600" t="inlineStr">
@@ -54724,7 +54804,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V600" t="inlineStr"/>
+      <c r="V600" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W600" t="inlineStr"/>
     </row>
     <row r="601">
@@ -54910,7 +54994,7 @@
       <c r="S602" t="inlineStr"/>
       <c r="T602" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U602" t="inlineStr">
@@ -54918,7 +55002,11 @@
           <t>2026-03-05 06:34:57</t>
         </is>
       </c>
-      <c r="V602" t="inlineStr"/>
+      <c r="V602" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W602" t="inlineStr"/>
     </row>
     <row r="603">
@@ -55803,7 +55891,7 @@
       <c r="S611" t="inlineStr"/>
       <c r="T611" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U611" t="inlineStr">
@@ -55811,7 +55899,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V611" t="inlineStr"/>
+      <c r="V611" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W611" t="inlineStr"/>
     </row>
     <row r="612">
@@ -56098,7 +56190,7 @@
       <c r="S614" t="inlineStr"/>
       <c r="T614" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U614" t="inlineStr">
@@ -56106,7 +56198,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V614" t="inlineStr"/>
+      <c r="V614" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W614" t="inlineStr"/>
     </row>
     <row r="615">
@@ -56393,7 +56489,7 @@
       <c r="S617" t="inlineStr"/>
       <c r="T617" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U617" t="inlineStr">
@@ -56401,7 +56497,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V617" t="inlineStr"/>
+      <c r="V617" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W617" t="inlineStr"/>
     </row>
     <row r="618">
@@ -56688,7 +56788,7 @@
       <c r="S620" t="inlineStr"/>
       <c r="T620" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U620" t="inlineStr">
@@ -56696,7 +56796,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V620" t="inlineStr"/>
+      <c r="V620" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W620" t="inlineStr"/>
     </row>
     <row r="621">
@@ -56886,7 +56990,7 @@
       <c r="S622" t="inlineStr"/>
       <c r="T622" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U622" t="inlineStr">
@@ -56894,7 +56998,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V622" t="inlineStr"/>
+      <c r="V622" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W622" t="inlineStr"/>
     </row>
     <row r="623">
@@ -56983,7 +57091,7 @@
       <c r="S623" t="inlineStr"/>
       <c r="T623" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U623" t="inlineStr">
@@ -56991,7 +57099,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V623" t="inlineStr"/>
+      <c r="V623" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W623" t="inlineStr"/>
     </row>
     <row r="624">
@@ -57177,7 +57289,7 @@
       <c r="S625" t="inlineStr"/>
       <c r="T625" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U625" t="inlineStr">
@@ -57185,7 +57297,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V625" t="inlineStr"/>
+      <c r="V625" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W625" t="inlineStr"/>
     </row>
     <row r="626">
@@ -57274,7 +57390,7 @@
       <c r="S626" t="inlineStr"/>
       <c r="T626" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U626" t="inlineStr">
@@ -57282,7 +57398,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V626" t="inlineStr"/>
+      <c r="V626" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W626" t="inlineStr"/>
     </row>
     <row r="627">
@@ -57666,7 +57786,7 @@
       <c r="S630" t="inlineStr"/>
       <c r="T630" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U630" t="inlineStr">
@@ -57674,7 +57794,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V630" t="inlineStr"/>
+      <c r="V630" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W630" t="inlineStr"/>
     </row>
     <row r="631">
@@ -57860,7 +57984,7 @@
       <c r="S632" t="inlineStr"/>
       <c r="T632" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U632" t="inlineStr">
@@ -57868,7 +57992,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V632" t="inlineStr"/>
+      <c r="V632" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W632" t="inlineStr"/>
     </row>
     <row r="633">
@@ -57957,7 +58085,7 @@
       <c r="S633" t="inlineStr"/>
       <c r="T633" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U633" t="inlineStr">
@@ -57965,7 +58093,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V633" t="inlineStr"/>
+      <c r="V633" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W633" t="inlineStr"/>
     </row>
     <row r="634">
@@ -58054,7 +58186,7 @@
       <c r="S634" t="inlineStr"/>
       <c r="T634" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U634" t="inlineStr">
@@ -58062,7 +58194,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V634" t="inlineStr"/>
+      <c r="V634" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W634" t="inlineStr"/>
     </row>
     <row r="635">
@@ -58151,7 +58287,7 @@
       <c r="S635" t="inlineStr"/>
       <c r="T635" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U635" t="inlineStr">
@@ -58159,7 +58295,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V635" t="inlineStr"/>
+      <c r="V635" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W635" t="inlineStr"/>
     </row>
     <row r="636">
@@ -58446,7 +58586,7 @@
       <c r="S638" t="inlineStr"/>
       <c r="T638" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U638" t="inlineStr">
@@ -58454,7 +58594,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V638" t="inlineStr"/>
+      <c r="V638" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W638" t="inlineStr"/>
     </row>
     <row r="639">
@@ -58543,7 +58687,7 @@
       <c r="S639" t="inlineStr"/>
       <c r="T639" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U639" t="inlineStr">
@@ -58551,7 +58695,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V639" t="inlineStr"/>
+      <c r="V639" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W639" t="inlineStr"/>
     </row>
     <row r="640">
@@ -58737,7 +58885,7 @@
       <c r="S641" t="inlineStr"/>
       <c r="T641" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U641" t="inlineStr">
@@ -58745,7 +58893,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V641" t="inlineStr"/>
+      <c r="V641" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W641" t="inlineStr"/>
     </row>
     <row r="642">
@@ -59028,7 +59180,7 @@
       <c r="S644" t="inlineStr"/>
       <c r="T644" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U644" t="inlineStr">
@@ -59036,7 +59188,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V644" t="inlineStr"/>
+      <c r="V644" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W644" t="inlineStr"/>
     </row>
     <row r="645">
@@ -59125,7 +59281,7 @@
       <c r="S645" t="inlineStr"/>
       <c r="T645" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U645" t="inlineStr">
@@ -59133,7 +59289,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V645" t="inlineStr"/>
+      <c r="V645" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W645" t="inlineStr"/>
     </row>
     <row r="646">
@@ -59323,7 +59483,7 @@
       <c r="S647" t="inlineStr"/>
       <c r="T647" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U647" t="inlineStr">
@@ -59331,7 +59491,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V647" t="inlineStr"/>
+      <c r="V647" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W647" t="inlineStr"/>
     </row>
     <row r="648">
@@ -59420,7 +59584,7 @@
       <c r="S648" t="inlineStr"/>
       <c r="T648" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U648" t="inlineStr">
@@ -59428,7 +59592,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V648" t="inlineStr"/>
+      <c r="V648" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W648" t="inlineStr"/>
     </row>
     <row r="649">
@@ -59517,7 +59685,7 @@
       <c r="S649" t="inlineStr"/>
       <c r="T649" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U649" t="inlineStr">
@@ -59525,7 +59693,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V649" t="inlineStr"/>
+      <c r="V649" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W649" t="inlineStr"/>
     </row>
     <row r="650">
@@ -59614,7 +59786,7 @@
       <c r="S650" t="inlineStr"/>
       <c r="T650" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U650" t="inlineStr">
@@ -59622,7 +59794,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V650" t="inlineStr"/>
+      <c r="V650" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W650" t="inlineStr"/>
     </row>
     <row r="651">
@@ -59711,7 +59887,7 @@
       <c r="S651" t="inlineStr"/>
       <c r="T651" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U651" t="inlineStr">
@@ -59719,7 +59895,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V651" t="inlineStr"/>
+      <c r="V651" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W651" t="inlineStr"/>
     </row>
     <row r="652">
@@ -59808,7 +59988,7 @@
       <c r="S652" t="inlineStr"/>
       <c r="T652" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U652" t="inlineStr">
@@ -59816,7 +59996,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V652" t="inlineStr"/>
+      <c r="V652" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W652" t="inlineStr"/>
     </row>
     <row r="653">
@@ -59905,7 +60089,7 @@
       <c r="S653" t="inlineStr"/>
       <c r="T653" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U653" t="inlineStr">
@@ -59913,7 +60097,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V653" t="inlineStr"/>
+      <c r="V653" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W653" t="inlineStr"/>
     </row>
     <row r="654">
@@ -60002,7 +60190,7 @@
       <c r="S654" t="inlineStr"/>
       <c r="T654" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U654" t="inlineStr">
@@ -60010,7 +60198,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V654" t="inlineStr"/>
+      <c r="V654" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W654" t="inlineStr"/>
     </row>
     <row r="655">
@@ -60099,7 +60291,7 @@
       <c r="S655" t="inlineStr"/>
       <c r="T655" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U655" t="inlineStr">
@@ -60107,7 +60299,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V655" t="inlineStr"/>
+      <c r="V655" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W655" t="inlineStr"/>
     </row>
     <row r="656">
@@ -60196,7 +60392,7 @@
       <c r="S656" t="inlineStr"/>
       <c r="T656" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U656" t="inlineStr">
@@ -60204,7 +60400,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V656" t="inlineStr"/>
+      <c r="V656" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W656" t="inlineStr"/>
     </row>
     <row r="657">
@@ -60293,7 +60493,7 @@
       <c r="S657" t="inlineStr"/>
       <c r="T657" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U657" t="inlineStr">
@@ -60301,7 +60501,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V657" t="inlineStr"/>
+      <c r="V657" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W657" t="inlineStr"/>
     </row>
     <row r="658">
@@ -60390,7 +60594,7 @@
       <c r="S658" t="inlineStr"/>
       <c r="T658" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U658" t="inlineStr">
@@ -60398,7 +60602,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V658" t="inlineStr"/>
+      <c r="V658" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W658" t="inlineStr"/>
     </row>
     <row r="659">
@@ -60487,7 +60695,7 @@
       <c r="S659" t="inlineStr"/>
       <c r="T659" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U659" t="inlineStr">
@@ -60495,7 +60703,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V659" t="inlineStr"/>
+      <c r="V659" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W659" t="inlineStr"/>
     </row>
     <row r="660">
@@ -60584,7 +60796,7 @@
       <c r="S660" t="inlineStr"/>
       <c r="T660" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U660" t="inlineStr">
@@ -60592,7 +60804,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V660" t="inlineStr"/>
+      <c r="V660" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W660" t="inlineStr"/>
     </row>
     <row r="661">
@@ -60681,7 +60897,7 @@
       <c r="S661" t="inlineStr"/>
       <c r="T661" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U661" t="inlineStr">
@@ -60689,7 +60905,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V661" t="inlineStr"/>
+      <c r="V661" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W661" t="inlineStr"/>
     </row>
     <row r="662">
@@ -60778,7 +60998,7 @@
       <c r="S662" t="inlineStr"/>
       <c r="T662" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U662" t="inlineStr">
@@ -60786,7 +61006,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V662" t="inlineStr"/>
+      <c r="V662" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W662" t="inlineStr"/>
     </row>
     <row r="663">
@@ -60875,7 +61099,7 @@
       <c r="S663" t="inlineStr"/>
       <c r="T663" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U663" t="inlineStr">
@@ -60883,7 +61107,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V663" t="inlineStr"/>
+      <c r="V663" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W663" t="inlineStr"/>
     </row>
     <row r="664">
@@ -60972,7 +61200,7 @@
       <c r="S664" t="inlineStr"/>
       <c r="T664" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U664" t="inlineStr">
@@ -60980,7 +61208,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V664" t="inlineStr"/>
+      <c r="V664" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W664" t="inlineStr"/>
     </row>
     <row r="665">
@@ -61069,7 +61301,7 @@
       <c r="S665" t="inlineStr"/>
       <c r="T665" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U665" t="inlineStr">
@@ -61077,7 +61309,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V665" t="inlineStr"/>
+      <c r="V665" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W665" t="inlineStr"/>
     </row>
     <row r="666">
@@ -61166,7 +61402,7 @@
       <c r="S666" t="inlineStr"/>
       <c r="T666" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U666" t="inlineStr">
@@ -61174,7 +61410,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V666" t="inlineStr"/>
+      <c r="V666" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W666" t="inlineStr"/>
     </row>
     <row r="667">
@@ -61360,7 +61600,7 @@
       <c r="S668" t="inlineStr"/>
       <c r="T668" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U668" t="inlineStr">
@@ -61368,7 +61608,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V668" t="inlineStr"/>
+      <c r="V668" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W668" t="inlineStr"/>
     </row>
     <row r="669">
@@ -61457,7 +61701,7 @@
       <c r="S669" t="inlineStr"/>
       <c r="T669" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U669" t="inlineStr">
@@ -61465,7 +61709,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V669" t="inlineStr"/>
+      <c r="V669" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W669" t="inlineStr"/>
     </row>
     <row r="670">
@@ -61554,7 +61802,7 @@
       <c r="S670" t="inlineStr"/>
       <c r="T670" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U670" t="inlineStr">
@@ -61562,7 +61810,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V670" t="inlineStr"/>
+      <c r="V670" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W670" t="inlineStr"/>
     </row>
     <row r="671">
@@ -61752,7 +62004,7 @@
       <c r="S672" t="inlineStr"/>
       <c r="T672" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U672" t="inlineStr">
@@ -61760,7 +62012,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V672" t="inlineStr"/>
+      <c r="V672" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W672" t="inlineStr"/>
     </row>
     <row r="673">
@@ -61849,7 +62105,7 @@
       <c r="S673" t="inlineStr"/>
       <c r="T673" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U673" t="inlineStr">
@@ -61857,7 +62113,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V673" t="inlineStr"/>
+      <c r="V673" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W673" t="inlineStr"/>
     </row>
     <row r="674">
@@ -61946,7 +62206,7 @@
       <c r="S674" t="inlineStr"/>
       <c r="T674" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U674" t="inlineStr">
@@ -61954,7 +62214,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V674" t="inlineStr"/>
+      <c r="V674" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W674" t="inlineStr"/>
     </row>
     <row r="675">
@@ -62144,7 +62408,7 @@
       <c r="S676" t="inlineStr"/>
       <c r="T676" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U676" t="inlineStr">
@@ -62152,7 +62416,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V676" t="inlineStr"/>
+      <c r="V676" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W676" t="inlineStr"/>
     </row>
     <row r="677">
@@ -62241,7 +62509,7 @@
       <c r="S677" t="inlineStr"/>
       <c r="T677" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U677" t="inlineStr">
@@ -62249,7 +62517,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V677" t="inlineStr"/>
+      <c r="V677" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W677" t="inlineStr"/>
     </row>
     <row r="678">
@@ -62338,7 +62610,7 @@
       <c r="S678" t="inlineStr"/>
       <c r="T678" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U678" t="inlineStr">
@@ -62346,7 +62618,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V678" t="inlineStr"/>
+      <c r="V678" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W678" t="inlineStr"/>
     </row>
     <row r="679">
@@ -62435,7 +62711,7 @@
       <c r="S679" t="inlineStr"/>
       <c r="T679" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U679" t="inlineStr">
@@ -62443,7 +62719,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V679" t="inlineStr"/>
+      <c r="V679" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W679" t="inlineStr"/>
     </row>
     <row r="680">
@@ -62532,7 +62812,7 @@
       <c r="S680" t="inlineStr"/>
       <c r="T680" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U680" t="inlineStr">
@@ -62540,7 +62820,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V680" t="inlineStr"/>
+      <c r="V680" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W680" t="inlineStr"/>
     </row>
     <row r="681">
@@ -62629,7 +62913,7 @@
       <c r="S681" t="inlineStr"/>
       <c r="T681" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U681" t="inlineStr">
@@ -62637,7 +62921,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V681" t="inlineStr"/>
+      <c r="V681" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W681" t="inlineStr"/>
     </row>
     <row r="682">
@@ -62726,7 +63014,7 @@
       <c r="S682" t="inlineStr"/>
       <c r="T682" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U682" t="inlineStr">
@@ -62734,7 +63022,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V682" t="inlineStr"/>
+      <c r="V682" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W682" t="inlineStr"/>
     </row>
     <row r="683">
@@ -62823,7 +63115,7 @@
       <c r="S683" t="inlineStr"/>
       <c r="T683" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U683" t="inlineStr">
@@ -62831,7 +63123,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V683" t="inlineStr"/>
+      <c r="V683" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W683" t="inlineStr"/>
     </row>
     <row r="684">
@@ -62920,7 +63216,7 @@
       <c r="S684" t="inlineStr"/>
       <c r="T684" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U684" t="inlineStr">
@@ -62928,7 +63224,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V684" t="inlineStr"/>
+      <c r="V684" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W684" t="inlineStr"/>
     </row>
     <row r="685">
@@ -63017,7 +63317,7 @@
       <c r="S685" t="inlineStr"/>
       <c r="T685" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U685" t="inlineStr">
@@ -63025,7 +63325,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V685" t="inlineStr"/>
+      <c r="V685" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W685" t="inlineStr"/>
     </row>
     <row r="686">
@@ -63215,7 +63519,7 @@
       <c r="S687" t="inlineStr"/>
       <c r="T687" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U687" t="inlineStr">
@@ -63223,7 +63527,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V687" t="inlineStr"/>
+      <c r="V687" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W687" t="inlineStr"/>
     </row>
     <row r="688">
@@ -63409,7 +63717,7 @@
       <c r="S689" t="inlineStr"/>
       <c r="T689" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U689" t="inlineStr">
@@ -63417,7 +63725,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V689" t="inlineStr"/>
+      <c r="V689" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W689" t="inlineStr"/>
     </row>
     <row r="690">
@@ -63704,7 +64016,7 @@
       <c r="S692" t="inlineStr"/>
       <c r="T692" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U692" t="inlineStr">
@@ -63712,7 +64024,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V692" t="inlineStr"/>
+      <c r="V692" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W692" t="inlineStr"/>
     </row>
     <row r="693">
@@ -63902,7 +64218,7 @@
       <c r="S694" t="inlineStr"/>
       <c r="T694" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U694" t="inlineStr">
@@ -63910,7 +64226,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V694" t="inlineStr"/>
+      <c r="V694" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W694" t="inlineStr"/>
     </row>
     <row r="695">
@@ -64100,7 +64420,7 @@
       <c r="S696" t="inlineStr"/>
       <c r="T696" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U696" t="inlineStr">
@@ -64108,7 +64428,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V696" t="inlineStr"/>
+      <c r="V696" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W696" t="inlineStr"/>
     </row>
     <row r="697">
@@ -64197,7 +64521,7 @@
       <c r="S697" t="inlineStr"/>
       <c r="T697" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U697" t="inlineStr">
@@ -64205,7 +64529,11 @@
           <t>2026-03-05 07:31:00</t>
         </is>
       </c>
-      <c r="V697" t="inlineStr"/>
+      <c r="V697" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W697" t="inlineStr"/>
     </row>
     <row r="698">
@@ -64488,7 +64816,7 @@
       <c r="S700" t="inlineStr"/>
       <c r="T700" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U700" t="inlineStr">
@@ -64496,7 +64824,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V700" t="inlineStr"/>
+      <c r="V700" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W700" t="inlineStr"/>
     </row>
     <row r="701">
@@ -64585,7 +64917,7 @@
       <c r="S701" t="inlineStr"/>
       <c r="T701" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U701" t="inlineStr">
@@ -64593,7 +64925,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V701" t="inlineStr"/>
+      <c r="V701" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W701" t="inlineStr"/>
     </row>
     <row r="702">
@@ -64682,7 +65018,7 @@
       <c r="S702" t="inlineStr"/>
       <c r="T702" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U702" t="inlineStr">
@@ -64690,7 +65026,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V702" t="inlineStr"/>
+      <c r="V702" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W702" t="inlineStr"/>
     </row>
     <row r="703">
@@ -64880,7 +65220,7 @@
       <c r="S704" t="inlineStr"/>
       <c r="T704" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U704" t="inlineStr">
@@ -64888,7 +65228,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V704" t="inlineStr"/>
+      <c r="V704" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W704" t="inlineStr"/>
     </row>
     <row r="705">
@@ -65179,7 +65523,7 @@
       <c r="S707" t="inlineStr"/>
       <c r="T707" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U707" t="inlineStr">
@@ -65187,7 +65531,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V707" t="inlineStr"/>
+      <c r="V707" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W707" t="inlineStr"/>
     </row>
     <row r="708">
@@ -65377,7 +65725,7 @@
       <c r="S709" t="inlineStr"/>
       <c r="T709" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U709" t="inlineStr">
@@ -65385,7 +65733,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V709" t="inlineStr"/>
+      <c r="V709" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W709" t="inlineStr"/>
     </row>
     <row r="710">
@@ -65474,7 +65826,7 @@
       <c r="S710" t="inlineStr"/>
       <c r="T710" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U710" t="inlineStr">
@@ -65482,7 +65834,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V710" t="inlineStr"/>
+      <c r="V710" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W710" t="inlineStr"/>
     </row>
     <row r="711">
@@ -65571,7 +65927,7 @@
       <c r="S711" t="inlineStr"/>
       <c r="T711" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U711" t="inlineStr">
@@ -65579,7 +65935,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V711" t="inlineStr"/>
+      <c r="V711" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W711" t="inlineStr"/>
     </row>
     <row r="712">
@@ -66666,7 +67026,7 @@
       <c r="S722" t="inlineStr"/>
       <c r="T722" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U722" t="inlineStr">
@@ -66674,7 +67034,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V722" t="inlineStr"/>
+      <c r="V722" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W722" t="inlineStr"/>
     </row>
     <row r="723">
@@ -66763,7 +67127,7 @@
       <c r="S723" t="inlineStr"/>
       <c r="T723" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U723" t="inlineStr">
@@ -66771,7 +67135,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V723" t="inlineStr"/>
+      <c r="V723" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W723" t="inlineStr"/>
     </row>
     <row r="724">
@@ -67062,7 +67430,7 @@
       <c r="S726" t="inlineStr"/>
       <c r="T726" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U726" t="inlineStr">
@@ -67070,7 +67438,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V726" t="inlineStr"/>
+      <c r="V726" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W726" t="inlineStr"/>
     </row>
     <row r="727">
@@ -67159,7 +67531,7 @@
       <c r="S727" t="inlineStr"/>
       <c r="T727" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U727" t="inlineStr">
@@ -67167,7 +67539,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V727" t="inlineStr"/>
+      <c r="V727" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W727" t="inlineStr"/>
     </row>
     <row r="728">
@@ -67846,7 +68222,7 @@
       <c r="S734" t="inlineStr"/>
       <c r="T734" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U734" t="inlineStr">
@@ -67854,7 +68230,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V734" t="inlineStr"/>
+      <c r="V734" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W734" t="inlineStr"/>
     </row>
     <row r="735">
@@ -67943,7 +68323,7 @@
       <c r="S735" t="inlineStr"/>
       <c r="T735" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U735" t="inlineStr">
@@ -67951,7 +68331,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V735" t="inlineStr"/>
+      <c r="V735" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W735" t="inlineStr"/>
     </row>
     <row r="736">
@@ -68238,7 +68622,7 @@
       <c r="S738" t="inlineStr"/>
       <c r="T738" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U738" t="inlineStr">
@@ -68246,7 +68630,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V738" t="inlineStr"/>
+      <c r="V738" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W738" t="inlineStr"/>
     </row>
     <row r="739">
@@ -68820,7 +69208,7 @@
       <c r="S744" t="inlineStr"/>
       <c r="T744" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U744" t="inlineStr">
@@ -68828,7 +69216,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V744" t="inlineStr"/>
+      <c r="V744" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W744" t="inlineStr"/>
     </row>
     <row r="745">
@@ -69115,7 +69507,7 @@
       <c r="S747" t="inlineStr"/>
       <c r="T747" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U747" t="inlineStr">
@@ -69123,7 +69515,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V747" t="inlineStr"/>
+      <c r="V747" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W747" t="inlineStr"/>
     </row>
     <row r="748">
@@ -69713,7 +70109,7 @@
       <c r="S753" t="inlineStr"/>
       <c r="T753" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U753" t="inlineStr">
@@ -69721,7 +70117,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V753" t="inlineStr"/>
+      <c r="V753" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W753" t="inlineStr"/>
     </row>
     <row r="754">
@@ -69810,7 +70210,7 @@
       <c r="S754" t="inlineStr"/>
       <c r="T754" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U754" t="inlineStr">
@@ -69818,7 +70218,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V754" t="inlineStr"/>
+      <c r="V754" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W754" t="inlineStr"/>
     </row>
     <row r="755">
@@ -69907,7 +70311,7 @@
       <c r="S755" t="inlineStr"/>
       <c r="T755" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U755" t="inlineStr">
@@ -69915,7 +70319,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V755" t="inlineStr"/>
+      <c r="V755" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W755" t="inlineStr"/>
     </row>
     <row r="756">
@@ -70004,7 +70412,7 @@
       <c r="S756" t="inlineStr"/>
       <c r="T756" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U756" t="inlineStr">
@@ -70012,7 +70420,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V756" t="inlineStr"/>
+      <c r="V756" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W756" t="inlineStr"/>
     </row>
     <row r="757">
@@ -71002,7 +71414,7 @@
       <c r="S766" t="inlineStr"/>
       <c r="T766" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U766" t="inlineStr">
@@ -71010,7 +71422,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V766" t="inlineStr"/>
+      <c r="V766" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W766" t="inlineStr"/>
     </row>
     <row r="767">
@@ -71297,7 +71713,7 @@
       <c r="S769" t="inlineStr"/>
       <c r="T769" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U769" t="inlineStr">
@@ -71305,7 +71721,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V769" t="inlineStr"/>
+      <c r="V769" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W769" t="inlineStr"/>
     </row>
     <row r="770">
@@ -71693,7 +72113,7 @@
       <c r="S773" t="inlineStr"/>
       <c r="T773" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U773" t="inlineStr">
@@ -71701,7 +72121,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V773" t="inlineStr"/>
+      <c r="V773" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W773" t="inlineStr"/>
     </row>
     <row r="774">
@@ -71790,7 +72214,7 @@
       <c r="S774" t="inlineStr"/>
       <c r="T774" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U774" t="inlineStr">
@@ -71798,7 +72222,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V774" t="inlineStr"/>
+      <c r="V774" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W774" t="inlineStr"/>
     </row>
     <row r="775">
@@ -72388,7 +72816,7 @@
       <c r="S780" t="inlineStr"/>
       <c r="T780" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U780" t="inlineStr">
@@ -72396,7 +72824,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V780" t="inlineStr"/>
+      <c r="V780" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W780" t="inlineStr"/>
     </row>
     <row r="781">
@@ -73091,7 +73523,7 @@
       <c r="S787" t="inlineStr"/>
       <c r="T787" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U787" t="inlineStr">
@@ -73099,7 +73531,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V787" t="inlineStr"/>
+      <c r="V787" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W787" t="inlineStr"/>
     </row>
     <row r="788">
@@ -73794,7 +74230,7 @@
       <c r="S794" t="inlineStr"/>
       <c r="T794" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U794" t="inlineStr">
@@ -73802,7 +74238,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V794" t="inlineStr"/>
+      <c r="V794" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W794" t="inlineStr"/>
     </row>
     <row r="795">
@@ -74679,7 +75119,7 @@
       <c r="S803" t="inlineStr"/>
       <c r="T803" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U803" t="inlineStr">
@@ -74687,7 +75127,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V803" t="inlineStr"/>
+      <c r="V803" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W803" t="inlineStr"/>
     </row>
     <row r="804">
@@ -75863,7 +76307,7 @@
       <c r="S815" t="inlineStr"/>
       <c r="T815" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U815" t="inlineStr">
@@ -75871,7 +76315,11 @@
           <t>2026-03-05 08:28:20</t>
         </is>
       </c>
-      <c r="V815" t="inlineStr"/>
+      <c r="V815" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W815" t="inlineStr"/>
     </row>
     <row r="816">
@@ -77051,7 +77499,7 @@
       <c r="S827" t="inlineStr"/>
       <c r="T827" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U827" t="inlineStr">
@@ -77059,7 +77507,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V827" t="inlineStr"/>
+      <c r="V827" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W827" t="inlineStr"/>
     </row>
     <row r="828">
@@ -77346,7 +77798,7 @@
       <c r="S830" t="inlineStr"/>
       <c r="T830" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U830" t="inlineStr">
@@ -77354,7 +77806,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V830" t="inlineStr"/>
+      <c r="V830" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W830" t="inlineStr"/>
     </row>
     <row r="831">
@@ -77540,7 +77996,7 @@
       <c r="S832" t="inlineStr"/>
       <c r="T832" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U832" t="inlineStr">
@@ -77548,7 +78004,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V832" t="inlineStr"/>
+      <c r="V832" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W832" t="inlineStr"/>
     </row>
     <row r="833">
@@ -80235,7 +80695,7 @@
       <c r="S859" t="inlineStr"/>
       <c r="T859" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U859" t="inlineStr">
@@ -80243,7 +80703,11 @@
           <t>2026-03-05 09:03:05</t>
         </is>
       </c>
-      <c r="V859" t="inlineStr"/>
+      <c r="V859" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W859" t="inlineStr"/>
     </row>
     <row r="860">
@@ -81528,7 +81992,7 @@
       <c r="S872" t="inlineStr"/>
       <c r="T872" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U872" t="inlineStr">
@@ -81536,7 +82000,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V872" t="inlineStr"/>
+      <c r="V872" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W872" t="inlineStr"/>
     </row>
     <row r="873">
@@ -81625,7 +82093,7 @@
       <c r="S873" t="inlineStr"/>
       <c r="T873" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U873" t="inlineStr">
@@ -81633,7 +82101,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V873" t="inlineStr"/>
+      <c r="V873" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W873" t="inlineStr"/>
     </row>
     <row r="874">
@@ -83023,7 +83495,7 @@
       <c r="S887" t="inlineStr"/>
       <c r="T887" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U887" t="inlineStr">
@@ -83031,7 +83503,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V887" t="inlineStr"/>
+      <c r="V887" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W887" t="inlineStr"/>
     </row>
     <row r="888">
@@ -83120,7 +83596,7 @@
       <c r="S888" t="inlineStr"/>
       <c r="T888" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U888" t="inlineStr">
@@ -83128,7 +83604,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V888" t="inlineStr"/>
+      <c r="V888" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W888" t="inlineStr"/>
     </row>
     <row r="889">
@@ -83520,7 +84000,7 @@
       <c r="S892" t="inlineStr"/>
       <c r="T892" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U892" t="inlineStr">
@@ -83528,7 +84008,11 @@
           <t>2026-03-05 09:58:26</t>
         </is>
       </c>
-      <c r="V892" t="inlineStr"/>
+      <c r="V892" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W892" t="inlineStr"/>
     </row>
     <row r="893">
@@ -84922,7 +85406,7 @@
       <c r="S906" t="inlineStr"/>
       <c r="T906" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U906" t="inlineStr">
@@ -84930,7 +85414,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V906" t="inlineStr"/>
+      <c r="V906" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W906" t="inlineStr"/>
     </row>
     <row r="907">
@@ -86126,7 +86614,7 @@
       <c r="S918" t="inlineStr"/>
       <c r="T918" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U918" t="inlineStr">
@@ -86134,7 +86622,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V918" t="inlineStr"/>
+      <c r="V918" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W918" t="inlineStr"/>
     </row>
     <row r="919">
@@ -86720,7 +87212,7 @@
       <c r="S924" t="inlineStr"/>
       <c r="T924" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U924" t="inlineStr">
@@ -86728,7 +87220,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V924" t="inlineStr"/>
+      <c r="V924" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W924" t="inlineStr"/>
     </row>
     <row r="925">
@@ -86817,7 +87313,7 @@
       <c r="S925" t="inlineStr"/>
       <c r="T925" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U925" t="inlineStr">
@@ -86825,7 +87321,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V925" t="inlineStr"/>
+      <c r="V925" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W925" t="inlineStr"/>
     </row>
     <row r="926">
@@ -86914,7 +87414,7 @@
       <c r="S926" t="inlineStr"/>
       <c r="T926" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U926" t="inlineStr">
@@ -86922,7 +87422,11 @@
           <t>2026-03-05 10:57:21</t>
         </is>
       </c>
-      <c r="V926" t="inlineStr"/>
+      <c r="V926" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W926" t="inlineStr"/>
     </row>
     <row r="927">
@@ -89415,7 +89919,7 @@
       <c r="S951" t="inlineStr"/>
       <c r="T951" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U951" t="inlineStr">
@@ -89423,7 +89927,11 @@
           <t>2026-03-05 12:34:44</t>
         </is>
       </c>
-      <c r="V951" t="inlineStr"/>
+      <c r="V951" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W951" t="inlineStr"/>
     </row>
     <row r="952">
@@ -89512,7 +90020,7 @@
       <c r="S952" t="inlineStr"/>
       <c r="T952" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U952" t="inlineStr">
@@ -89520,7 +90028,11 @@
           <t>2026-03-05 12:34:44</t>
         </is>
       </c>
-      <c r="V952" t="inlineStr"/>
+      <c r="V952" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W952" t="inlineStr"/>
     </row>
     <row r="953">
@@ -89609,7 +90121,7 @@
       <c r="S953" t="inlineStr"/>
       <c r="T953" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U953" t="inlineStr">
@@ -89617,7 +90129,11 @@
           <t>2026-03-05 12:34:44</t>
         </is>
       </c>
-      <c r="V953" t="inlineStr"/>
+      <c r="V953" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W953" t="inlineStr"/>
     </row>
     <row r="954">
@@ -90300,7 +90816,7 @@
       <c r="S960" t="inlineStr"/>
       <c r="T960" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U960" t="inlineStr">
@@ -90308,7 +90824,11 @@
           <t>2026-03-05 13:00:52</t>
         </is>
       </c>
-      <c r="V960" t="inlineStr"/>
+      <c r="V960" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W960" t="inlineStr"/>
     </row>
     <row r="961">
@@ -90397,7 +90917,7 @@
       <c r="S961" t="inlineStr"/>
       <c r="T961" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U961" t="inlineStr">
@@ -90405,7 +90925,11 @@
           <t>2026-03-05 13:00:52</t>
         </is>
       </c>
-      <c r="V961" t="inlineStr"/>
+      <c r="V961" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W961" t="inlineStr"/>
     </row>
     <row r="962">
@@ -90789,7 +91313,7 @@
       <c r="S965" t="inlineStr"/>
       <c r="T965" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U965" t="inlineStr">
@@ -90797,7 +91321,11 @@
           <t>2026-03-05 14:23:19</t>
         </is>
       </c>
-      <c r="V965" t="inlineStr"/>
+      <c r="V965" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W965" t="inlineStr"/>
     </row>
     <row r="966">
@@ -90886,7 +91414,7 @@
       <c r="S966" t="inlineStr"/>
       <c r="T966" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U966" t="inlineStr">
@@ -90894,7 +91422,11 @@
           <t>2026-03-05 14:23:19</t>
         </is>
       </c>
-      <c r="V966" t="inlineStr"/>
+      <c r="V966" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W966" t="inlineStr"/>
     </row>
     <row r="967">
@@ -90983,7 +91515,7 @@
       <c r="S967" t="inlineStr"/>
       <c r="T967" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U967" t="inlineStr">
@@ -90991,7 +91523,11 @@
           <t>2026-03-05 14:23:19</t>
         </is>
       </c>
-      <c r="V967" t="inlineStr"/>
+      <c r="V967" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W967" t="inlineStr"/>
     </row>
     <row r="968">
@@ -91080,7 +91616,7 @@
       <c r="S968" t="inlineStr"/>
       <c r="T968" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U968" t="inlineStr">
@@ -91088,7 +91624,11 @@
           <t>2026-03-05 14:23:19</t>
         </is>
       </c>
-      <c r="V968" t="inlineStr"/>
+      <c r="V968" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W968" t="inlineStr"/>
     </row>
     <row r="969">
@@ -91177,7 +91717,7 @@
       <c r="S969" t="inlineStr"/>
       <c r="T969" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U969" t="inlineStr">
@@ -91185,7 +91725,11 @@
           <t>2026-03-05 14:23:19</t>
         </is>
       </c>
-      <c r="V969" t="inlineStr"/>
+      <c r="V969" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W969" t="inlineStr"/>
     </row>
     <row r="970">
@@ -91468,7 +92012,7 @@
       <c r="S972" t="inlineStr"/>
       <c r="T972" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U972" t="inlineStr">
@@ -91476,7 +92020,11 @@
           <t>2026-03-05 14:23:19</t>
         </is>
       </c>
-      <c r="V972" t="inlineStr"/>
+      <c r="V972" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W972" t="inlineStr"/>
     </row>
     <row r="973">
@@ -92147,7 +92695,7 @@
       <c r="S979" t="inlineStr"/>
       <c r="T979" t="inlineStr">
         <is>
-          <t>AKTIV</t>
+          <t>LEZART</t>
         </is>
       </c>
       <c r="U979" t="inlineStr">
@@ -92155,7 +92703,11 @@
           <t>2026-03-05 14:23:19</t>
         </is>
       </c>
-      <c r="V979" t="inlineStr"/>
+      <c r="V979" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
       <c r="W979" t="inlineStr"/>
     </row>
     <row r="980">
@@ -92244,16 +92796,1273 @@
       <c r="S980" t="inlineStr"/>
       <c r="T980" t="inlineStr">
         <is>
+          <t>LEZART</t>
+        </is>
+      </c>
+      <c r="U980" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:23:19</t>
+        </is>
+      </c>
+      <c r="V980" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="W980" t="inlineStr"/>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133719_1</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>3133719_1</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133719</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:55:44</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:55:44</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:55:44</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:40:00</t>
+        </is>
+      </c>
+      <c r="J981" t="inlineStr"/>
+      <c r="K981" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="M981" t="inlineStr">
+        <is>
+          <t>47.372562</t>
+        </is>
+      </c>
+      <c r="N981" t="inlineStr">
+        <is>
+          <t>19.250395</t>
+        </is>
+      </c>
+      <c r="O981" t="inlineStr"/>
+      <c r="P981" t="inlineStr"/>
+      <c r="Q981" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R981" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S981" t="inlineStr"/>
+      <c r="T981" t="inlineStr">
+        <is>
           <t>AKTIV</t>
         </is>
       </c>
-      <c r="U980" t="inlineStr">
-        <is>
-          <t>2026-03-05 14:23:19</t>
-        </is>
-      </c>
-      <c r="V980" t="inlineStr"/>
-      <c r="W980" t="inlineStr"/>
+      <c r="U981" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V981" t="inlineStr"/>
+      <c r="W981" t="inlineStr"/>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133720_1</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>3133720_1</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_3133720</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:02:37</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:02:37</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:02:37</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:45:00</t>
+        </is>
+      </c>
+      <c r="J982" t="inlineStr"/>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M982" t="inlineStr">
+        <is>
+          <t>47.568195</t>
+        </is>
+      </c>
+      <c r="N982" t="inlineStr">
+        <is>
+          <t>19.148922</t>
+        </is>
+      </c>
+      <c r="O982" t="inlineStr"/>
+      <c r="P982" t="inlineStr"/>
+      <c r="Q982" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="R982" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="S982" t="inlineStr"/>
+      <c r="T982" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U982" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V982" t="inlineStr"/>
+      <c r="W982" t="inlineStr"/>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011493_1</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>41011493_1</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011493</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:44</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:44</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:30:44</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>2026-03-06 07:30:00</t>
+        </is>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>2026-03-06 14:45:00</t>
+        </is>
+      </c>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>5501</t>
+        </is>
+      </c>
+      <c r="M983" t="inlineStr">
+        <is>
+          <t>46.1455</t>
+        </is>
+      </c>
+      <c r="N983" t="inlineStr">
+        <is>
+          <t>19.07871</t>
+        </is>
+      </c>
+      <c r="O983" t="inlineStr"/>
+      <c r="P983" t="inlineStr"/>
+      <c r="Q983" t="inlineStr">
+        <is>
+          <t>310.0</t>
+        </is>
+      </c>
+      <c r="R983" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S983" t="inlineStr"/>
+      <c r="T983" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U983" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V983" t="inlineStr"/>
+      <c r="W983" t="inlineStr"/>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011495_1</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>41011495_1</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011495</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:36:35</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:32:35</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:36:35</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>2026-03-06 07:30:00</t>
+        </is>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>2026-03-06 14:45:00</t>
+        </is>
+      </c>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>5107</t>
+        </is>
+      </c>
+      <c r="M984" t="inlineStr">
+        <is>
+          <t>46.009033</t>
+        </is>
+      </c>
+      <c r="N984" t="inlineStr">
+        <is>
+          <t>18.742117</t>
+        </is>
+      </c>
+      <c r="O984" t="inlineStr"/>
+      <c r="P984" t="inlineStr"/>
+      <c r="Q984" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="R984" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S984" t="inlineStr"/>
+      <c r="T984" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U984" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V984" t="inlineStr"/>
+      <c r="W984" t="inlineStr"/>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011496_1</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>41011496_1</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011496</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:34:13</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:34:13</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:34:13</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>2026-03-06 07:30:00</t>
+        </is>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>2026-03-06 14:45:00</t>
+        </is>
+      </c>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>55108</t>
+        </is>
+      </c>
+      <c r="M985" t="inlineStr">
+        <is>
+          <t>46.114716</t>
+        </is>
+      </c>
+      <c r="N985" t="inlineStr">
+        <is>
+          <t>19.478966</t>
+        </is>
+      </c>
+      <c r="O985" t="inlineStr"/>
+      <c r="P985" t="inlineStr"/>
+      <c r="Q985" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R985" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S985" t="inlineStr"/>
+      <c r="T985" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U985" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V985" t="inlineStr"/>
+      <c r="W985" t="inlineStr"/>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011497_1</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>41011497_1</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011497</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:36:17</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:36:17</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:36:17</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>2026-03-06 07:30:00</t>
+        </is>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>2026-03-06 14:45:00</t>
+        </is>
+      </c>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>51148</t>
+        </is>
+      </c>
+      <c r="M986" t="inlineStr">
+        <is>
+          <t>45.943306</t>
+        </is>
+      </c>
+      <c r="N986" t="inlineStr">
+        <is>
+          <t>18.876286</t>
+        </is>
+      </c>
+      <c r="O986" t="inlineStr"/>
+      <c r="P986" t="inlineStr"/>
+      <c r="Q986" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R986" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S986" t="inlineStr"/>
+      <c r="T986" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U986" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V986" t="inlineStr"/>
+      <c r="W986" t="inlineStr"/>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011498_1</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>41011498_1</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011498</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:51:42</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:49:28</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:51:42</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>2026-03-09 07:00:00</t>
+        </is>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>2026-03-16 08:00:00</t>
+        </is>
+      </c>
+      <c r="K987" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>6832</t>
+        </is>
+      </c>
+      <c r="M987" t="inlineStr">
+        <is>
+          <t>46.468212</t>
+        </is>
+      </c>
+      <c r="N987" t="inlineStr">
+        <is>
+          <t>17.12717</t>
+        </is>
+      </c>
+      <c r="O987" t="inlineStr"/>
+      <c r="P987" t="inlineStr"/>
+      <c r="Q987" t="inlineStr">
+        <is>
+          <t>480.0</t>
+        </is>
+      </c>
+      <c r="R987" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S987" t="inlineStr"/>
+      <c r="T987" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U987" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V987" t="inlineStr"/>
+      <c r="W987" t="inlineStr"/>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011499_1</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>41011499_1</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011499</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:51:31</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:51:31</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:51:31</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>2026-03-09 07:00:00</t>
+        </is>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>2026-03-16 07:00:00</t>
+        </is>
+      </c>
+      <c r="K988" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>7416</t>
+        </is>
+      </c>
+      <c r="M988" t="inlineStr">
+        <is>
+          <t>46.67938</t>
+        </is>
+      </c>
+      <c r="N988" t="inlineStr">
+        <is>
+          <t>16.528717</t>
+        </is>
+      </c>
+      <c r="O988" t="inlineStr"/>
+      <c r="P988" t="inlineStr"/>
+      <c r="Q988" t="inlineStr">
+        <is>
+          <t>643.0</t>
+        </is>
+      </c>
+      <c r="R988" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S988" t="inlineStr"/>
+      <c r="T988" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U988" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V988" t="inlineStr"/>
+      <c r="W988" t="inlineStr"/>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011500_1</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>41011500_1</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011500</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:56:05</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:53:58</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:56:05</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>2026-03-16 07:00:00</t>
+        </is>
+      </c>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>7426</t>
+        </is>
+      </c>
+      <c r="M989" t="inlineStr">
+        <is>
+          <t>46.684345</t>
+        </is>
+      </c>
+      <c r="N989" t="inlineStr">
+        <is>
+          <t>16.55181</t>
+        </is>
+      </c>
+      <c r="O989" t="inlineStr"/>
+      <c r="P989" t="inlineStr"/>
+      <c r="Q989" t="inlineStr">
+        <is>
+          <t>225.0</t>
+        </is>
+      </c>
+      <c r="R989" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="S989" t="inlineStr"/>
+      <c r="T989" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U989" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V989" t="inlineStr"/>
+      <c r="W989" t="inlineStr"/>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011501_1</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>41011501_1</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011501</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>ConstructionWorks</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:55:42</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:55:42</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:55:42</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>2026-03-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>2026-03-16 07:00:00</t>
+        </is>
+      </c>
+      <c r="K990" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L990" t="inlineStr">
+        <is>
+          <t>74112</t>
+        </is>
+      </c>
+      <c r="M990" t="inlineStr">
+        <is>
+          <t>46.850224</t>
+        </is>
+      </c>
+      <c r="N990" t="inlineStr">
+        <is>
+          <t>16.775257</t>
+        </is>
+      </c>
+      <c r="O990" t="inlineStr"/>
+      <c r="P990" t="inlineStr"/>
+      <c r="Q990" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R990" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="S990" t="inlineStr"/>
+      <c r="T990" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U990" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V990" t="inlineStr"/>
+      <c r="W990" t="inlineStr"/>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011502_1</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>41011502_1</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011502</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:56:28</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:56:28</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:56:28</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:40:00</t>
+        </is>
+      </c>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:55:00</t>
+        </is>
+      </c>
+      <c r="K991" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L991" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="M991" t="inlineStr">
+        <is>
+          <t>47.372562</t>
+        </is>
+      </c>
+      <c r="N991" t="inlineStr">
+        <is>
+          <t>19.250395</t>
+        </is>
+      </c>
+      <c r="O991" t="inlineStr"/>
+      <c r="P991" t="inlineStr"/>
+      <c r="Q991" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R991" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S991" t="inlineStr"/>
+      <c r="T991" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U991" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V991" t="inlineStr"/>
+      <c r="W991" t="inlineStr"/>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011503_1</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>41011503_1</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011503</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>MaintenanceWorks</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:01:40</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:01:40</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:01:40</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>2026-03-05 18:58:00</t>
+        </is>
+      </c>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L992" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="M992" t="inlineStr">
+        <is>
+          <t>47.210556</t>
+        </is>
+      </c>
+      <c r="N992" t="inlineStr">
+        <is>
+          <t>20.283789</t>
+        </is>
+      </c>
+      <c r="O992" t="inlineStr"/>
+      <c r="P992" t="inlineStr"/>
+      <c r="Q992" t="inlineStr">
+        <is>
+          <t>970.0</t>
+        </is>
+      </c>
+      <c r="R992" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S992" t="inlineStr"/>
+      <c r="T992" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U992" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V992" t="inlineStr"/>
+      <c r="W992" t="inlineStr"/>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011504_1</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>41011504_1</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>hu_UTINFORM_41011504</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>AuthorityOperation</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:03:46</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:03:46</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:03:46</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>2026-03-05 17:02:00</t>
+        </is>
+      </c>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>Magyar Közút</t>
+        </is>
+      </c>
+      <c r="L993" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="M993" t="inlineStr">
+        <is>
+          <t>47.568195</t>
+        </is>
+      </c>
+      <c r="N993" t="inlineStr">
+        <is>
+          <t>19.148922</t>
+        </is>
+      </c>
+      <c r="O993" t="inlineStr"/>
+      <c r="P993" t="inlineStr"/>
+      <c r="Q993" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R993" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="S993" t="inlineStr"/>
+      <c r="T993" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
+      </c>
+      <c r="U993" t="inlineStr">
+        <is>
+          <t>2026-03-05 15:12:02</t>
+        </is>
+      </c>
+      <c r="V993" t="inlineStr"/>
+      <c r="W993" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
